--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,57 +421,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>operador</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pn</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sn</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nomenclatura</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inspecao</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>tipo_vencimento</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disponibilidade_valor</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disponibilidade_texto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>data_vencimento</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>vencido</t>
         </is>
@@ -527,7 +515,7 @@
         <v>-4402.8</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="1" t="n">
         <v>41388</v>
       </c>
       <c r="K2" t="b">
@@ -572,7 +560,7 @@
         <v>-4254.8</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="1" t="n">
         <v>39285</v>
       </c>
       <c r="K3" t="b">
@@ -617,7 +605,7 @@
         <v>-2354.2</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="1" t="n">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -662,7 +650,7 @@
         <v>-896.8</v>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="1" t="n">
         <v>40669</v>
       </c>
       <c r="K5" t="b">
@@ -707,7 +695,7 @@
         <v>-854.1</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="1" t="n">
         <v>44884</v>
       </c>
       <c r="K6" t="b">
@@ -752,7 +740,7 @@
         <v>-413.2</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="1" t="n">
         <v>43855</v>
       </c>
       <c r="K7" t="b">
@@ -797,7 +785,7 @@
         <v>-391.8</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="1" t="n">
         <v>42769</v>
       </c>
       <c r="K8" t="b">
@@ -842,7 +830,7 @@
         <v>-371.5</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -887,7 +875,7 @@
         <v>-368.8</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="K10" t="b">
@@ -932,7 +920,7 @@
         <v>-359</v>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="1" t="n">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -977,7 +965,7 @@
         <v>-359</v>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="1" t="n">
         <v>45804</v>
       </c>
       <c r="K12" t="b">
@@ -1022,7 +1010,7 @@
         <v>-351</v>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="1" t="n">
         <v>42821</v>
       </c>
       <c r="K13" t="b">
@@ -1067,7 +1055,7 @@
         <v>-351</v>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1112,7 +1100,7 @@
         <v>-351</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1157,7 +1145,7 @@
         <v>-351</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" s="2" t="n">
+      <c r="J16" s="1" t="n">
         <v>46014</v>
       </c>
       <c r="K16" t="b">
@@ -1202,7 +1190,7 @@
         <v>-345.8</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" s="2" t="n">
+      <c r="J17" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1247,7 +1235,7 @@
         <v>-345.8</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" s="2" t="n">
+      <c r="J18" s="1" t="n">
         <v>46017</v>
       </c>
       <c r="K18" t="b">
@@ -1292,7 +1280,7 @@
         <v>-264.2</v>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="2" t="n">
+      <c r="J19" s="1" t="n">
         <v>40979</v>
       </c>
       <c r="K19" t="b">
@@ -1337,7 +1325,7 @@
         <v>-206.4</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" s="2" t="n">
+      <c r="J20" s="1" t="n">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -1382,7 +1370,7 @@
         <v>-131.6</v>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" s="2" t="n">
+      <c r="J21" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -1427,7 +1415,7 @@
         <v>-131.6</v>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" s="2" t="n">
+      <c r="J22" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -1472,7 +1460,7 @@
         <v>-131.6</v>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" s="2" t="n">
+      <c r="J23" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -1517,7 +1505,7 @@
         <v>-131.6</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" s="2" t="n">
+      <c r="J24" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -1562,7 +1550,7 @@
         <v>-131.6</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" s="2" t="n">
+      <c r="J25" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -1607,7 +1595,7 @@
         <v>-105</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" s="2" t="n">
+      <c r="J26" s="1" t="n">
         <v>46161</v>
       </c>
       <c r="K26" t="b">
@@ -1652,7 +1640,7 @@
         <v>-79.8</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" s="2" t="n">
+      <c r="J27" s="1" t="n">
         <v>43340</v>
       </c>
       <c r="K27" t="b">
@@ -1697,7 +1685,7 @@
         <v>-12.3</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="2" t="n">
+      <c r="J28" s="1" t="n">
         <v>46048</v>
       </c>
       <c r="K28" t="b">
@@ -1742,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" s="2" t="n">
+      <c r="J29" s="1" t="n">
         <v>46211</v>
       </c>
       <c r="K29" t="b">
@@ -1787,7 +1775,7 @@
         <v>3.6</v>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="2" t="n">
+      <c r="J30" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K30" t="b">
@@ -1832,7 +1820,7 @@
         <v>6.2</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" s="2" t="n">
+      <c r="J31" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K31" t="b">
@@ -1877,7 +1865,7 @@
         <v>7.5</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="2" t="n">
+      <c r="J32" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K32" t="b">
@@ -1922,7 +1910,7 @@
         <v>10.7</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="2" t="n">
+      <c r="J33" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K33" t="b">
@@ -1967,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" s="2" t="n">
+      <c r="J34" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K34" t="b">
@@ -2012,7 +2000,7 @@
         <v>30.8</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="2" t="n">
+      <c r="J35" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K35" t="b">
@@ -2057,7 +2045,7 @@
         <v>37.1</v>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" s="2" t="n">
+      <c r="J36" s="1" t="n">
         <v>46256</v>
       </c>
       <c r="K36" t="b">
@@ -2102,7 +2090,7 @@
         <v>42.8</v>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" s="2" t="n">
+      <c r="J37" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="K37" t="b">
@@ -2147,7 +2135,7 @@
         <v>45.2</v>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="2" t="n">
+      <c r="J38" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K38" t="b">
@@ -2192,7 +2180,7 @@
         <v>46</v>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" s="2" t="n">
+      <c r="J39" s="1" t="n">
         <v>46251</v>
       </c>
       <c r="K39" t="b">
@@ -2237,7 +2225,7 @@
         <v>47.5</v>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" s="2" t="n">
+      <c r="J40" s="1" t="n">
         <v>46456</v>
       </c>
       <c r="K40" t="b">
@@ -2282,7 +2270,7 @@
         <v>57.2</v>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" s="2" t="n">
+      <c r="J41" s="1" t="n">
         <v>46246</v>
       </c>
       <c r="K41" t="b">
@@ -2327,7 +2315,7 @@
         <v>59.6</v>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" s="2" t="n">
+      <c r="J42" s="1" t="n">
         <v>46487</v>
       </c>
       <c r="K42" t="b">
@@ -2372,7 +2360,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" s="2" t="n">
+      <c r="J43" s="1" t="n">
         <v>46283</v>
       </c>
       <c r="K43" t="b">
@@ -2417,7 +2405,7 @@
         <v>76.8</v>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" s="2" t="n">
+      <c r="J44" s="1" t="n">
         <v>46285</v>
       </c>
       <c r="K44" t="b">
@@ -2462,7 +2450,7 @@
         <v>83.2</v>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" s="2" t="n">
+      <c r="J45" s="1" t="n">
         <v>46547</v>
       </c>
       <c r="K45" t="b">
@@ -2507,7 +2495,7 @@
         <v>84.5</v>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" s="2" t="n">
+      <c r="J46" s="1" t="n">
         <v>46240</v>
       </c>
       <c r="K46" t="b">
@@ -2552,7 +2540,7 @@
         <v>85.8</v>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" s="2" t="n">
+      <c r="J47" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="K47" t="b">
@@ -2597,7 +2585,7 @@
         <v>86.5</v>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" s="2" t="n">
+      <c r="J48" s="1" t="n">
         <v>46241</v>
       </c>
       <c r="K48" t="b">
@@ -2642,7 +2630,7 @@
         <v>91.7</v>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" s="2" t="n">
+      <c r="J49" s="1" t="n">
         <v>46243</v>
       </c>
       <c r="K49" t="b">
@@ -2687,7 +2675,7 @@
         <v>91.7</v>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" s="2" t="n">
+      <c r="J50" s="1" t="n">
         <v>46243</v>
       </c>
       <c r="K50" t="b">
@@ -2732,7 +2720,7 @@
         <v>91.7</v>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" s="2" t="n">
+      <c r="J51" s="1" t="n">
         <v>46250</v>
       </c>
       <c r="K51" t="b">
@@ -2777,7 +2765,7 @@
         <v>98.90000000000001</v>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" s="2" t="n">
+      <c r="J52" s="1" t="n">
         <v>46253</v>
       </c>
       <c r="K52" t="b">
@@ -2822,7 +2810,7 @@
         <v>105.5</v>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" s="2" t="n">
+      <c r="J53" s="1" t="n">
         <v>46280</v>
       </c>
       <c r="K53" t="b">
@@ -2867,7 +2855,7 @@
         <v>105.6</v>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" s="2" t="n">
+      <c r="J54" s="1" t="n">
         <v>46361</v>
       </c>
       <c r="K54" t="b">
@@ -2912,7 +2900,7 @@
         <v>105.7</v>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" s="2" t="n">
+      <c r="J55" s="1" t="n">
         <v>46362</v>
       </c>
       <c r="K55" t="b">
@@ -2957,7 +2945,7 @@
         <v>110.7</v>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" s="2" t="n">
+      <c r="J56" s="1" t="n">
         <v>46275</v>
       </c>
       <c r="K56" t="b">
@@ -3002,7 +2990,7 @@
         <v>113.2</v>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" s="2" t="n">
+      <c r="J57" s="1" t="n">
         <v>46377</v>
       </c>
       <c r="K57" t="b">
@@ -3047,7 +3035,7 @@
         <v>128.8</v>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" s="2" t="n">
+      <c r="J58" s="1" t="n">
         <v>46434</v>
       </c>
       <c r="K58" t="b">
@@ -3092,7 +3080,7 @@
         <v>128.8</v>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" s="2" t="n">
+      <c r="J59" s="1" t="n">
         <v>46434</v>
       </c>
       <c r="K59" t="b">
@@ -3137,7 +3125,7 @@
         <v>128.8</v>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" s="2" t="n">
+      <c r="J60" s="1" t="n">
         <v>46434</v>
       </c>
       <c r="K60" t="b">
@@ -3182,7 +3170,7 @@
         <v>128.8</v>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" s="2" t="n">
+      <c r="J61" s="1" t="n">
         <v>46434</v>
       </c>
       <c r="K61" t="b">
@@ -3227,7 +3215,7 @@
         <v>128.8</v>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" s="2" t="n">
+      <c r="J62" s="1" t="n">
         <v>46434</v>
       </c>
       <c r="K62" t="b">
@@ -3272,7 +3260,7 @@
         <v>135</v>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" s="2" t="n">
+      <c r="J63" s="1" t="n">
         <v>46280</v>
       </c>
       <c r="K63" t="b">
@@ -3317,7 +3305,7 @@
         <v>150.6</v>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" s="2" t="n">
+      <c r="J64" s="1" t="n">
         <v>46271</v>
       </c>
       <c r="K64" t="b">
@@ -3362,7 +3350,7 @@
         <v>174.2</v>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" s="2" t="n">
+      <c r="J65" s="1" t="n">
         <v>46363</v>
       </c>
       <c r="K65" t="b">
@@ -3407,7 +3395,7 @@
         <v>176.6</v>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" s="2" t="n">
+      <c r="J66" s="1" t="n">
         <v>46334</v>
       </c>
       <c r="K66" t="b">
@@ -3452,7 +3440,7 @@
         <v>177.4</v>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" s="2" t="n">
+      <c r="J67" s="1" t="n">
         <v>46407</v>
       </c>
       <c r="K67" t="b">
@@ -3497,7 +3485,7 @@
         <v>183.9</v>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" s="2" t="n">
+      <c r="J68" s="1" t="n">
         <v>46341</v>
       </c>
       <c r="K68" t="b">
@@ -3542,7 +3530,7 @@
         <v>191.7</v>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" s="2" t="n">
+      <c r="J69" s="1" t="n">
         <v>46300</v>
       </c>
       <c r="K69" t="b">
@@ -3587,7 +3575,7 @@
         <v>200</v>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" s="2" t="n">
+      <c r="J70" s="1" t="n">
         <v>46336</v>
       </c>
       <c r="K70" t="b">
@@ -3632,7 +3620,7 @@
         <v>201.1</v>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" s="2" t="n">
+      <c r="J71" s="1" t="n">
         <v>46319</v>
       </c>
       <c r="K71" t="b">
@@ -3677,7 +3665,7 @@
         <v>206.5</v>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" s="2" t="n">
+      <c r="J72" s="1" t="n">
         <v>46308</v>
       </c>
       <c r="K72" t="b">
@@ -3722,7 +3710,7 @@
         <v>207.5</v>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" s="2" t="n">
+      <c r="J73" s="1" t="n">
         <v>46390</v>
       </c>
       <c r="K73" t="b">
@@ -3767,7 +3755,7 @@
         <v>247</v>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" s="2" t="n">
+      <c r="J74" s="1" t="n">
         <v>46443</v>
       </c>
       <c r="K74" t="b">
@@ -3812,7 +3800,7 @@
         <v>285.3</v>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" s="2" t="n">
+      <c r="J75" s="1" t="n">
         <v>46304</v>
       </c>
       <c r="K75" t="b">
@@ -3857,7 +3845,7 @@
         <v>290.8</v>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" s="2" t="n">
+      <c r="J76" s="1" t="n">
         <v>46362</v>
       </c>
       <c r="K76" t="b">
@@ -3902,7 +3890,7 @@
         <v>295.2</v>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" s="2" t="n">
+      <c r="J77" s="1" t="n">
         <v>46463</v>
       </c>
       <c r="K77" t="b">
@@ -3947,7 +3935,7 @@
         <v>300.2</v>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" s="2" t="n">
+      <c r="J78" s="1" t="n">
         <v>46466</v>
       </c>
       <c r="K78" t="b">
@@ -3996,7 +3984,7 @@
           <t>-317m</t>
         </is>
       </c>
-      <c r="J79" s="2" t="n">
+      <c r="J79" s="1" t="n">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -4045,7 +4033,7 @@
           <t>-164m</t>
         </is>
       </c>
-      <c r="J80" s="2" t="n">
+      <c r="J80" s="1" t="n">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -4094,7 +4082,7 @@
           <t>-27m</t>
         </is>
       </c>
-      <c r="J81" s="2" t="n">
+      <c r="J81" s="1" t="n">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -4143,7 +4131,7 @@
           <t>-25m</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n">
+      <c r="J82" s="1" t="n">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4192,7 +4180,7 @@
           <t>-25m</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n">
+      <c r="J83" s="1" t="n">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4241,7 +4229,7 @@
           <t>-23m</t>
         </is>
       </c>
-      <c r="J84" s="2" t="n">
+      <c r="J84" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4290,7 +4278,7 @@
           <t>-21m</t>
         </is>
       </c>
-      <c r="J85" s="2" t="n">
+      <c r="J85" s="1" t="n">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4339,7 +4327,7 @@
           <t>-7m</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n">
+      <c r="J86" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4388,7 +4376,7 @@
           <t>-3m</t>
         </is>
       </c>
-      <c r="J87" s="2" t="n">
+      <c r="J87" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="K87" t="b">
@@ -4437,7 +4425,7 @@
           <t>-2m</t>
         </is>
       </c>
-      <c r="J88" s="2" t="n">
+      <c r="J88" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="K88" t="b">
@@ -4486,7 +4474,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J89" s="2" t="n">
+      <c r="J89" s="1" t="n">
         <v>46274</v>
       </c>
       <c r="K89" t="b">
@@ -4535,7 +4523,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J90" s="2" t="n">
+      <c r="J90" s="1" t="n">
         <v>46276</v>
       </c>
       <c r="K90" t="b">
@@ -4584,7 +4572,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J91" s="2" t="n">
+      <c r="J91" s="1" t="n">
         <v>46284</v>
       </c>
       <c r="K91" t="b">
@@ -4633,7 +4621,7 @@
           <t>3m</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n">
+      <c r="J92" s="1" t="n">
         <v>46317</v>
       </c>
       <c r="K92" t="b">
@@ -4682,7 +4670,7 @@
           <t>3m</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n">
+      <c r="J93" s="1" t="n">
         <v>46319</v>
       </c>
       <c r="K93" t="b">
@@ -4731,7 +4719,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J94" s="2" t="n">
+      <c r="J94" s="1" t="n">
         <v>46333</v>
       </c>
       <c r="K94" t="b">
@@ -4780,7 +4768,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n">
+      <c r="J95" s="1" t="n">
         <v>46338</v>
       </c>
       <c r="K95" t="b">
@@ -4829,7 +4817,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n">
+      <c r="J96" s="1" t="n">
         <v>46338</v>
       </c>
       <c r="K96" t="b">
@@ -4878,7 +4866,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n">
+      <c r="J97" s="1" t="n">
         <v>46341</v>
       </c>
       <c r="K97" t="b">
@@ -4927,7 +4915,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n">
+      <c r="J98" s="1" t="n">
         <v>46344</v>
       </c>
       <c r="K98" t="b">
@@ -4976,7 +4964,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J99" s="2" t="n">
+      <c r="J99" s="1" t="n">
         <v>46354</v>
       </c>
       <c r="K99" t="b">
@@ -5025,7 +5013,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n">
+      <c r="J100" s="1" t="n">
         <v>46360</v>
       </c>
       <c r="K100" t="b">
@@ -5074,7 +5062,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n">
+      <c r="J101" s="1" t="n">
         <v>46360</v>
       </c>
       <c r="K101" t="b">
@@ -5123,7 +5111,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n">
+      <c r="J102" s="1" t="n">
         <v>46366</v>
       </c>
       <c r="K102" t="b">
@@ -5172,7 +5160,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J103" s="2" t="n">
+      <c r="J103" s="1" t="n">
         <v>46375</v>
       </c>
       <c r="K103" t="b">
@@ -5221,7 +5209,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J104" s="2" t="n">
+      <c r="J104" s="1" t="n">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -5270,7 +5258,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J105" s="2" t="n">
+      <c r="J105" s="1" t="n">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -5319,7 +5307,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n">
+      <c r="J106" s="1" t="n">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -5368,7 +5356,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n">
+      <c r="J107" s="1" t="n">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -5417,7 +5405,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n">
+      <c r="J108" s="1" t="n">
         <v>46413</v>
       </c>
       <c r="K108" t="b">
@@ -5466,7 +5454,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n">
+      <c r="J109" s="1" t="n">
         <v>46424</v>
       </c>
       <c r="K109" t="b">
@@ -5515,7 +5503,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J110" s="2" t="n">
+      <c r="J110" s="1" t="n">
         <v>46427</v>
       </c>
       <c r="K110" t="b">
@@ -5564,7 +5552,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J111" s="2" t="n">
+      <c r="J111" s="1" t="n">
         <v>46437</v>
       </c>
       <c r="K111" t="b">
@@ -5613,7 +5601,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n">
+      <c r="J112" s="1" t="n">
         <v>46451</v>
       </c>
       <c r="K112" t="b">
@@ -5662,7 +5650,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J113" s="1" t="n">
         <v>46455</v>
       </c>
       <c r="K113" t="b">
@@ -5711,7 +5699,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J114" s="2" t="n">
+      <c r="J114" s="1" t="n">
         <v>46457</v>
       </c>
       <c r="K114" t="b">
@@ -5760,7 +5748,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J115" s="1" t="n">
         <v>46462</v>
       </c>
       <c r="K115" t="b">
@@ -5809,7 +5797,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J116" s="2" t="n">
+      <c r="J116" s="1" t="n">
         <v>46464</v>
       </c>
       <c r="K116" t="b">
@@ -5858,7 +5846,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J117" s="1" t="n">
         <v>46470</v>
       </c>
       <c r="K117" t="b">
@@ -5907,7 +5895,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J118" s="2" t="n">
+      <c r="J118" s="1" t="n">
         <v>46485</v>
       </c>
       <c r="K118" t="b">
@@ -5956,7 +5944,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J119" s="2" t="n">
+      <c r="J119" s="1" t="n">
         <v>46499</v>
       </c>
       <c r="K119" t="b">
@@ -6005,7 +5993,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J120" s="1" t="n">
         <v>46504</v>
       </c>
       <c r="K120" t="b">
@@ -6054,7 +6042,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J121" s="2" t="n">
+      <c r="J121" s="1" t="n">
         <v>46504</v>
       </c>
       <c r="K121" t="b">
@@ -6103,7 +6091,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J122" s="2" t="n">
+      <c r="J122" s="1" t="n">
         <v>46507</v>
       </c>
       <c r="K122" t="b">
@@ -6152,7 +6140,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J123" s="2" t="n">
+      <c r="J123" s="1" t="n">
         <v>46508</v>
       </c>
       <c r="K123" t="b">
@@ -6201,7 +6189,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J124" s="2" t="n">
+      <c r="J124" s="1" t="n">
         <v>46512</v>
       </c>
       <c r="K124" t="b">
@@ -6250,7 +6238,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J125" s="1" t="n">
         <v>46512</v>
       </c>
       <c r="K125" t="b">
@@ -6299,7 +6287,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J126" s="2" t="n">
+      <c r="J126" s="1" t="n">
         <v>46528</v>
       </c>
       <c r="K126" t="b">
@@ -6348,7 +6336,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J127" s="1" t="n">
         <v>46529</v>
       </c>
       <c r="K127" t="b">
@@ -6397,7 +6385,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J128" s="1" t="n">
         <v>46537</v>
       </c>
       <c r="K128" t="b">
@@ -6446,7 +6434,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J129" s="2" t="n">
+      <c r="J129" s="1" t="n">
         <v>46546</v>
       </c>
       <c r="K129" t="b">
@@ -6495,7 +6483,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J130" s="2" t="n">
+      <c r="J130" s="1" t="n">
         <v>46547</v>
       </c>
       <c r="K130" t="b">
@@ -6544,7 +6532,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J131" s="2" t="n">
+      <c r="J131" s="1" t="n">
         <v>46547</v>
       </c>
       <c r="K131" t="b">
@@ -6593,7 +6581,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J132" s="2" t="n">
+      <c r="J132" s="1" t="n">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -6642,7 +6630,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J133" s="2" t="n">
+      <c r="J133" s="1" t="n">
         <v>46551</v>
       </c>
       <c r="K133" t="b">
@@ -6691,7 +6679,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J134" s="2" t="n">
+      <c r="J134" s="1" t="n">
         <v>46560</v>
       </c>
       <c r="K134" t="b">
@@ -6740,7 +6728,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J135" s="2" t="n">
+      <c r="J135" s="1" t="n">
         <v>46564</v>
       </c>
       <c r="K135" t="b">
@@ -6789,7 +6777,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J136" s="2" t="n">
+      <c r="J136" s="1" t="n">
         <v>46567</v>
       </c>
       <c r="K136" t="b">
@@ -6838,7 +6826,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J137" s="2" t="n">
+      <c r="J137" s="1" t="n">
         <v>46568</v>
       </c>
       <c r="K137" t="b">
@@ -6887,7 +6875,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J138" s="2" t="n">
+      <c r="J138" s="1" t="n">
         <v>46571</v>
       </c>
       <c r="K138" t="b">
@@ -6936,7 +6924,7 @@
           <t>-14d</t>
         </is>
       </c>
-      <c r="J139" s="2" t="n">
+      <c r="J139" s="1" t="n">
         <v>46197</v>
       </c>
       <c r="K139" t="b">
@@ -6985,7 +6973,7 @@
           <t>1d</t>
         </is>
       </c>
-      <c r="J140" s="2" t="n">
+      <c r="J140" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="K140" t="b">
@@ -7034,7 +7022,7 @@
           <t>14d</t>
         </is>
       </c>
-      <c r="J141" s="2" t="n">
+      <c r="J141" s="1" t="n">
         <v>46225</v>
       </c>
       <c r="K141" t="b">
@@ -7083,7 +7071,7 @@
           <t>23d</t>
         </is>
       </c>
-      <c r="J142" s="2" t="n">
+      <c r="J142" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K142" t="b">
@@ -7132,7 +7120,7 @@
           <t>24d</t>
         </is>
       </c>
-      <c r="J143" s="2" t="n">
+      <c r="J143" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="K143" t="b">
@@ -7181,7 +7169,7 @@
           <t>1me23d</t>
         </is>
       </c>
-      <c r="J144" s="2" t="n">
+      <c r="J144" s="1" t="n">
         <v>46263</v>
       </c>
       <c r="K144" t="b">
@@ -7230,7 +7218,7 @@
           <t>1me25d</t>
         </is>
       </c>
-      <c r="J145" s="2" t="n">
+      <c r="J145" s="1" t="n">
         <v>46266</v>
       </c>
       <c r="K145" t="b">
@@ -7275,7 +7263,7 @@
         <v>-1476</v>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" s="2" t="n">
+      <c r="J146" s="1" t="n">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -7320,7 +7308,7 @@
         <v>-1469</v>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" s="2" t="n">
+      <c r="J147" s="1" t="n">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -7365,7 +7353,7 @@
         <v>-1121</v>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" s="2" t="n">
+      <c r="J148" s="1" t="n">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -7410,7 +7398,7 @@
         <v>-1018</v>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" s="2" t="n">
+      <c r="J149" s="1" t="n">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -7455,7 +7443,7 @@
         <v>-950</v>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" s="2" t="n">
+      <c r="J150" s="1" t="n">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -7500,7 +7488,7 @@
         <v>-943</v>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" s="2" t="n">
+      <c r="J151" s="1" t="n">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -7545,7 +7533,7 @@
         <v>-252</v>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" s="2" t="n">
+      <c r="J152" s="1" t="n">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -7590,7 +7578,7 @@
         <v>-196</v>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" s="2" t="n">
+      <c r="J153" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="K153" t="b">
@@ -7635,7 +7623,7 @@
         <v>-196</v>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" s="2" t="n">
+      <c r="J154" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="K154" t="b">
@@ -7680,7 +7668,7 @@
         <v>-47</v>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" s="2" t="n">
+      <c r="J155" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="K155" t="b">
@@ -7725,7 +7713,7 @@
         <v>-47</v>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" s="2" t="n">
+      <c r="J156" s="1" t="n">
         <v>46176</v>
       </c>
       <c r="K156" t="b">
@@ -7770,7 +7758,7 @@
         <v>-33</v>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" s="2" t="n">
+      <c r="J157" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="K157" t="b">
@@ -7815,7 +7803,7 @@
         <v>-33</v>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" s="2" t="n">
+      <c r="J158" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="K158" t="b">
@@ -7860,7 +7848,7 @@
         <v>-6</v>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" s="2" t="n">
+      <c r="J159" s="1" t="n">
         <v>45967</v>
       </c>
       <c r="K159" t="b">
@@ -7905,7 +7893,7 @@
         <v>43</v>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" s="2" t="n">
+      <c r="J160" s="1" t="n">
         <v>46440</v>
       </c>
       <c r="K160" t="b">
@@ -7950,7 +7938,7 @@
         <v>43</v>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" s="2" t="n">
+      <c r="J161" s="1" t="n">
         <v>46440</v>
       </c>
       <c r="K161" t="b">
@@ -7995,7 +7983,7 @@
         <v>73</v>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" s="2" t="n">
+      <c r="J162" s="1" t="n">
         <v>46264</v>
       </c>
       <c r="K162" t="b">
@@ -8040,7 +8028,7 @@
         <v>73</v>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" s="2" t="n">
+      <c r="J163" s="1" t="n">
         <v>46264</v>
       </c>
       <c r="K163" t="b">
@@ -8085,7 +8073,7 @@
         <v>102</v>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" s="2" t="n">
+      <c r="J164" s="1" t="n">
         <v>46463</v>
       </c>
       <c r="K164" t="b">
@@ -8130,7 +8118,7 @@
         <v>118</v>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" s="2" t="n">
+      <c r="J165" s="1" t="n">
         <v>46337</v>
       </c>
       <c r="K165" t="b">
@@ -8175,7 +8163,7 @@
         <v>146</v>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" s="2" t="n">
+      <c r="J166" s="1" t="n">
         <v>46451</v>
       </c>
       <c r="K166" t="b">
@@ -8220,7 +8208,7 @@
         <v>152</v>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" s="2" t="n">
+      <c r="J167" s="1" t="n">
         <v>46245</v>
       </c>
       <c r="K167" t="b">
@@ -8265,7 +8253,7 @@
         <v>152</v>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" s="2" t="n">
+      <c r="J168" s="1" t="n">
         <v>46245</v>
       </c>
       <c r="K168" t="b">
@@ -8310,7 +8298,7 @@
         <v>163</v>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" s="2" t="n">
+      <c r="J169" s="1" t="n">
         <v>46324</v>
       </c>
       <c r="K169" t="b">
@@ -8355,7 +8343,7 @@
         <v>163</v>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" s="2" t="n">
+      <c r="J170" s="1" t="n">
         <v>46324</v>
       </c>
       <c r="K170" t="b">
@@ -8400,7 +8388,7 @@
         <v>164</v>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" s="2" t="n">
+      <c r="J171" s="1" t="n">
         <v>46426</v>
       </c>
       <c r="K171" t="b">
@@ -8445,7 +8433,7 @@
         <v>175</v>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" s="2" t="n">
+      <c r="J172" s="1" t="n">
         <v>46383</v>
       </c>
       <c r="K172" t="b">
@@ -8490,7 +8478,7 @@
         <v>186</v>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" s="2" t="n">
+      <c r="J173" s="1" t="n">
         <v>46392</v>
       </c>
       <c r="K173" t="b">
@@ -8535,7 +8523,7 @@
         <v>205</v>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" s="2" t="n">
+      <c r="J174" s="1" t="n">
         <v>46390</v>
       </c>
       <c r="K174" t="b">
@@ -8580,7 +8568,7 @@
         <v>207</v>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" s="2" t="n">
+      <c r="J175" s="1" t="n">
         <v>46392</v>
       </c>
       <c r="K175" t="b">
@@ -8625,7 +8613,7 @@
         <v>218</v>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" s="2" t="n">
+      <c r="J176" s="1" t="n">
         <v>46506</v>
       </c>
       <c r="K176" t="b">
@@ -8670,7 +8658,7 @@
         <v>246</v>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" s="2" t="n">
+      <c r="J177" s="1" t="n">
         <v>46478</v>
       </c>
       <c r="K177" t="b">
@@ -8715,7 +8703,7 @@
         <v>248</v>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" s="2" t="n">
+      <c r="J178" s="1" t="n">
         <v>46500</v>
       </c>
       <c r="K178" t="b">
@@ -8760,7 +8748,7 @@
         <v>276</v>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" s="2" t="n">
+      <c r="J179" s="1" t="n">
         <v>46430</v>
       </c>
       <c r="K179" t="b">
@@ -8805,7 +8793,7 @@
         <v>276</v>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" s="2" t="n">
+      <c r="J180" s="1" t="n">
         <v>46430</v>
       </c>
       <c r="K180" t="b">
@@ -8850,7 +8838,7 @@
         <v>290</v>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" s="2" t="n">
+      <c r="J181" s="1" t="n">
         <v>46467</v>
       </c>
       <c r="K181" t="b">
@@ -8895,7 +8883,7 @@
         <v>317</v>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" s="2" t="n">
+      <c r="J182" s="1" t="n">
         <v>46529</v>
       </c>
       <c r="K182" t="b">
@@ -8940,7 +8928,7 @@
         <v>420</v>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" s="2" t="n">
+      <c r="J183" s="1" t="n">
         <v>46566</v>
       </c>
       <c r="K183" t="b">
@@ -8985,7 +8973,7 @@
         <v>426</v>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" s="2" t="n">
+      <c r="J184" s="1" t="n">
         <v>46571</v>
       </c>
       <c r="K184" t="b">
@@ -9030,7 +9018,7 @@
         <v>721</v>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" s="2" t="n">
+      <c r="J185" s="1" t="n">
         <v>46325</v>
       </c>
       <c r="K185" t="b">
@@ -9075,7 +9063,7 @@
         <v>721</v>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" s="2" t="n">
+      <c r="J186" s="1" t="n">
         <v>46325</v>
       </c>
       <c r="K186" t="b">
@@ -9120,7 +9108,7 @@
         <v>850</v>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" s="2" t="n">
+      <c r="J187" s="1" t="n">
         <v>46345</v>
       </c>
       <c r="K187" t="b">
@@ -9165,7 +9153,7 @@
         <v>850</v>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" s="2" t="n">
+      <c r="J188" s="1" t="n">
         <v>46345</v>
       </c>
       <c r="K188" t="b">
@@ -9210,7 +9198,7 @@
         <v>1661</v>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" s="2" t="n">
+      <c r="J189" s="1" t="n">
         <v>46498</v>
       </c>
       <c r="K189" t="b">
@@ -9255,7 +9243,7 @@
         <v>1661</v>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" s="2" t="n">
+      <c r="J190" s="1" t="n">
         <v>46498</v>
       </c>
       <c r="K190" t="b">
@@ -9300,7 +9288,7 @@
         <v>488</v>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" s="2" t="n">
+      <c r="J191" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -9345,7 +9333,7 @@
         <v>25565</v>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" s="2" t="n">
+      <c r="J192" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -9390,7 +9378,7 @@
         <v>25567</v>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" s="2" t="n">
+      <c r="J193" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -9435,7 +9423,7 @@
         <v>31293</v>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" s="2" t="n">
+      <c r="J194" s="1" t="n">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,57 +433,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>matricula</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>operador</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pn</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sn</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nomenclatura</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>inspecao</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tipo_vencimento</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>disponibilidade_valor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>disponibilidade_texto</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>data_vencimento</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>vencido</t>
         </is>
@@ -515,7 +527,7 @@
         <v>-4402.8</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" s="1" t="n">
+      <c r="J2" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K2" t="b">
@@ -560,7 +572,7 @@
         <v>-4254.8</v>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="2" t="n">
         <v>39285</v>
       </c>
       <c r="K3" t="b">
@@ -605,7 +617,7 @@
         <v>-2354.2</v>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -650,7 +662,7 @@
         <v>-896.8</v>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40669</v>
       </c>
       <c r="K5" t="b">
@@ -695,7 +707,7 @@
         <v>-854.1</v>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>44884</v>
       </c>
       <c r="K6" t="b">
@@ -740,7 +752,7 @@
         <v>-413.2</v>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43855</v>
       </c>
       <c r="K7" t="b">
@@ -785,7 +797,7 @@
         <v>-391.8</v>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="K8" t="b">
@@ -830,7 +842,7 @@
         <v>-371.5</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -875,7 +887,7 @@
         <v>-368.8</v>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="K10" t="b">
@@ -920,7 +932,7 @@
         <v>-359</v>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -965,7 +977,7 @@
         <v>-359</v>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>45804</v>
       </c>
       <c r="K12" t="b">
@@ -1010,7 +1022,7 @@
         <v>-351</v>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42821</v>
       </c>
       <c r="K13" t="b">
@@ -1055,7 +1067,7 @@
         <v>-351</v>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1100,7 +1112,7 @@
         <v>-351</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1145,7 +1157,7 @@
         <v>-351</v>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>46014</v>
       </c>
       <c r="K16" t="b">
@@ -1190,7 +1202,7 @@
         <v>-345.8</v>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1235,7 +1247,7 @@
         <v>-345.8</v>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="K18" t="b">
@@ -1280,7 +1292,7 @@
         <v>-264.2</v>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>40979</v>
       </c>
       <c r="K19" t="b">
@@ -1325,7 +1337,7 @@
         <v>-206.4</v>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -1370,7 +1382,7 @@
         <v>-131.6</v>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -1415,7 +1427,7 @@
         <v>-131.6</v>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -1460,7 +1472,7 @@
         <v>-131.6</v>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -1505,7 +1517,7 @@
         <v>-131.6</v>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -1550,7 +1562,7 @@
         <v>-131.6</v>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -1595,7 +1607,7 @@
         <v>-105</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>46161</v>
       </c>
       <c r="K26" t="b">
@@ -1640,7 +1652,7 @@
         <v>-79.8</v>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43340</v>
       </c>
       <c r="K27" t="b">
@@ -1685,7 +1697,7 @@
         <v>-12.3</v>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>46048</v>
       </c>
       <c r="K28" t="b">
@@ -1730,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="K29" t="b">
@@ -1775,7 +1787,7 @@
         <v>3.6</v>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K30" t="b">
@@ -1820,7 +1832,7 @@
         <v>6.2</v>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K31" t="b">
@@ -1865,7 +1877,7 @@
         <v>7.5</v>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K32" t="b">
@@ -1910,7 +1922,7 @@
         <v>10.7</v>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K33" t="b">
@@ -1955,7 +1967,7 @@
         <v>20</v>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K34" t="b">
@@ -2000,7 +2012,7 @@
         <v>30.8</v>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K35" t="b">
@@ -2045,7 +2057,7 @@
         <v>37.1</v>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>46256</v>
       </c>
       <c r="K36" t="b">
@@ -2090,7 +2102,7 @@
         <v>42.8</v>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="K37" t="b">
@@ -2135,7 +2147,7 @@
         <v>45.2</v>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K38" t="b">
@@ -2180,7 +2192,7 @@
         <v>46</v>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="K39" t="b">
@@ -2225,7 +2237,7 @@
         <v>47.5</v>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>46456</v>
       </c>
       <c r="K40" t="b">
@@ -2270,7 +2282,7 @@
         <v>57.2</v>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>46246</v>
       </c>
       <c r="K41" t="b">
@@ -2315,7 +2327,7 @@
         <v>59.6</v>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>46487</v>
       </c>
       <c r="K42" t="b">
@@ -2360,7 +2372,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="K43" t="b">
@@ -2405,7 +2417,7 @@
         <v>76.8</v>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="K44" t="b">
@@ -2450,7 +2462,7 @@
         <v>83.2</v>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>46547</v>
       </c>
       <c r="K45" t="b">
@@ -2495,7 +2507,7 @@
         <v>84.5</v>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K46" t="b">
@@ -2540,7 +2552,7 @@
         <v>85.8</v>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="K47" t="b">
@@ -2585,7 +2597,7 @@
         <v>86.5</v>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="K48" t="b">
@@ -2630,7 +2642,7 @@
         <v>91.7</v>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>46243</v>
       </c>
       <c r="K49" t="b">
@@ -2675,7 +2687,7 @@
         <v>91.7</v>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>46243</v>
       </c>
       <c r="K50" t="b">
@@ -2720,7 +2732,7 @@
         <v>91.7</v>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>46250</v>
       </c>
       <c r="K51" t="b">
@@ -2765,7 +2777,7 @@
         <v>98.90000000000001</v>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>46253</v>
       </c>
       <c r="K52" t="b">
@@ -2810,7 +2822,7 @@
         <v>105.5</v>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>46280</v>
       </c>
       <c r="K53" t="b">
@@ -2855,7 +2867,7 @@
         <v>105.6</v>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>46361</v>
       </c>
       <c r="K54" t="b">
@@ -2900,7 +2912,7 @@
         <v>105.7</v>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="K55" t="b">
@@ -2945,7 +2957,7 @@
         <v>110.7</v>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="K56" t="b">
@@ -2990,7 +3002,7 @@
         <v>113.2</v>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>46377</v>
       </c>
       <c r="K57" t="b">
@@ -3035,7 +3047,7 @@
         <v>128.8</v>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>46434</v>
       </c>
       <c r="K58" t="b">
@@ -3080,7 +3092,7 @@
         <v>128.8</v>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>46434</v>
       </c>
       <c r="K59" t="b">
@@ -3125,7 +3137,7 @@
         <v>128.8</v>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>46434</v>
       </c>
       <c r="K60" t="b">
@@ -3170,7 +3182,7 @@
         <v>128.8</v>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>46434</v>
       </c>
       <c r="K61" t="b">
@@ -3215,7 +3227,7 @@
         <v>128.8</v>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>46434</v>
       </c>
       <c r="K62" t="b">
@@ -3260,7 +3272,7 @@
         <v>135</v>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>46280</v>
       </c>
       <c r="K63" t="b">
@@ -3305,7 +3317,7 @@
         <v>150.6</v>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="K64" t="b">
@@ -3350,7 +3362,7 @@
         <v>174.2</v>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46363</v>
       </c>
       <c r="K65" t="b">
@@ -3395,7 +3407,7 @@
         <v>176.6</v>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46334</v>
       </c>
       <c r="K66" t="b">
@@ -3440,7 +3452,7 @@
         <v>177.4</v>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46407</v>
       </c>
       <c r="K67" t="b">
@@ -3485,7 +3497,7 @@
         <v>183.9</v>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="K68" t="b">
@@ -3530,7 +3542,7 @@
         <v>191.7</v>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>46300</v>
       </c>
       <c r="K69" t="b">
@@ -3575,7 +3587,7 @@
         <v>200</v>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46336</v>
       </c>
       <c r="K70" t="b">
@@ -3620,7 +3632,7 @@
         <v>201.1</v>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46319</v>
       </c>
       <c r="K71" t="b">
@@ -3665,7 +3677,7 @@
         <v>206.5</v>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46308</v>
       </c>
       <c r="K72" t="b">
@@ -3710,7 +3722,7 @@
         <v>207.5</v>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="K73" t="b">
@@ -3755,7 +3767,7 @@
         <v>247</v>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46443</v>
       </c>
       <c r="K74" t="b">
@@ -3800,7 +3812,7 @@
         <v>285.3</v>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46304</v>
       </c>
       <c r="K75" t="b">
@@ -3845,7 +3857,7 @@
         <v>290.8</v>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" s="1" t="n">
+      <c r="J76" s="2" t="n">
         <v>46362</v>
       </c>
       <c r="K76" t="b">
@@ -3890,7 +3902,7 @@
         <v>295.2</v>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" s="1" t="n">
+      <c r="J77" s="2" t="n">
         <v>46463</v>
       </c>
       <c r="K77" t="b">
@@ -3935,7 +3947,7 @@
         <v>300.2</v>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" s="1" t="n">
+      <c r="J78" s="2" t="n">
         <v>46466</v>
       </c>
       <c r="K78" t="b">
@@ -3984,7 +3996,7 @@
           <t>-317m</t>
         </is>
       </c>
-      <c r="J79" s="1" t="n">
+      <c r="J79" s="2" t="n">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -4033,7 +4045,7 @@
           <t>-164m</t>
         </is>
       </c>
-      <c r="J80" s="1" t="n">
+      <c r="J80" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -4082,7 +4094,7 @@
           <t>-27m</t>
         </is>
       </c>
-      <c r="J81" s="1" t="n">
+      <c r="J81" s="2" t="n">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -4131,7 +4143,7 @@
           <t>-25m</t>
         </is>
       </c>
-      <c r="J82" s="1" t="n">
+      <c r="J82" s="2" t="n">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4180,7 +4192,7 @@
           <t>-25m</t>
         </is>
       </c>
-      <c r="J83" s="1" t="n">
+      <c r="J83" s="2" t="n">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4229,7 +4241,7 @@
           <t>-23m</t>
         </is>
       </c>
-      <c r="J84" s="1" t="n">
+      <c r="J84" s="2" t="n">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4278,7 +4290,7 @@
           <t>-21m</t>
         </is>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="J85" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4327,7 +4339,7 @@
           <t>-7m</t>
         </is>
       </c>
-      <c r="J86" s="1" t="n">
+      <c r="J86" s="2" t="n">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4376,7 +4388,7 @@
           <t>-3m</t>
         </is>
       </c>
-      <c r="J87" s="1" t="n">
+      <c r="J87" s="2" t="n">
         <v>46106</v>
       </c>
       <c r="K87" t="b">
@@ -4425,7 +4437,7 @@
           <t>-2m</t>
         </is>
       </c>
-      <c r="J88" s="1" t="n">
+      <c r="J88" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K88" t="b">
@@ -4474,7 +4486,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="J89" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="K89" t="b">
@@ -4523,7 +4535,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J90" s="1" t="n">
+      <c r="J90" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="K90" t="b">
@@ -4572,7 +4584,7 @@
           <t>2m</t>
         </is>
       </c>
-      <c r="J91" s="1" t="n">
+      <c r="J91" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="K91" t="b">
@@ -4621,7 +4633,7 @@
           <t>3m</t>
         </is>
       </c>
-      <c r="J92" s="1" t="n">
+      <c r="J92" s="2" t="n">
         <v>46317</v>
       </c>
       <c r="K92" t="b">
@@ -4670,7 +4682,7 @@
           <t>3m</t>
         </is>
       </c>
-      <c r="J93" s="1" t="n">
+      <c r="J93" s="2" t="n">
         <v>46319</v>
       </c>
       <c r="K93" t="b">
@@ -4719,7 +4731,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J94" s="1" t="n">
+      <c r="J94" s="2" t="n">
         <v>46333</v>
       </c>
       <c r="K94" t="b">
@@ -4768,7 +4780,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="J95" s="2" t="n">
         <v>46338</v>
       </c>
       <c r="K95" t="b">
@@ -4817,7 +4829,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="J96" s="2" t="n">
         <v>46338</v>
       </c>
       <c r="K96" t="b">
@@ -4866,7 +4878,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J97" s="1" t="n">
+      <c r="J97" s="2" t="n">
         <v>46341</v>
       </c>
       <c r="K97" t="b">
@@ -4915,7 +4927,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="J98" s="2" t="n">
         <v>46344</v>
       </c>
       <c r="K98" t="b">
@@ -4964,7 +4976,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="J99" s="2" t="n">
         <v>46354</v>
       </c>
       <c r="K99" t="b">
@@ -5013,7 +5025,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J100" s="1" t="n">
+      <c r="J100" s="2" t="n">
         <v>46360</v>
       </c>
       <c r="K100" t="b">
@@ -5062,7 +5074,7 @@
           <t>4m</t>
         </is>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="J101" s="2" t="n">
         <v>46360</v>
       </c>
       <c r="K101" t="b">
@@ -5111,7 +5123,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="J102" s="2" t="n">
         <v>46366</v>
       </c>
       <c r="K102" t="b">
@@ -5160,7 +5172,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="J103" s="2" t="n">
         <v>46375</v>
       </c>
       <c r="K103" t="b">
@@ -5209,7 +5221,7 @@
           <t>5m</t>
         </is>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="2" t="n">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -5258,7 +5270,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="J105" s="2" t="n">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -5307,7 +5319,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J106" s="1" t="n">
+      <c r="J106" s="2" t="n">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -5356,7 +5368,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J107" s="1" t="n">
+      <c r="J107" s="2" t="n">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -5405,7 +5417,7 @@
           <t>6m</t>
         </is>
       </c>
-      <c r="J108" s="1" t="n">
+      <c r="J108" s="2" t="n">
         <v>46413</v>
       </c>
       <c r="K108" t="b">
@@ -5454,7 +5466,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J109" s="1" t="n">
+      <c r="J109" s="2" t="n">
         <v>46424</v>
       </c>
       <c r="K109" t="b">
@@ -5503,7 +5515,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="J110" s="2" t="n">
         <v>46427</v>
       </c>
       <c r="K110" t="b">
@@ -5552,7 +5564,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J111" s="1" t="n">
+      <c r="J111" s="2" t="n">
         <v>46437</v>
       </c>
       <c r="K111" t="b">
@@ -5601,7 +5613,7 @@
           <t>7m</t>
         </is>
       </c>
-      <c r="J112" s="1" t="n">
+      <c r="J112" s="2" t="n">
         <v>46451</v>
       </c>
       <c r="K112" t="b">
@@ -5650,7 +5662,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J113" s="1" t="n">
+      <c r="J113" s="2" t="n">
         <v>46455</v>
       </c>
       <c r="K113" t="b">
@@ -5699,7 +5711,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J114" s="1" t="n">
+      <c r="J114" s="2" t="n">
         <v>46457</v>
       </c>
       <c r="K114" t="b">
@@ -5748,7 +5760,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="J115" s="2" t="n">
         <v>46462</v>
       </c>
       <c r="K115" t="b">
@@ -5797,7 +5809,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J116" s="1" t="n">
+      <c r="J116" s="2" t="n">
         <v>46464</v>
       </c>
       <c r="K116" t="b">
@@ -5846,7 +5858,7 @@
           <t>8m</t>
         </is>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="J117" s="2" t="n">
         <v>46470</v>
       </c>
       <c r="K117" t="b">
@@ -5895,7 +5907,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J118" s="1" t="n">
+      <c r="J118" s="2" t="n">
         <v>46485</v>
       </c>
       <c r="K118" t="b">
@@ -5944,7 +5956,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="J119" s="2" t="n">
         <v>46499</v>
       </c>
       <c r="K119" t="b">
@@ -5993,7 +6005,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="J120" s="2" t="n">
         <v>46504</v>
       </c>
       <c r="K120" t="b">
@@ -6042,7 +6054,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="J121" s="2" t="n">
         <v>46504</v>
       </c>
       <c r="K121" t="b">
@@ -6091,7 +6103,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J122" s="1" t="n">
+      <c r="J122" s="2" t="n">
         <v>46507</v>
       </c>
       <c r="K122" t="b">
@@ -6140,7 +6152,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J123" s="1" t="n">
+      <c r="J123" s="2" t="n">
         <v>46508</v>
       </c>
       <c r="K123" t="b">
@@ -6189,7 +6201,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J124" s="1" t="n">
+      <c r="J124" s="2" t="n">
         <v>46512</v>
       </c>
       <c r="K124" t="b">
@@ -6238,7 +6250,7 @@
           <t>9m</t>
         </is>
       </c>
-      <c r="J125" s="1" t="n">
+      <c r="J125" s="2" t="n">
         <v>46512</v>
       </c>
       <c r="K125" t="b">
@@ -6287,7 +6299,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J126" s="1" t="n">
+      <c r="J126" s="2" t="n">
         <v>46528</v>
       </c>
       <c r="K126" t="b">
@@ -6336,7 +6348,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J127" s="1" t="n">
+      <c r="J127" s="2" t="n">
         <v>46529</v>
       </c>
       <c r="K127" t="b">
@@ -6385,7 +6397,7 @@
           <t>10m</t>
         </is>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="J128" s="2" t="n">
         <v>46537</v>
       </c>
       <c r="K128" t="b">
@@ -6434,7 +6446,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J129" s="1" t="n">
+      <c r="J129" s="2" t="n">
         <v>46546</v>
       </c>
       <c r="K129" t="b">
@@ -6483,7 +6495,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="J130" s="2" t="n">
         <v>46547</v>
       </c>
       <c r="K130" t="b">
@@ -6532,7 +6544,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="J131" s="2" t="n">
         <v>46547</v>
       </c>
       <c r="K131" t="b">
@@ -6581,7 +6593,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J132" s="1" t="n">
+      <c r="J132" s="2" t="n">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -6630,7 +6642,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J133" s="1" t="n">
+      <c r="J133" s="2" t="n">
         <v>46551</v>
       </c>
       <c r="K133" t="b">
@@ -6679,7 +6691,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J134" s="1" t="n">
+      <c r="J134" s="2" t="n">
         <v>46560</v>
       </c>
       <c r="K134" t="b">
@@ -6728,7 +6740,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J135" s="1" t="n">
+      <c r="J135" s="2" t="n">
         <v>46564</v>
       </c>
       <c r="K135" t="b">
@@ -6777,7 +6789,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J136" s="1" t="n">
+      <c r="J136" s="2" t="n">
         <v>46567</v>
       </c>
       <c r="K136" t="b">
@@ -6826,7 +6838,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J137" s="1" t="n">
+      <c r="J137" s="2" t="n">
         <v>46568</v>
       </c>
       <c r="K137" t="b">
@@ -6875,7 +6887,7 @@
           <t>11m</t>
         </is>
       </c>
-      <c r="J138" s="1" t="n">
+      <c r="J138" s="2" t="n">
         <v>46571</v>
       </c>
       <c r="K138" t="b">
@@ -6924,7 +6936,7 @@
           <t>-14d</t>
         </is>
       </c>
-      <c r="J139" s="1" t="n">
+      <c r="J139" s="2" t="n">
         <v>46197</v>
       </c>
       <c r="K139" t="b">
@@ -6973,7 +6985,7 @@
           <t>1d</t>
         </is>
       </c>
-      <c r="J140" s="1" t="n">
+      <c r="J140" s="2" t="n">
         <v>46212</v>
       </c>
       <c r="K140" t="b">
@@ -7022,7 +7034,7 @@
           <t>14d</t>
         </is>
       </c>
-      <c r="J141" s="1" t="n">
+      <c r="J141" s="2" t="n">
         <v>46225</v>
       </c>
       <c r="K141" t="b">
@@ -7071,7 +7083,7 @@
           <t>23d</t>
         </is>
       </c>
-      <c r="J142" s="1" t="n">
+      <c r="J142" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K142" t="b">
@@ -7120,7 +7132,7 @@
           <t>24d</t>
         </is>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="J143" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K143" t="b">
@@ -7169,7 +7181,7 @@
           <t>1me23d</t>
         </is>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="J144" s="2" t="n">
         <v>46263</v>
       </c>
       <c r="K144" t="b">
@@ -7218,7 +7230,7 @@
           <t>1me25d</t>
         </is>
       </c>
-      <c r="J145" s="1" t="n">
+      <c r="J145" s="2" t="n">
         <v>46266</v>
       </c>
       <c r="K145" t="b">
@@ -7263,7 +7275,7 @@
         <v>-1476</v>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" s="1" t="n">
+      <c r="J146" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -7308,7 +7320,7 @@
         <v>-1469</v>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" s="1" t="n">
+      <c r="J147" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -7353,7 +7365,7 @@
         <v>-1121</v>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" s="1" t="n">
+      <c r="J148" s="2" t="n">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -7398,7 +7410,7 @@
         <v>-1018</v>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" s="1" t="n">
+      <c r="J149" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -7443,7 +7455,7 @@
         <v>-950</v>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" s="1" t="n">
+      <c r="J150" s="2" t="n">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -7488,7 +7500,7 @@
         <v>-943</v>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" s="1" t="n">
+      <c r="J151" s="2" t="n">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -7533,7 +7545,7 @@
         <v>-252</v>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" s="1" t="n">
+      <c r="J152" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -7578,7 +7590,7 @@
         <v>-196</v>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" s="1" t="n">
+      <c r="J153" s="2" t="n">
         <v>45988</v>
       </c>
       <c r="K153" t="b">
@@ -7623,7 +7635,7 @@
         <v>-196</v>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" s="1" t="n">
+      <c r="J154" s="2" t="n">
         <v>45988</v>
       </c>
       <c r="K154" t="b">
@@ -7668,7 +7680,7 @@
         <v>-47</v>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" s="1" t="n">
+      <c r="J155" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="K155" t="b">
@@ -7713,7 +7725,7 @@
         <v>-47</v>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" s="1" t="n">
+      <c r="J156" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="K156" t="b">
@@ -7758,7 +7770,7 @@
         <v>-33</v>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" s="1" t="n">
+      <c r="J157" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="K157" t="b">
@@ -7803,7 +7815,7 @@
         <v>-33</v>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" s="1" t="n">
+      <c r="J158" s="2" t="n">
         <v>46199</v>
       </c>
       <c r="K158" t="b">
@@ -7848,7 +7860,7 @@
         <v>-6</v>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" s="1" t="n">
+      <c r="J159" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="K159" t="b">
@@ -7893,7 +7905,7 @@
         <v>43</v>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" s="1" t="n">
+      <c r="J160" s="2" t="n">
         <v>46440</v>
       </c>
       <c r="K160" t="b">
@@ -7938,7 +7950,7 @@
         <v>43</v>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" s="1" t="n">
+      <c r="J161" s="2" t="n">
         <v>46440</v>
       </c>
       <c r="K161" t="b">
@@ -7983,7 +7995,7 @@
         <v>73</v>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" s="1" t="n">
+      <c r="J162" s="2" t="n">
         <v>46264</v>
       </c>
       <c r="K162" t="b">
@@ -8028,7 +8040,7 @@
         <v>73</v>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" s="1" t="n">
+      <c r="J163" s="2" t="n">
         <v>46264</v>
       </c>
       <c r="K163" t="b">
@@ -8073,7 +8085,7 @@
         <v>102</v>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" s="1" t="n">
+      <c r="J164" s="2" t="n">
         <v>46463</v>
       </c>
       <c r="K164" t="b">
@@ -8118,7 +8130,7 @@
         <v>118</v>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" s="1" t="n">
+      <c r="J165" s="2" t="n">
         <v>46337</v>
       </c>
       <c r="K165" t="b">
@@ -8163,7 +8175,7 @@
         <v>146</v>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" s="1" t="n">
+      <c r="J166" s="2" t="n">
         <v>46451</v>
       </c>
       <c r="K166" t="b">
@@ -8208,7 +8220,7 @@
         <v>152</v>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" s="1" t="n">
+      <c r="J167" s="2" t="n">
         <v>46245</v>
       </c>
       <c r="K167" t="b">
@@ -8253,7 +8265,7 @@
         <v>152</v>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" s="1" t="n">
+      <c r="J168" s="2" t="n">
         <v>46245</v>
       </c>
       <c r="K168" t="b">
@@ -8298,7 +8310,7 @@
         <v>163</v>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" s="1" t="n">
+      <c r="J169" s="2" t="n">
         <v>46324</v>
       </c>
       <c r="K169" t="b">
@@ -8343,7 +8355,7 @@
         <v>163</v>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" s="1" t="n">
+      <c r="J170" s="2" t="n">
         <v>46324</v>
       </c>
       <c r="K170" t="b">
@@ -8388,7 +8400,7 @@
         <v>164</v>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" s="1" t="n">
+      <c r="J171" s="2" t="n">
         <v>46426</v>
       </c>
       <c r="K171" t="b">
@@ -8433,7 +8445,7 @@
         <v>175</v>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" s="1" t="n">
+      <c r="J172" s="2" t="n">
         <v>46383</v>
       </c>
       <c r="K172" t="b">
@@ -8478,7 +8490,7 @@
         <v>186</v>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" s="1" t="n">
+      <c r="J173" s="2" t="n">
         <v>46392</v>
       </c>
       <c r="K173" t="b">
@@ -8523,7 +8535,7 @@
         <v>205</v>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" s="1" t="n">
+      <c r="J174" s="2" t="n">
         <v>46390</v>
       </c>
       <c r="K174" t="b">
@@ -8568,7 +8580,7 @@
         <v>207</v>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" s="1" t="n">
+      <c r="J175" s="2" t="n">
         <v>46392</v>
       </c>
       <c r="K175" t="b">
@@ -8613,7 +8625,7 @@
         <v>218</v>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" s="1" t="n">
+      <c r="J176" s="2" t="n">
         <v>46506</v>
       </c>
       <c r="K176" t="b">
@@ -8658,7 +8670,7 @@
         <v>246</v>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" s="1" t="n">
+      <c r="J177" s="2" t="n">
         <v>46478</v>
       </c>
       <c r="K177" t="b">
@@ -8703,7 +8715,7 @@
         <v>248</v>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" s="1" t="n">
+      <c r="J178" s="2" t="n">
         <v>46500</v>
       </c>
       <c r="K178" t="b">
@@ -8748,7 +8760,7 @@
         <v>276</v>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" s="1" t="n">
+      <c r="J179" s="2" t="n">
         <v>46430</v>
       </c>
       <c r="K179" t="b">
@@ -8793,7 +8805,7 @@
         <v>276</v>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" s="1" t="n">
+      <c r="J180" s="2" t="n">
         <v>46430</v>
       </c>
       <c r="K180" t="b">
@@ -8838,7 +8850,7 @@
         <v>290</v>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" s="1" t="n">
+      <c r="J181" s="2" t="n">
         <v>46467</v>
       </c>
       <c r="K181" t="b">
@@ -8883,7 +8895,7 @@
         <v>317</v>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" s="1" t="n">
+      <c r="J182" s="2" t="n">
         <v>46529</v>
       </c>
       <c r="K182" t="b">
@@ -8928,7 +8940,7 @@
         <v>420</v>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" s="1" t="n">
+      <c r="J183" s="2" t="n">
         <v>46566</v>
       </c>
       <c r="K183" t="b">
@@ -8973,7 +8985,7 @@
         <v>426</v>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" s="1" t="n">
+      <c r="J184" s="2" t="n">
         <v>46571</v>
       </c>
       <c r="K184" t="b">
@@ -9018,7 +9030,7 @@
         <v>721</v>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" s="1" t="n">
+      <c r="J185" s="2" t="n">
         <v>46325</v>
       </c>
       <c r="K185" t="b">
@@ -9063,7 +9075,7 @@
         <v>721</v>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" s="1" t="n">
+      <c r="J186" s="2" t="n">
         <v>46325</v>
       </c>
       <c r="K186" t="b">
@@ -9108,7 +9120,7 @@
         <v>850</v>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" s="1" t="n">
+      <c r="J187" s="2" t="n">
         <v>46345</v>
       </c>
       <c r="K187" t="b">
@@ -9153,7 +9165,7 @@
         <v>850</v>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" s="1" t="n">
+      <c r="J188" s="2" t="n">
         <v>46345</v>
       </c>
       <c r="K188" t="b">
@@ -9198,7 +9210,7 @@
         <v>1661</v>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" s="1" t="n">
+      <c r="J189" s="2" t="n">
         <v>46498</v>
       </c>
       <c r="K189" t="b">
@@ -9243,7 +9255,7 @@
         <v>1661</v>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" s="1" t="n">
+      <c r="J190" s="2" t="n">
         <v>46498</v>
       </c>
       <c r="K190" t="b">
@@ -9288,7 +9300,7 @@
         <v>488</v>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" s="1" t="n">
+      <c r="J191" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -9333,7 +9345,7 @@
         <v>25565</v>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" s="1" t="n">
+      <c r="J192" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -9378,7 +9390,7 @@
         <v>25567</v>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" s="1" t="n">
+      <c r="J193" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -9423,7 +9435,7 @@
         <v>31293</v>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" s="1" t="n">
+      <c r="J194" s="2" t="n">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1040,8 +1040,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1057,7 +1065,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1065,12 +1073,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,37 +1396,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1429,7 +1455,7 @@
       <c r="H2">
         <v>-4402.8</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>41388</v>
       </c>
       <c r="K2" t="b">
@@ -1461,7 +1487,7 @@
       <c r="H3">
         <v>-4254.8</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>39285</v>
       </c>
       <c r="K3" t="b">
@@ -1493,7 +1519,7 @@
       <c r="H4">
         <v>-2354.2</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1525,7 +1551,7 @@
       <c r="H5">
         <v>-896.8</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>40669</v>
       </c>
       <c r="K5" t="b">
@@ -1557,7 +1583,7 @@
       <c r="H6">
         <v>-854.1</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>44884</v>
       </c>
       <c r="K6" t="b">
@@ -1589,7 +1615,7 @@
       <c r="H7">
         <v>-413.2</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>43855</v>
       </c>
       <c r="K7" t="b">
@@ -1621,7 +1647,7 @@
       <c r="H8">
         <v>-391.8</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>42769</v>
       </c>
       <c r="K8" t="b">
@@ -1653,7 +1679,7 @@
       <c r="H9">
         <v>-371.5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1685,7 +1711,7 @@
       <c r="H10">
         <v>-368.8</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>46014</v>
       </c>
       <c r="K10" t="b">
@@ -1717,7 +1743,7 @@
       <c r="H11">
         <v>-359</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -1749,7 +1775,7 @@
       <c r="H12">
         <v>-359</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>45804</v>
       </c>
       <c r="K12" t="b">
@@ -1781,7 +1807,7 @@
       <c r="H13">
         <v>-351</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>42821</v>
       </c>
       <c r="K13" t="b">
@@ -1813,7 +1839,7 @@
       <c r="H14">
         <v>-351</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1845,7 +1871,7 @@
       <c r="H15">
         <v>-351</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1877,7 +1903,7 @@
       <c r="H16">
         <v>-351</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>46014</v>
       </c>
       <c r="K16" t="b">
@@ -1909,7 +1935,7 @@
       <c r="H17">
         <v>-345.8</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1941,7 +1967,7 @@
       <c r="H18">
         <v>-345.8</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>46017</v>
       </c>
       <c r="K18" t="b">
@@ -1973,7 +1999,7 @@
       <c r="H19">
         <v>-264.2</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="2">
         <v>40979</v>
       </c>
       <c r="K19" t="b">
@@ -2005,7 +2031,7 @@
       <c r="H20">
         <v>-206.4</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="2">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -2037,7 +2063,7 @@
       <c r="H21">
         <v>-131.6</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -2069,7 +2095,7 @@
       <c r="H22">
         <v>-131.6</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="2">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -2101,7 +2127,7 @@
       <c r="H23">
         <v>-131.6</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="2">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -2133,7 +2159,7 @@
       <c r="H24">
         <v>-131.6</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="2">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -2165,7 +2191,7 @@
       <c r="H25">
         <v>-131.6</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="2">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -2197,7 +2223,7 @@
       <c r="H26">
         <v>-105</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="2">
         <v>46161</v>
       </c>
       <c r="K26" t="b">
@@ -2229,7 +2255,7 @@
       <c r="H27">
         <v>-79.8</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="2">
         <v>43340</v>
       </c>
       <c r="K27" t="b">
@@ -2261,7 +2287,7 @@
       <c r="H28">
         <v>-12.3</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="2">
         <v>46048</v>
       </c>
       <c r="K28" t="b">
@@ -2293,7 +2319,7 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>46211</v>
       </c>
       <c r="K29" t="b">
@@ -2325,7 +2351,7 @@
       <c r="H30">
         <v>3.6</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="2">
         <v>46234</v>
       </c>
       <c r="K30" t="b">
@@ -2357,7 +2383,7 @@
       <c r="H31">
         <v>6.2</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>46234</v>
       </c>
       <c r="K31" t="b">
@@ -2389,7 +2415,7 @@
       <c r="H32">
         <v>7.5</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="2">
         <v>46234</v>
       </c>
       <c r="K32" t="b">
@@ -2421,7 +2447,7 @@
       <c r="H33">
         <v>10.7</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="2">
         <v>46234</v>
       </c>
       <c r="K33" t="b">
@@ -2453,7 +2479,7 @@
       <c r="H34">
         <v>20</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>46234</v>
       </c>
       <c r="K34" t="b">
@@ -2485,7 +2511,7 @@
       <c r="H35">
         <v>30.8</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>46234</v>
       </c>
       <c r="K35" t="b">
@@ -2517,7 +2543,7 @@
       <c r="H36">
         <v>37.1</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="2">
         <v>46256</v>
       </c>
       <c r="K36" t="b">
@@ -2549,7 +2575,7 @@
       <c r="H37">
         <v>42.8</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="2">
         <v>46276</v>
       </c>
       <c r="K37" t="b">
@@ -2581,7 +2607,7 @@
       <c r="H38">
         <v>45.2</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="2">
         <v>46234</v>
       </c>
       <c r="K38" t="b">
@@ -2613,7 +2639,7 @@
       <c r="H39">
         <v>46</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>46251</v>
       </c>
       <c r="K39" t="b">
@@ -2645,7 +2671,7 @@
       <c r="H40">
         <v>47.5</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="2">
         <v>46456</v>
       </c>
       <c r="K40" t="b">
@@ -2677,7 +2703,7 @@
       <c r="H41">
         <v>57.2</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="2">
         <v>46246</v>
       </c>
       <c r="K41" t="b">
@@ -2709,7 +2735,7 @@
       <c r="H42">
         <v>59.6</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="2">
         <v>46487</v>
       </c>
       <c r="K42" t="b">
@@ -2741,7 +2767,7 @@
       <c r="H43">
         <v>75.40000000000001</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="2">
         <v>46283</v>
       </c>
       <c r="K43" t="b">
@@ -2773,7 +2799,7 @@
       <c r="H44">
         <v>76.8</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="2">
         <v>46285</v>
       </c>
       <c r="K44" t="b">
@@ -2805,7 +2831,7 @@
       <c r="H45">
         <v>83.2</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="2">
         <v>46547</v>
       </c>
       <c r="K45" t="b">
@@ -2837,7 +2863,7 @@
       <c r="H46">
         <v>84.5</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="2">
         <v>46240</v>
       </c>
       <c r="K46" t="b">
@@ -2869,7 +2895,7 @@
       <c r="H47">
         <v>85.8</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="2">
         <v>46266</v>
       </c>
       <c r="K47" t="b">
@@ -2901,7 +2927,7 @@
       <c r="H48">
         <v>86.5</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
         <v>46241</v>
       </c>
       <c r="K48" t="b">
@@ -2933,7 +2959,7 @@
       <c r="H49">
         <v>91.7</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
         <v>46243</v>
       </c>
       <c r="K49" t="b">
@@ -2965,7 +2991,7 @@
       <c r="H50">
         <v>91.7</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="2">
         <v>46243</v>
       </c>
       <c r="K50" t="b">
@@ -2997,7 +3023,7 @@
       <c r="H51">
         <v>91.7</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="2">
         <v>46250</v>
       </c>
       <c r="K51" t="b">
@@ -3029,7 +3055,7 @@
       <c r="H52">
         <v>98.90000000000001</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="2">
         <v>46253</v>
       </c>
       <c r="K52" t="b">
@@ -3061,7 +3087,7 @@
       <c r="H53">
         <v>105.5</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="2">
         <v>46280</v>
       </c>
       <c r="K53" t="b">
@@ -3093,7 +3119,7 @@
       <c r="H54">
         <v>105.6</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="2">
         <v>46361</v>
       </c>
       <c r="K54" t="b">
@@ -3125,7 +3151,7 @@
       <c r="H55">
         <v>105.7</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="2">
         <v>46362</v>
       </c>
       <c r="K55" t="b">
@@ -3157,7 +3183,7 @@
       <c r="H56">
         <v>110.7</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="2">
         <v>46275</v>
       </c>
       <c r="K56" t="b">
@@ -3189,7 +3215,7 @@
       <c r="H57">
         <v>113.2</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="2">
         <v>46377</v>
       </c>
       <c r="K57" t="b">
@@ -3221,7 +3247,7 @@
       <c r="H58">
         <v>128.8</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="2">
         <v>46434</v>
       </c>
       <c r="K58" t="b">
@@ -3253,7 +3279,7 @@
       <c r="H59">
         <v>128.8</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="2">
         <v>46434</v>
       </c>
       <c r="K59" t="b">
@@ -3285,7 +3311,7 @@
       <c r="H60">
         <v>128.8</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="2">
         <v>46434</v>
       </c>
       <c r="K60" t="b">
@@ -3317,7 +3343,7 @@
       <c r="H61">
         <v>128.8</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="2">
         <v>46434</v>
       </c>
       <c r="K61" t="b">
@@ -3349,7 +3375,7 @@
       <c r="H62">
         <v>128.8</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="2">
         <v>46434</v>
       </c>
       <c r="K62" t="b">
@@ -3381,7 +3407,7 @@
       <c r="H63">
         <v>135</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="2">
         <v>46280</v>
       </c>
       <c r="K63" t="b">
@@ -3413,7 +3439,7 @@
       <c r="H64">
         <v>150.6</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="2">
         <v>46271</v>
       </c>
       <c r="K64" t="b">
@@ -3445,7 +3471,7 @@
       <c r="H65">
         <v>174.2</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="2">
         <v>46363</v>
       </c>
       <c r="K65" t="b">
@@ -3477,7 +3503,7 @@
       <c r="H66">
         <v>176.6</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="2">
         <v>46334</v>
       </c>
       <c r="K66" t="b">
@@ -3509,7 +3535,7 @@
       <c r="H67">
         <v>177.4</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="2">
         <v>46407</v>
       </c>
       <c r="K67" t="b">
@@ -3541,7 +3567,7 @@
       <c r="H68">
         <v>183.9</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="2">
         <v>46341</v>
       </c>
       <c r="K68" t="b">
@@ -3573,7 +3599,7 @@
       <c r="H69">
         <v>191.7</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="2">
         <v>46300</v>
       </c>
       <c r="K69" t="b">
@@ -3605,7 +3631,7 @@
       <c r="H70">
         <v>200</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="2">
         <v>46336</v>
       </c>
       <c r="K70" t="b">
@@ -3637,7 +3663,7 @@
       <c r="H71">
         <v>201.1</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="2">
         <v>46319</v>
       </c>
       <c r="K71" t="b">
@@ -3669,7 +3695,7 @@
       <c r="H72">
         <v>206.5</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="2">
         <v>46308</v>
       </c>
       <c r="K72" t="b">
@@ -3701,7 +3727,7 @@
       <c r="H73">
         <v>207.5</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73" s="2">
         <v>46390</v>
       </c>
       <c r="K73" t="b">
@@ -3733,7 +3759,7 @@
       <c r="H74">
         <v>247</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="2">
         <v>46443</v>
       </c>
       <c r="K74" t="b">
@@ -3765,7 +3791,7 @@
       <c r="H75">
         <v>285.3</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75" s="2">
         <v>46304</v>
       </c>
       <c r="K75" t="b">
@@ -3797,7 +3823,7 @@
       <c r="H76">
         <v>290.8</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="2">
         <v>46362</v>
       </c>
       <c r="K76" t="b">
@@ -3829,7 +3855,7 @@
       <c r="H77">
         <v>295.2</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="2">
         <v>46463</v>
       </c>
       <c r="K77" t="b">
@@ -3861,7 +3887,7 @@
       <c r="H78">
         <v>300.2</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="2">
         <v>46466</v>
       </c>
       <c r="K78" t="b">
@@ -3896,7 +3922,7 @@
       <c r="I79" t="s">
         <v>313</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79" s="2">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -3931,7 +3957,7 @@
       <c r="I80" t="s">
         <v>314</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80" s="2">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -3966,7 +3992,7 @@
       <c r="I81" t="s">
         <v>315</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81" s="2">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -4001,7 +4027,7 @@
       <c r="I82" t="s">
         <v>316</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82" s="2">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4036,7 +4062,7 @@
       <c r="I83" t="s">
         <v>316</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="2">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4071,7 +4097,7 @@
       <c r="I84" t="s">
         <v>317</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="2">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4106,7 +4132,7 @@
       <c r="I85" t="s">
         <v>318</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="2">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4141,7 +4167,7 @@
       <c r="I86" t="s">
         <v>319</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="2">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4176,7 +4202,7 @@
       <c r="I87" t="s">
         <v>320</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="2">
         <v>46106</v>
       </c>
       <c r="K87" t="b">
@@ -4211,7 +4237,7 @@
       <c r="I88" t="s">
         <v>321</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="2">
         <v>46142</v>
       </c>
       <c r="K88" t="b">
@@ -4246,7 +4272,7 @@
       <c r="I89" t="s">
         <v>322</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89" s="2">
         <v>46274</v>
       </c>
       <c r="K89" t="b">
@@ -4281,7 +4307,7 @@
       <c r="I90" t="s">
         <v>322</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90" s="2">
         <v>46276</v>
       </c>
       <c r="K90" t="b">
@@ -4316,7 +4342,7 @@
       <c r="I91" t="s">
         <v>322</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91" s="2">
         <v>46284</v>
       </c>
       <c r="K91" t="b">
@@ -4351,7 +4377,7 @@
       <c r="I92" t="s">
         <v>323</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="2">
         <v>46317</v>
       </c>
       <c r="K92" t="b">
@@ -4386,7 +4412,7 @@
       <c r="I93" t="s">
         <v>323</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="2">
         <v>46319</v>
       </c>
       <c r="K93" t="b">
@@ -4421,7 +4447,7 @@
       <c r="I94" t="s">
         <v>324</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="2">
         <v>46333</v>
       </c>
       <c r="K94" t="b">
@@ -4456,7 +4482,7 @@
       <c r="I95" t="s">
         <v>324</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95" s="2">
         <v>46338</v>
       </c>
       <c r="K95" t="b">
@@ -4491,7 +4517,7 @@
       <c r="I96" t="s">
         <v>324</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96" s="2">
         <v>46338</v>
       </c>
       <c r="K96" t="b">
@@ -4526,7 +4552,7 @@
       <c r="I97" t="s">
         <v>324</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97" s="2">
         <v>46341</v>
       </c>
       <c r="K97" t="b">
@@ -4561,7 +4587,7 @@
       <c r="I98" t="s">
         <v>324</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98" s="2">
         <v>46344</v>
       </c>
       <c r="K98" t="b">
@@ -4596,7 +4622,7 @@
       <c r="I99" t="s">
         <v>324</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99" s="2">
         <v>46354</v>
       </c>
       <c r="K99" t="b">
@@ -4631,7 +4657,7 @@
       <c r="I100" t="s">
         <v>324</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J100" s="2">
         <v>46360</v>
       </c>
       <c r="K100" t="b">
@@ -4666,7 +4692,7 @@
       <c r="I101" t="s">
         <v>324</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J101" s="2">
         <v>46360</v>
       </c>
       <c r="K101" t="b">
@@ -4701,7 +4727,7 @@
       <c r="I102" t="s">
         <v>325</v>
       </c>
-      <c r="J102" s="1">
+      <c r="J102" s="2">
         <v>46366</v>
       </c>
       <c r="K102" t="b">
@@ -4736,7 +4762,7 @@
       <c r="I103" t="s">
         <v>325</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J103" s="2">
         <v>46375</v>
       </c>
       <c r="K103" t="b">
@@ -4771,7 +4797,7 @@
       <c r="I104" t="s">
         <v>325</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J104" s="2">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -4806,7 +4832,7 @@
       <c r="I105" t="s">
         <v>326</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J105" s="2">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -4841,7 +4867,7 @@
       <c r="I106" t="s">
         <v>326</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J106" s="2">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -4876,7 +4902,7 @@
       <c r="I107" t="s">
         <v>326</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J107" s="2">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -4911,7 +4937,7 @@
       <c r="I108" t="s">
         <v>326</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J108" s="2">
         <v>46413</v>
       </c>
       <c r="K108" t="b">
@@ -4946,7 +4972,7 @@
       <c r="I109" t="s">
         <v>327</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J109" s="2">
         <v>46424</v>
       </c>
       <c r="K109" t="b">
@@ -4981,7 +5007,7 @@
       <c r="I110" t="s">
         <v>327</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J110" s="2">
         <v>46427</v>
       </c>
       <c r="K110" t="b">
@@ -5016,7 +5042,7 @@
       <c r="I111" t="s">
         <v>327</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J111" s="2">
         <v>46437</v>
       </c>
       <c r="K111" t="b">
@@ -5051,7 +5077,7 @@
       <c r="I112" t="s">
         <v>327</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J112" s="2">
         <v>46451</v>
       </c>
       <c r="K112" t="b">
@@ -5086,7 +5112,7 @@
       <c r="I113" t="s">
         <v>328</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J113" s="2">
         <v>46455</v>
       </c>
       <c r="K113" t="b">
@@ -5121,7 +5147,7 @@
       <c r="I114" t="s">
         <v>328</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J114" s="2">
         <v>46457</v>
       </c>
       <c r="K114" t="b">
@@ -5156,7 +5182,7 @@
       <c r="I115" t="s">
         <v>328</v>
       </c>
-      <c r="J115" s="1">
+      <c r="J115" s="2">
         <v>46462</v>
       </c>
       <c r="K115" t="b">
@@ -5191,7 +5217,7 @@
       <c r="I116" t="s">
         <v>328</v>
       </c>
-      <c r="J116" s="1">
+      <c r="J116" s="2">
         <v>46464</v>
       </c>
       <c r="K116" t="b">
@@ -5226,7 +5252,7 @@
       <c r="I117" t="s">
         <v>328</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J117" s="2">
         <v>46470</v>
       </c>
       <c r="K117" t="b">
@@ -5261,7 +5287,7 @@
       <c r="I118" t="s">
         <v>329</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J118" s="2">
         <v>46485</v>
       </c>
       <c r="K118" t="b">
@@ -5296,7 +5322,7 @@
       <c r="I119" t="s">
         <v>329</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J119" s="2">
         <v>46499</v>
       </c>
       <c r="K119" t="b">
@@ -5331,7 +5357,7 @@
       <c r="I120" t="s">
         <v>329</v>
       </c>
-      <c r="J120" s="1">
+      <c r="J120" s="2">
         <v>46504</v>
       </c>
       <c r="K120" t="b">
@@ -5366,7 +5392,7 @@
       <c r="I121" t="s">
         <v>329</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="2">
         <v>46504</v>
       </c>
       <c r="K121" t="b">
@@ -5401,7 +5427,7 @@
       <c r="I122" t="s">
         <v>329</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J122" s="2">
         <v>46507</v>
       </c>
       <c r="K122" t="b">
@@ -5436,7 +5462,7 @@
       <c r="I123" t="s">
         <v>329</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J123" s="2">
         <v>46508</v>
       </c>
       <c r="K123" t="b">
@@ -5471,7 +5497,7 @@
       <c r="I124" t="s">
         <v>329</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J124" s="2">
         <v>46512</v>
       </c>
       <c r="K124" t="b">
@@ -5506,7 +5532,7 @@
       <c r="I125" t="s">
         <v>329</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J125" s="2">
         <v>46512</v>
       </c>
       <c r="K125" t="b">
@@ -5541,7 +5567,7 @@
       <c r="I126" t="s">
         <v>330</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J126" s="2">
         <v>46528</v>
       </c>
       <c r="K126" t="b">
@@ -5576,7 +5602,7 @@
       <c r="I127" t="s">
         <v>330</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J127" s="2">
         <v>46529</v>
       </c>
       <c r="K127" t="b">
@@ -5611,7 +5637,7 @@
       <c r="I128" t="s">
         <v>330</v>
       </c>
-      <c r="J128" s="1">
+      <c r="J128" s="2">
         <v>46537</v>
       </c>
       <c r="K128" t="b">
@@ -5646,7 +5672,7 @@
       <c r="I129" t="s">
         <v>331</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J129" s="2">
         <v>46546</v>
       </c>
       <c r="K129" t="b">
@@ -5681,7 +5707,7 @@
       <c r="I130" t="s">
         <v>331</v>
       </c>
-      <c r="J130" s="1">
+      <c r="J130" s="2">
         <v>46547</v>
       </c>
       <c r="K130" t="b">
@@ -5716,7 +5742,7 @@
       <c r="I131" t="s">
         <v>331</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J131" s="2">
         <v>46547</v>
       </c>
       <c r="K131" t="b">
@@ -5751,7 +5777,7 @@
       <c r="I132" t="s">
         <v>331</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J132" s="2">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -5786,7 +5812,7 @@
       <c r="I133" t="s">
         <v>331</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J133" s="2">
         <v>46551</v>
       </c>
       <c r="K133" t="b">
@@ -5821,7 +5847,7 @@
       <c r="I134" t="s">
         <v>331</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J134" s="2">
         <v>46560</v>
       </c>
       <c r="K134" t="b">
@@ -5856,7 +5882,7 @@
       <c r="I135" t="s">
         <v>331</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J135" s="2">
         <v>46564</v>
       </c>
       <c r="K135" t="b">
@@ -5891,7 +5917,7 @@
       <c r="I136" t="s">
         <v>331</v>
       </c>
-      <c r="J136" s="1">
+      <c r="J136" s="2">
         <v>46567</v>
       </c>
       <c r="K136" t="b">
@@ -5926,7 +5952,7 @@
       <c r="I137" t="s">
         <v>331</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J137" s="2">
         <v>46568</v>
       </c>
       <c r="K137" t="b">
@@ -5961,7 +5987,7 @@
       <c r="I138" t="s">
         <v>331</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J138" s="2">
         <v>46571</v>
       </c>
       <c r="K138" t="b">
@@ -5996,7 +6022,7 @@
       <c r="I139" t="s">
         <v>332</v>
       </c>
-      <c r="J139" s="1">
+      <c r="J139" s="2">
         <v>46197</v>
       </c>
       <c r="K139" t="b">
@@ -6031,7 +6057,7 @@
       <c r="I140" t="s">
         <v>333</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J140" s="2">
         <v>46212</v>
       </c>
       <c r="K140" t="b">
@@ -6066,7 +6092,7 @@
       <c r="I141" t="s">
         <v>334</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J141" s="2">
         <v>46225</v>
       </c>
       <c r="K141" t="b">
@@ -6101,7 +6127,7 @@
       <c r="I142" t="s">
         <v>335</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J142" s="2">
         <v>46234</v>
       </c>
       <c r="K142" t="b">
@@ -6136,7 +6162,7 @@
       <c r="I143" t="s">
         <v>336</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J143" s="2">
         <v>46234</v>
       </c>
       <c r="K143" t="b">
@@ -6171,7 +6197,7 @@
       <c r="I144" t="s">
         <v>337</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J144" s="2">
         <v>46263</v>
       </c>
       <c r="K144" t="b">
@@ -6206,7 +6232,7 @@
       <c r="I145" t="s">
         <v>338</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J145" s="2">
         <v>46266</v>
       </c>
       <c r="K145" t="b">
@@ -6238,7 +6264,7 @@
       <c r="H146">
         <v>-1476</v>
       </c>
-      <c r="J146" s="1">
+      <c r="J146" s="2">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -6270,7 +6296,7 @@
       <c r="H147">
         <v>-1469</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J147" s="2">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -6302,7 +6328,7 @@
       <c r="H148">
         <v>-1121</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J148" s="2">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -6334,7 +6360,7 @@
       <c r="H149">
         <v>-1018</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="2">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -6366,7 +6392,7 @@
       <c r="H150">
         <v>-950</v>
       </c>
-      <c r="J150" s="1">
+      <c r="J150" s="2">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -6398,7 +6424,7 @@
       <c r="H151">
         <v>-943</v>
       </c>
-      <c r="J151" s="1">
+      <c r="J151" s="2">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -6430,7 +6456,7 @@
       <c r="H152">
         <v>-252</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J152" s="2">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -6462,7 +6488,7 @@
       <c r="H153">
         <v>-196</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J153" s="2">
         <v>45988</v>
       </c>
       <c r="K153" t="b">
@@ -6494,7 +6520,7 @@
       <c r="H154">
         <v>-196</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J154" s="2">
         <v>45988</v>
       </c>
       <c r="K154" t="b">
@@ -6526,7 +6552,7 @@
       <c r="H155">
         <v>-47</v>
       </c>
-      <c r="J155" s="1">
+      <c r="J155" s="2">
         <v>46176</v>
       </c>
       <c r="K155" t="b">
@@ -6558,7 +6584,7 @@
       <c r="H156">
         <v>-47</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J156" s="2">
         <v>46176</v>
       </c>
       <c r="K156" t="b">
@@ -6590,7 +6616,7 @@
       <c r="H157">
         <v>-33</v>
       </c>
-      <c r="J157" s="1">
+      <c r="J157" s="2">
         <v>46199</v>
       </c>
       <c r="K157" t="b">
@@ -6622,7 +6648,7 @@
       <c r="H158">
         <v>-33</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J158" s="2">
         <v>46199</v>
       </c>
       <c r="K158" t="b">
@@ -6654,7 +6680,7 @@
       <c r="H159">
         <v>-6</v>
       </c>
-      <c r="J159" s="1">
+      <c r="J159" s="2">
         <v>45967</v>
       </c>
       <c r="K159" t="b">
@@ -6686,7 +6712,7 @@
       <c r="H160">
         <v>43</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J160" s="2">
         <v>46440</v>
       </c>
       <c r="K160" t="b">
@@ -6718,7 +6744,7 @@
       <c r="H161">
         <v>43</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J161" s="2">
         <v>46440</v>
       </c>
       <c r="K161" t="b">
@@ -6750,7 +6776,7 @@
       <c r="H162">
         <v>73</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J162" s="2">
         <v>46264</v>
       </c>
       <c r="K162" t="b">
@@ -6782,7 +6808,7 @@
       <c r="H163">
         <v>73</v>
       </c>
-      <c r="J163" s="1">
+      <c r="J163" s="2">
         <v>46264</v>
       </c>
       <c r="K163" t="b">
@@ -6814,7 +6840,7 @@
       <c r="H164">
         <v>102</v>
       </c>
-      <c r="J164" s="1">
+      <c r="J164" s="2">
         <v>46463</v>
       </c>
       <c r="K164" t="b">
@@ -6846,7 +6872,7 @@
       <c r="H165">
         <v>118</v>
       </c>
-      <c r="J165" s="1">
+      <c r="J165" s="2">
         <v>46337</v>
       </c>
       <c r="K165" t="b">
@@ -6878,7 +6904,7 @@
       <c r="H166">
         <v>146</v>
       </c>
-      <c r="J166" s="1">
+      <c r="J166" s="2">
         <v>46451</v>
       </c>
       <c r="K166" t="b">
@@ -6910,7 +6936,7 @@
       <c r="H167">
         <v>152</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J167" s="2">
         <v>46245</v>
       </c>
       <c r="K167" t="b">
@@ -6942,7 +6968,7 @@
       <c r="H168">
         <v>152</v>
       </c>
-      <c r="J168" s="1">
+      <c r="J168" s="2">
         <v>46245</v>
       </c>
       <c r="K168" t="b">
@@ -6974,7 +7000,7 @@
       <c r="H169">
         <v>163</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J169" s="2">
         <v>46324</v>
       </c>
       <c r="K169" t="b">
@@ -7006,7 +7032,7 @@
       <c r="H170">
         <v>163</v>
       </c>
-      <c r="J170" s="1">
+      <c r="J170" s="2">
         <v>46324</v>
       </c>
       <c r="K170" t="b">
@@ -7038,7 +7064,7 @@
       <c r="H171">
         <v>164</v>
       </c>
-      <c r="J171" s="1">
+      <c r="J171" s="2">
         <v>46426</v>
       </c>
       <c r="K171" t="b">
@@ -7070,7 +7096,7 @@
       <c r="H172">
         <v>175</v>
       </c>
-      <c r="J172" s="1">
+      <c r="J172" s="2">
         <v>46383</v>
       </c>
       <c r="K172" t="b">
@@ -7102,7 +7128,7 @@
       <c r="H173">
         <v>186</v>
       </c>
-      <c r="J173" s="1">
+      <c r="J173" s="2">
         <v>46392</v>
       </c>
       <c r="K173" t="b">
@@ -7134,7 +7160,7 @@
       <c r="H174">
         <v>205</v>
       </c>
-      <c r="J174" s="1">
+      <c r="J174" s="2">
         <v>46390</v>
       </c>
       <c r="K174" t="b">
@@ -7166,7 +7192,7 @@
       <c r="H175">
         <v>207</v>
       </c>
-      <c r="J175" s="1">
+      <c r="J175" s="2">
         <v>46392</v>
       </c>
       <c r="K175" t="b">
@@ -7198,7 +7224,7 @@
       <c r="H176">
         <v>218</v>
       </c>
-      <c r="J176" s="1">
+      <c r="J176" s="2">
         <v>46506</v>
       </c>
       <c r="K176" t="b">
@@ -7230,7 +7256,7 @@
       <c r="H177">
         <v>246</v>
       </c>
-      <c r="J177" s="1">
+      <c r="J177" s="2">
         <v>46478</v>
       </c>
       <c r="K177" t="b">
@@ -7262,7 +7288,7 @@
       <c r="H178">
         <v>248</v>
       </c>
-      <c r="J178" s="1">
+      <c r="J178" s="2">
         <v>46500</v>
       </c>
       <c r="K178" t="b">
@@ -7294,7 +7320,7 @@
       <c r="H179">
         <v>276</v>
       </c>
-      <c r="J179" s="1">
+      <c r="J179" s="2">
         <v>46430</v>
       </c>
       <c r="K179" t="b">
@@ -7326,7 +7352,7 @@
       <c r="H180">
         <v>276</v>
       </c>
-      <c r="J180" s="1">
+      <c r="J180" s="2">
         <v>46430</v>
       </c>
       <c r="K180" t="b">
@@ -7358,7 +7384,7 @@
       <c r="H181">
         <v>290</v>
       </c>
-      <c r="J181" s="1">
+      <c r="J181" s="2">
         <v>46467</v>
       </c>
       <c r="K181" t="b">
@@ -7390,7 +7416,7 @@
       <c r="H182">
         <v>317</v>
       </c>
-      <c r="J182" s="1">
+      <c r="J182" s="2">
         <v>46529</v>
       </c>
       <c r="K182" t="b">
@@ -7422,7 +7448,7 @@
       <c r="H183">
         <v>420</v>
       </c>
-      <c r="J183" s="1">
+      <c r="J183" s="2">
         <v>46566</v>
       </c>
       <c r="K183" t="b">
@@ -7454,7 +7480,7 @@
       <c r="H184">
         <v>426</v>
       </c>
-      <c r="J184" s="1">
+      <c r="J184" s="2">
         <v>46571</v>
       </c>
       <c r="K184" t="b">
@@ -7486,7 +7512,7 @@
       <c r="H185">
         <v>721</v>
       </c>
-      <c r="J185" s="1">
+      <c r="J185" s="2">
         <v>46325</v>
       </c>
       <c r="K185" t="b">
@@ -7518,7 +7544,7 @@
       <c r="H186">
         <v>721</v>
       </c>
-      <c r="J186" s="1">
+      <c r="J186" s="2">
         <v>46325</v>
       </c>
       <c r="K186" t="b">
@@ -7550,7 +7576,7 @@
       <c r="H187">
         <v>850</v>
       </c>
-      <c r="J187" s="1">
+      <c r="J187" s="2">
         <v>46345</v>
       </c>
       <c r="K187" t="b">
@@ -7582,7 +7608,7 @@
       <c r="H188">
         <v>850</v>
       </c>
-      <c r="J188" s="1">
+      <c r="J188" s="2">
         <v>46345</v>
       </c>
       <c r="K188" t="b">
@@ -7614,7 +7640,7 @@
       <c r="H189">
         <v>1661</v>
       </c>
-      <c r="J189" s="1">
+      <c r="J189" s="2">
         <v>46498</v>
       </c>
       <c r="K189" t="b">
@@ -7646,7 +7672,7 @@
       <c r="H190">
         <v>1661</v>
       </c>
-      <c r="J190" s="1">
+      <c r="J190" s="2">
         <v>46498</v>
       </c>
       <c r="K190" t="b">
@@ -7678,7 +7704,7 @@
       <c r="H191">
         <v>488</v>
       </c>
-      <c r="J191" s="1">
+      <c r="J191" s="2">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -7710,7 +7736,7 @@
       <c r="H192">
         <v>25565</v>
       </c>
-      <c r="J192" s="1">
+      <c r="J192" s="2">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -7742,7 +7768,7 @@
       <c r="H193">
         <v>25567</v>
       </c>
-      <c r="J193" s="1">
+      <c r="J193" s="2">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -7774,7 +7800,7 @@
       <c r="H194">
         <v>31293</v>
       </c>
-      <c r="J194" s="1">
+      <c r="J194" s="2">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1040,16 +1040,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1065,7 +1057,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1073,30 +1065,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1396,37 +1370,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1455,7 +1429,7 @@
       <c r="H2">
         <v>-4402.8</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>41388</v>
       </c>
       <c r="K2" t="b">
@@ -1487,7 +1461,7 @@
       <c r="H3">
         <v>-4254.8</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>39285</v>
       </c>
       <c r="K3" t="b">
@@ -1519,7 +1493,7 @@
       <c r="H4">
         <v>-2354.2</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1551,7 +1525,7 @@
       <c r="H5">
         <v>-896.8</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>40669</v>
       </c>
       <c r="K5" t="b">
@@ -1583,7 +1557,7 @@
       <c r="H6">
         <v>-854.1</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>44884</v>
       </c>
       <c r="K6" t="b">
@@ -1615,7 +1589,7 @@
       <c r="H7">
         <v>-413.2</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>43855</v>
       </c>
       <c r="K7" t="b">
@@ -1647,7 +1621,7 @@
       <c r="H8">
         <v>-391.8</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>42769</v>
       </c>
       <c r="K8" t="b">
@@ -1679,7 +1653,7 @@
       <c r="H9">
         <v>-371.5</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>46014</v>
       </c>
       <c r="K9" t="b">
@@ -1711,7 +1685,7 @@
       <c r="H10">
         <v>-368.8</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>46014</v>
       </c>
       <c r="K10" t="b">
@@ -1743,7 +1717,7 @@
       <c r="H11">
         <v>-359</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -1775,7 +1749,7 @@
       <c r="H12">
         <v>-359</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>45804</v>
       </c>
       <c r="K12" t="b">
@@ -1807,7 +1781,7 @@
       <c r="H13">
         <v>-351</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>42821</v>
       </c>
       <c r="K13" t="b">
@@ -1839,7 +1813,7 @@
       <c r="H14">
         <v>-351</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1871,7 +1845,7 @@
       <c r="H15">
         <v>-351</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1903,7 +1877,7 @@
       <c r="H16">
         <v>-351</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>46014</v>
       </c>
       <c r="K16" t="b">
@@ -1935,7 +1909,7 @@
       <c r="H17">
         <v>-345.8</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1967,7 +1941,7 @@
       <c r="H18">
         <v>-345.8</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>46017</v>
       </c>
       <c r="K18" t="b">
@@ -1999,7 +1973,7 @@
       <c r="H19">
         <v>-264.2</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>40979</v>
       </c>
       <c r="K19" t="b">
@@ -2031,7 +2005,7 @@
       <c r="H20">
         <v>-206.4</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -2063,7 +2037,7 @@
       <c r="H21">
         <v>-131.6</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -2095,7 +2069,7 @@
       <c r="H22">
         <v>-131.6</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -2127,7 +2101,7 @@
       <c r="H23">
         <v>-131.6</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -2159,7 +2133,7 @@
       <c r="H24">
         <v>-131.6</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -2191,7 +2165,7 @@
       <c r="H25">
         <v>-131.6</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -2223,7 +2197,7 @@
       <c r="H26">
         <v>-105</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>46161</v>
       </c>
       <c r="K26" t="b">
@@ -2255,7 +2229,7 @@
       <c r="H27">
         <v>-79.8</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>43340</v>
       </c>
       <c r="K27" t="b">
@@ -2287,7 +2261,7 @@
       <c r="H28">
         <v>-12.3</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>46048</v>
       </c>
       <c r="K28" t="b">
@@ -2319,7 +2293,7 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>46211</v>
       </c>
       <c r="K29" t="b">
@@ -2351,7 +2325,7 @@
       <c r="H30">
         <v>3.6</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>46234</v>
       </c>
       <c r="K30" t="b">
@@ -2383,7 +2357,7 @@
       <c r="H31">
         <v>6.2</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>46234</v>
       </c>
       <c r="K31" t="b">
@@ -2415,7 +2389,7 @@
       <c r="H32">
         <v>7.5</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>46234</v>
       </c>
       <c r="K32" t="b">
@@ -2447,7 +2421,7 @@
       <c r="H33">
         <v>10.7</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>46234</v>
       </c>
       <c r="K33" t="b">
@@ -2479,7 +2453,7 @@
       <c r="H34">
         <v>20</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>46234</v>
       </c>
       <c r="K34" t="b">
@@ -2511,7 +2485,7 @@
       <c r="H35">
         <v>30.8</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>46234</v>
       </c>
       <c r="K35" t="b">
@@ -2543,7 +2517,7 @@
       <c r="H36">
         <v>37.1</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>46256</v>
       </c>
       <c r="K36" t="b">
@@ -2575,7 +2549,7 @@
       <c r="H37">
         <v>42.8</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>46276</v>
       </c>
       <c r="K37" t="b">
@@ -2607,7 +2581,7 @@
       <c r="H38">
         <v>45.2</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="1">
         <v>46234</v>
       </c>
       <c r="K38" t="b">
@@ -2639,7 +2613,7 @@
       <c r="H39">
         <v>46</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>46251</v>
       </c>
       <c r="K39" t="b">
@@ -2671,7 +2645,7 @@
       <c r="H40">
         <v>47.5</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>46456</v>
       </c>
       <c r="K40" t="b">
@@ -2703,7 +2677,7 @@
       <c r="H41">
         <v>57.2</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>46246</v>
       </c>
       <c r="K41" t="b">
@@ -2735,7 +2709,7 @@
       <c r="H42">
         <v>59.6</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>46487</v>
       </c>
       <c r="K42" t="b">
@@ -2767,7 +2741,7 @@
       <c r="H43">
         <v>75.40000000000001</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>46283</v>
       </c>
       <c r="K43" t="b">
@@ -2799,7 +2773,7 @@
       <c r="H44">
         <v>76.8</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>46285</v>
       </c>
       <c r="K44" t="b">
@@ -2831,7 +2805,7 @@
       <c r="H45">
         <v>83.2</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>46547</v>
       </c>
       <c r="K45" t="b">
@@ -2863,7 +2837,7 @@
       <c r="H46">
         <v>84.5</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>46240</v>
       </c>
       <c r="K46" t="b">
@@ -2895,7 +2869,7 @@
       <c r="H47">
         <v>85.8</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>46266</v>
       </c>
       <c r="K47" t="b">
@@ -2927,7 +2901,7 @@
       <c r="H48">
         <v>86.5</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="1">
         <v>46241</v>
       </c>
       <c r="K48" t="b">
@@ -2959,7 +2933,7 @@
       <c r="H49">
         <v>91.7</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>46243</v>
       </c>
       <c r="K49" t="b">
@@ -2991,7 +2965,7 @@
       <c r="H50">
         <v>91.7</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="1">
         <v>46243</v>
       </c>
       <c r="K50" t="b">
@@ -3023,7 +2997,7 @@
       <c r="H51">
         <v>91.7</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="1">
         <v>46250</v>
       </c>
       <c r="K51" t="b">
@@ -3055,7 +3029,7 @@
       <c r="H52">
         <v>98.90000000000001</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="1">
         <v>46253</v>
       </c>
       <c r="K52" t="b">
@@ -3087,7 +3061,7 @@
       <c r="H53">
         <v>105.5</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
         <v>46280</v>
       </c>
       <c r="K53" t="b">
@@ -3119,7 +3093,7 @@
       <c r="H54">
         <v>105.6</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="1">
         <v>46361</v>
       </c>
       <c r="K54" t="b">
@@ -3151,7 +3125,7 @@
       <c r="H55">
         <v>105.7</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
         <v>46362</v>
       </c>
       <c r="K55" t="b">
@@ -3183,7 +3157,7 @@
       <c r="H56">
         <v>110.7</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="1">
         <v>46275</v>
       </c>
       <c r="K56" t="b">
@@ -3215,7 +3189,7 @@
       <c r="H57">
         <v>113.2</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="1">
         <v>46377</v>
       </c>
       <c r="K57" t="b">
@@ -3247,7 +3221,7 @@
       <c r="H58">
         <v>128.8</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="1">
         <v>46434</v>
       </c>
       <c r="K58" t="b">
@@ -3279,7 +3253,7 @@
       <c r="H59">
         <v>128.8</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="1">
         <v>46434</v>
       </c>
       <c r="K59" t="b">
@@ -3311,7 +3285,7 @@
       <c r="H60">
         <v>128.8</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="1">
         <v>46434</v>
       </c>
       <c r="K60" t="b">
@@ -3343,7 +3317,7 @@
       <c r="H61">
         <v>128.8</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="1">
         <v>46434</v>
       </c>
       <c r="K61" t="b">
@@ -3375,7 +3349,7 @@
       <c r="H62">
         <v>128.8</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="1">
         <v>46434</v>
       </c>
       <c r="K62" t="b">
@@ -3407,7 +3381,7 @@
       <c r="H63">
         <v>135</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="1">
         <v>46280</v>
       </c>
       <c r="K63" t="b">
@@ -3439,7 +3413,7 @@
       <c r="H64">
         <v>150.6</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="1">
         <v>46271</v>
       </c>
       <c r="K64" t="b">
@@ -3471,7 +3445,7 @@
       <c r="H65">
         <v>174.2</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="1">
         <v>46363</v>
       </c>
       <c r="K65" t="b">
@@ -3503,7 +3477,7 @@
       <c r="H66">
         <v>176.6</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="1">
         <v>46334</v>
       </c>
       <c r="K66" t="b">
@@ -3535,7 +3509,7 @@
       <c r="H67">
         <v>177.4</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="1">
         <v>46407</v>
       </c>
       <c r="K67" t="b">
@@ -3567,7 +3541,7 @@
       <c r="H68">
         <v>183.9</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="1">
         <v>46341</v>
       </c>
       <c r="K68" t="b">
@@ -3599,7 +3573,7 @@
       <c r="H69">
         <v>191.7</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="1">
         <v>46300</v>
       </c>
       <c r="K69" t="b">
@@ -3631,7 +3605,7 @@
       <c r="H70">
         <v>200</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="1">
         <v>46336</v>
       </c>
       <c r="K70" t="b">
@@ -3663,7 +3637,7 @@
       <c r="H71">
         <v>201.1</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="1">
         <v>46319</v>
       </c>
       <c r="K71" t="b">
@@ -3695,7 +3669,7 @@
       <c r="H72">
         <v>206.5</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="1">
         <v>46308</v>
       </c>
       <c r="K72" t="b">
@@ -3727,7 +3701,7 @@
       <c r="H73">
         <v>207.5</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="1">
         <v>46390</v>
       </c>
       <c r="K73" t="b">
@@ -3759,7 +3733,7 @@
       <c r="H74">
         <v>247</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74" s="1">
         <v>46443</v>
       </c>
       <c r="K74" t="b">
@@ -3791,7 +3765,7 @@
       <c r="H75">
         <v>285.3</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75" s="1">
         <v>46304</v>
       </c>
       <c r="K75" t="b">
@@ -3823,7 +3797,7 @@
       <c r="H76">
         <v>290.8</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="1">
         <v>46362</v>
       </c>
       <c r="K76" t="b">
@@ -3855,7 +3829,7 @@
       <c r="H77">
         <v>295.2</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="1">
         <v>46463</v>
       </c>
       <c r="K77" t="b">
@@ -3887,7 +3861,7 @@
       <c r="H78">
         <v>300.2</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="1">
         <v>46466</v>
       </c>
       <c r="K78" t="b">
@@ -3922,7 +3896,7 @@
       <c r="I79" t="s">
         <v>313</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="1">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -3957,7 +3931,7 @@
       <c r="I80" t="s">
         <v>314</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="1">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -3992,7 +3966,7 @@
       <c r="I81" t="s">
         <v>315</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81" s="1">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -4027,7 +4001,7 @@
       <c r="I82" t="s">
         <v>316</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="1">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4062,7 +4036,7 @@
       <c r="I83" t="s">
         <v>316</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="1">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4097,7 +4071,7 @@
       <c r="I84" t="s">
         <v>317</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84" s="1">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4132,7 +4106,7 @@
       <c r="I85" t="s">
         <v>318</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="1">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4167,7 +4141,7 @@
       <c r="I86" t="s">
         <v>319</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86" s="1">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4202,7 +4176,7 @@
       <c r="I87" t="s">
         <v>320</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87" s="1">
         <v>46106</v>
       </c>
       <c r="K87" t="b">
@@ -4237,7 +4211,7 @@
       <c r="I88" t="s">
         <v>321</v>
       </c>
-      <c r="J88" s="2">
+      <c r="J88" s="1">
         <v>46142</v>
       </c>
       <c r="K88" t="b">
@@ -4272,7 +4246,7 @@
       <c r="I89" t="s">
         <v>322</v>
       </c>
-      <c r="J89" s="2">
+      <c r="J89" s="1">
         <v>46274</v>
       </c>
       <c r="K89" t="b">
@@ -4307,7 +4281,7 @@
       <c r="I90" t="s">
         <v>322</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90" s="1">
         <v>46276</v>
       </c>
       <c r="K90" t="b">
@@ -4342,7 +4316,7 @@
       <c r="I91" t="s">
         <v>322</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="1">
         <v>46284</v>
       </c>
       <c r="K91" t="b">
@@ -4377,7 +4351,7 @@
       <c r="I92" t="s">
         <v>323</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92" s="1">
         <v>46317</v>
       </c>
       <c r="K92" t="b">
@@ -4412,7 +4386,7 @@
       <c r="I93" t="s">
         <v>323</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93" s="1">
         <v>46319</v>
       </c>
       <c r="K93" t="b">
@@ -4447,7 +4421,7 @@
       <c r="I94" t="s">
         <v>324</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94" s="1">
         <v>46333</v>
       </c>
       <c r="K94" t="b">
@@ -4482,7 +4456,7 @@
       <c r="I95" t="s">
         <v>324</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95" s="1">
         <v>46338</v>
       </c>
       <c r="K95" t="b">
@@ -4517,7 +4491,7 @@
       <c r="I96" t="s">
         <v>324</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96" s="1">
         <v>46338</v>
       </c>
       <c r="K96" t="b">
@@ -4552,7 +4526,7 @@
       <c r="I97" t="s">
         <v>324</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97" s="1">
         <v>46341</v>
       </c>
       <c r="K97" t="b">
@@ -4587,7 +4561,7 @@
       <c r="I98" t="s">
         <v>324</v>
       </c>
-      <c r="J98" s="2">
+      <c r="J98" s="1">
         <v>46344</v>
       </c>
       <c r="K98" t="b">
@@ -4622,7 +4596,7 @@
       <c r="I99" t="s">
         <v>324</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99" s="1">
         <v>46354</v>
       </c>
       <c r="K99" t="b">
@@ -4657,7 +4631,7 @@
       <c r="I100" t="s">
         <v>324</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="1">
         <v>46360</v>
       </c>
       <c r="K100" t="b">
@@ -4692,7 +4666,7 @@
       <c r="I101" t="s">
         <v>324</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="1">
         <v>46360</v>
       </c>
       <c r="K101" t="b">
@@ -4727,7 +4701,7 @@
       <c r="I102" t="s">
         <v>325</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="1">
         <v>46366</v>
       </c>
       <c r="K102" t="b">
@@ -4762,7 +4736,7 @@
       <c r="I103" t="s">
         <v>325</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="1">
         <v>46375</v>
       </c>
       <c r="K103" t="b">
@@ -4797,7 +4771,7 @@
       <c r="I104" t="s">
         <v>325</v>
       </c>
-      <c r="J104" s="2">
+      <c r="J104" s="1">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -4832,7 +4806,7 @@
       <c r="I105" t="s">
         <v>326</v>
       </c>
-      <c r="J105" s="2">
+      <c r="J105" s="1">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -4867,7 +4841,7 @@
       <c r="I106" t="s">
         <v>326</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106" s="1">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -4902,7 +4876,7 @@
       <c r="I107" t="s">
         <v>326</v>
       </c>
-      <c r="J107" s="2">
+      <c r="J107" s="1">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -4937,7 +4911,7 @@
       <c r="I108" t="s">
         <v>326</v>
       </c>
-      <c r="J108" s="2">
+      <c r="J108" s="1">
         <v>46413</v>
       </c>
       <c r="K108" t="b">
@@ -4972,7 +4946,7 @@
       <c r="I109" t="s">
         <v>327</v>
       </c>
-      <c r="J109" s="2">
+      <c r="J109" s="1">
         <v>46424</v>
       </c>
       <c r="K109" t="b">
@@ -5007,7 +4981,7 @@
       <c r="I110" t="s">
         <v>327</v>
       </c>
-      <c r="J110" s="2">
+      <c r="J110" s="1">
         <v>46427</v>
       </c>
       <c r="K110" t="b">
@@ -5042,7 +5016,7 @@
       <c r="I111" t="s">
         <v>327</v>
       </c>
-      <c r="J111" s="2">
+      <c r="J111" s="1">
         <v>46437</v>
       </c>
       <c r="K111" t="b">
@@ -5077,7 +5051,7 @@
       <c r="I112" t="s">
         <v>327</v>
       </c>
-      <c r="J112" s="2">
+      <c r="J112" s="1">
         <v>46451</v>
       </c>
       <c r="K112" t="b">
@@ -5112,7 +5086,7 @@
       <c r="I113" t="s">
         <v>328</v>
       </c>
-      <c r="J113" s="2">
+      <c r="J113" s="1">
         <v>46455</v>
       </c>
       <c r="K113" t="b">
@@ -5147,7 +5121,7 @@
       <c r="I114" t="s">
         <v>328</v>
       </c>
-      <c r="J114" s="2">
+      <c r="J114" s="1">
         <v>46457</v>
       </c>
       <c r="K114" t="b">
@@ -5182,7 +5156,7 @@
       <c r="I115" t="s">
         <v>328</v>
       </c>
-      <c r="J115" s="2">
+      <c r="J115" s="1">
         <v>46462</v>
       </c>
       <c r="K115" t="b">
@@ -5217,7 +5191,7 @@
       <c r="I116" t="s">
         <v>328</v>
       </c>
-      <c r="J116" s="2">
+      <c r="J116" s="1">
         <v>46464</v>
       </c>
       <c r="K116" t="b">
@@ -5252,7 +5226,7 @@
       <c r="I117" t="s">
         <v>328</v>
       </c>
-      <c r="J117" s="2">
+      <c r="J117" s="1">
         <v>46470</v>
       </c>
       <c r="K117" t="b">
@@ -5287,7 +5261,7 @@
       <c r="I118" t="s">
         <v>329</v>
       </c>
-      <c r="J118" s="2">
+      <c r="J118" s="1">
         <v>46485</v>
       </c>
       <c r="K118" t="b">
@@ -5322,7 +5296,7 @@
       <c r="I119" t="s">
         <v>329</v>
       </c>
-      <c r="J119" s="2">
+      <c r="J119" s="1">
         <v>46499</v>
       </c>
       <c r="K119" t="b">
@@ -5357,7 +5331,7 @@
       <c r="I120" t="s">
         <v>329</v>
       </c>
-      <c r="J120" s="2">
+      <c r="J120" s="1">
         <v>46504</v>
       </c>
       <c r="K120" t="b">
@@ -5392,7 +5366,7 @@
       <c r="I121" t="s">
         <v>329</v>
       </c>
-      <c r="J121" s="2">
+      <c r="J121" s="1">
         <v>46504</v>
       </c>
       <c r="K121" t="b">
@@ -5427,7 +5401,7 @@
       <c r="I122" t="s">
         <v>329</v>
       </c>
-      <c r="J122" s="2">
+      <c r="J122" s="1">
         <v>46507</v>
       </c>
       <c r="K122" t="b">
@@ -5462,7 +5436,7 @@
       <c r="I123" t="s">
         <v>329</v>
       </c>
-      <c r="J123" s="2">
+      <c r="J123" s="1">
         <v>46508</v>
       </c>
       <c r="K123" t="b">
@@ -5497,7 +5471,7 @@
       <c r="I124" t="s">
         <v>329</v>
       </c>
-      <c r="J124" s="2">
+      <c r="J124" s="1">
         <v>46512</v>
       </c>
       <c r="K124" t="b">
@@ -5532,7 +5506,7 @@
       <c r="I125" t="s">
         <v>329</v>
       </c>
-      <c r="J125" s="2">
+      <c r="J125" s="1">
         <v>46512</v>
       </c>
       <c r="K125" t="b">
@@ -5567,7 +5541,7 @@
       <c r="I126" t="s">
         <v>330</v>
       </c>
-      <c r="J126" s="2">
+      <c r="J126" s="1">
         <v>46528</v>
       </c>
       <c r="K126" t="b">
@@ -5602,7 +5576,7 @@
       <c r="I127" t="s">
         <v>330</v>
       </c>
-      <c r="J127" s="2">
+      <c r="J127" s="1">
         <v>46529</v>
       </c>
       <c r="K127" t="b">
@@ -5637,7 +5611,7 @@
       <c r="I128" t="s">
         <v>330</v>
       </c>
-      <c r="J128" s="2">
+      <c r="J128" s="1">
         <v>46537</v>
       </c>
       <c r="K128" t="b">
@@ -5672,7 +5646,7 @@
       <c r="I129" t="s">
         <v>331</v>
       </c>
-      <c r="J129" s="2">
+      <c r="J129" s="1">
         <v>46546</v>
       </c>
       <c r="K129" t="b">
@@ -5707,7 +5681,7 @@
       <c r="I130" t="s">
         <v>331</v>
       </c>
-      <c r="J130" s="2">
+      <c r="J130" s="1">
         <v>46547</v>
       </c>
       <c r="K130" t="b">
@@ -5742,7 +5716,7 @@
       <c r="I131" t="s">
         <v>331</v>
       </c>
-      <c r="J131" s="2">
+      <c r="J131" s="1">
         <v>46547</v>
       </c>
       <c r="K131" t="b">
@@ -5777,7 +5751,7 @@
       <c r="I132" t="s">
         <v>331</v>
       </c>
-      <c r="J132" s="2">
+      <c r="J132" s="1">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -5812,7 +5786,7 @@
       <c r="I133" t="s">
         <v>331</v>
       </c>
-      <c r="J133" s="2">
+      <c r="J133" s="1">
         <v>46551</v>
       </c>
       <c r="K133" t="b">
@@ -5847,7 +5821,7 @@
       <c r="I134" t="s">
         <v>331</v>
       </c>
-      <c r="J134" s="2">
+      <c r="J134" s="1">
         <v>46560</v>
       </c>
       <c r="K134" t="b">
@@ -5882,7 +5856,7 @@
       <c r="I135" t="s">
         <v>331</v>
       </c>
-      <c r="J135" s="2">
+      <c r="J135" s="1">
         <v>46564</v>
       </c>
       <c r="K135" t="b">
@@ -5917,7 +5891,7 @@
       <c r="I136" t="s">
         <v>331</v>
       </c>
-      <c r="J136" s="2">
+      <c r="J136" s="1">
         <v>46567</v>
       </c>
       <c r="K136" t="b">
@@ -5952,7 +5926,7 @@
       <c r="I137" t="s">
         <v>331</v>
       </c>
-      <c r="J137" s="2">
+      <c r="J137" s="1">
         <v>46568</v>
       </c>
       <c r="K137" t="b">
@@ -5987,7 +5961,7 @@
       <c r="I138" t="s">
         <v>331</v>
       </c>
-      <c r="J138" s="2">
+      <c r="J138" s="1">
         <v>46571</v>
       </c>
       <c r="K138" t="b">
@@ -6022,7 +5996,7 @@
       <c r="I139" t="s">
         <v>332</v>
       </c>
-      <c r="J139" s="2">
+      <c r="J139" s="1">
         <v>46197</v>
       </c>
       <c r="K139" t="b">
@@ -6057,7 +6031,7 @@
       <c r="I140" t="s">
         <v>333</v>
       </c>
-      <c r="J140" s="2">
+      <c r="J140" s="1">
         <v>46212</v>
       </c>
       <c r="K140" t="b">
@@ -6092,7 +6066,7 @@
       <c r="I141" t="s">
         <v>334</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J141" s="1">
         <v>46225</v>
       </c>
       <c r="K141" t="b">
@@ -6127,7 +6101,7 @@
       <c r="I142" t="s">
         <v>335</v>
       </c>
-      <c r="J142" s="2">
+      <c r="J142" s="1">
         <v>46234</v>
       </c>
       <c r="K142" t="b">
@@ -6162,7 +6136,7 @@
       <c r="I143" t="s">
         <v>336</v>
       </c>
-      <c r="J143" s="2">
+      <c r="J143" s="1">
         <v>46234</v>
       </c>
       <c r="K143" t="b">
@@ -6197,7 +6171,7 @@
       <c r="I144" t="s">
         <v>337</v>
       </c>
-      <c r="J144" s="2">
+      <c r="J144" s="1">
         <v>46263</v>
       </c>
       <c r="K144" t="b">
@@ -6232,7 +6206,7 @@
       <c r="I145" t="s">
         <v>338</v>
       </c>
-      <c r="J145" s="2">
+      <c r="J145" s="1">
         <v>46266</v>
       </c>
       <c r="K145" t="b">
@@ -6264,7 +6238,7 @@
       <c r="H146">
         <v>-1476</v>
       </c>
-      <c r="J146" s="2">
+      <c r="J146" s="1">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -6296,7 +6270,7 @@
       <c r="H147">
         <v>-1469</v>
       </c>
-      <c r="J147" s="2">
+      <c r="J147" s="1">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -6328,7 +6302,7 @@
       <c r="H148">
         <v>-1121</v>
       </c>
-      <c r="J148" s="2">
+      <c r="J148" s="1">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -6360,7 +6334,7 @@
       <c r="H149">
         <v>-1018</v>
       </c>
-      <c r="J149" s="2">
+      <c r="J149" s="1">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -6392,7 +6366,7 @@
       <c r="H150">
         <v>-950</v>
       </c>
-      <c r="J150" s="2">
+      <c r="J150" s="1">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -6424,7 +6398,7 @@
       <c r="H151">
         <v>-943</v>
       </c>
-      <c r="J151" s="2">
+      <c r="J151" s="1">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -6456,7 +6430,7 @@
       <c r="H152">
         <v>-252</v>
       </c>
-      <c r="J152" s="2">
+      <c r="J152" s="1">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -6488,7 +6462,7 @@
       <c r="H153">
         <v>-196</v>
       </c>
-      <c r="J153" s="2">
+      <c r="J153" s="1">
         <v>45988</v>
       </c>
       <c r="K153" t="b">
@@ -6520,7 +6494,7 @@
       <c r="H154">
         <v>-196</v>
       </c>
-      <c r="J154" s="2">
+      <c r="J154" s="1">
         <v>45988</v>
       </c>
       <c r="K154" t="b">
@@ -6552,7 +6526,7 @@
       <c r="H155">
         <v>-47</v>
       </c>
-      <c r="J155" s="2">
+      <c r="J155" s="1">
         <v>46176</v>
       </c>
       <c r="K155" t="b">
@@ -6584,7 +6558,7 @@
       <c r="H156">
         <v>-47</v>
       </c>
-      <c r="J156" s="2">
+      <c r="J156" s="1">
         <v>46176</v>
       </c>
       <c r="K156" t="b">
@@ -6616,7 +6590,7 @@
       <c r="H157">
         <v>-33</v>
       </c>
-      <c r="J157" s="2">
+      <c r="J157" s="1">
         <v>46199</v>
       </c>
       <c r="K157" t="b">
@@ -6648,7 +6622,7 @@
       <c r="H158">
         <v>-33</v>
       </c>
-      <c r="J158" s="2">
+      <c r="J158" s="1">
         <v>46199</v>
       </c>
       <c r="K158" t="b">
@@ -6680,7 +6654,7 @@
       <c r="H159">
         <v>-6</v>
       </c>
-      <c r="J159" s="2">
+      <c r="J159" s="1">
         <v>45967</v>
       </c>
       <c r="K159" t="b">
@@ -6712,7 +6686,7 @@
       <c r="H160">
         <v>43</v>
       </c>
-      <c r="J160" s="2">
+      <c r="J160" s="1">
         <v>46440</v>
       </c>
       <c r="K160" t="b">
@@ -6744,7 +6718,7 @@
       <c r="H161">
         <v>43</v>
       </c>
-      <c r="J161" s="2">
+      <c r="J161" s="1">
         <v>46440</v>
       </c>
       <c r="K161" t="b">
@@ -6776,7 +6750,7 @@
       <c r="H162">
         <v>73</v>
       </c>
-      <c r="J162" s="2">
+      <c r="J162" s="1">
         <v>46264</v>
       </c>
       <c r="K162" t="b">
@@ -6808,7 +6782,7 @@
       <c r="H163">
         <v>73</v>
       </c>
-      <c r="J163" s="2">
+      <c r="J163" s="1">
         <v>46264</v>
       </c>
       <c r="K163" t="b">
@@ -6840,7 +6814,7 @@
       <c r="H164">
         <v>102</v>
       </c>
-      <c r="J164" s="2">
+      <c r="J164" s="1">
         <v>46463</v>
       </c>
       <c r="K164" t="b">
@@ -6872,7 +6846,7 @@
       <c r="H165">
         <v>118</v>
       </c>
-      <c r="J165" s="2">
+      <c r="J165" s="1">
         <v>46337</v>
       </c>
       <c r="K165" t="b">
@@ -6904,7 +6878,7 @@
       <c r="H166">
         <v>146</v>
       </c>
-      <c r="J166" s="2">
+      <c r="J166" s="1">
         <v>46451</v>
       </c>
       <c r="K166" t="b">
@@ -6936,7 +6910,7 @@
       <c r="H167">
         <v>152</v>
       </c>
-      <c r="J167" s="2">
+      <c r="J167" s="1">
         <v>46245</v>
       </c>
       <c r="K167" t="b">
@@ -6968,7 +6942,7 @@
       <c r="H168">
         <v>152</v>
       </c>
-      <c r="J168" s="2">
+      <c r="J168" s="1">
         <v>46245</v>
       </c>
       <c r="K168" t="b">
@@ -7000,7 +6974,7 @@
       <c r="H169">
         <v>163</v>
       </c>
-      <c r="J169" s="2">
+      <c r="J169" s="1">
         <v>46324</v>
       </c>
       <c r="K169" t="b">
@@ -7032,7 +7006,7 @@
       <c r="H170">
         <v>163</v>
       </c>
-      <c r="J170" s="2">
+      <c r="J170" s="1">
         <v>46324</v>
       </c>
       <c r="K170" t="b">
@@ -7064,7 +7038,7 @@
       <c r="H171">
         <v>164</v>
       </c>
-      <c r="J171" s="2">
+      <c r="J171" s="1">
         <v>46426</v>
       </c>
       <c r="K171" t="b">
@@ -7096,7 +7070,7 @@
       <c r="H172">
         <v>175</v>
       </c>
-      <c r="J172" s="2">
+      <c r="J172" s="1">
         <v>46383</v>
       </c>
       <c r="K172" t="b">
@@ -7128,7 +7102,7 @@
       <c r="H173">
         <v>186</v>
       </c>
-      <c r="J173" s="2">
+      <c r="J173" s="1">
         <v>46392</v>
       </c>
       <c r="K173" t="b">
@@ -7160,7 +7134,7 @@
       <c r="H174">
         <v>205</v>
       </c>
-      <c r="J174" s="2">
+      <c r="J174" s="1">
         <v>46390</v>
       </c>
       <c r="K174" t="b">
@@ -7192,7 +7166,7 @@
       <c r="H175">
         <v>207</v>
       </c>
-      <c r="J175" s="2">
+      <c r="J175" s="1">
         <v>46392</v>
       </c>
       <c r="K175" t="b">
@@ -7224,7 +7198,7 @@
       <c r="H176">
         <v>218</v>
       </c>
-      <c r="J176" s="2">
+      <c r="J176" s="1">
         <v>46506</v>
       </c>
       <c r="K176" t="b">
@@ -7256,7 +7230,7 @@
       <c r="H177">
         <v>246</v>
       </c>
-      <c r="J177" s="2">
+      <c r="J177" s="1">
         <v>46478</v>
       </c>
       <c r="K177" t="b">
@@ -7288,7 +7262,7 @@
       <c r="H178">
         <v>248</v>
       </c>
-      <c r="J178" s="2">
+      <c r="J178" s="1">
         <v>46500</v>
       </c>
       <c r="K178" t="b">
@@ -7320,7 +7294,7 @@
       <c r="H179">
         <v>276</v>
       </c>
-      <c r="J179" s="2">
+      <c r="J179" s="1">
         <v>46430</v>
       </c>
       <c r="K179" t="b">
@@ -7352,7 +7326,7 @@
       <c r="H180">
         <v>276</v>
       </c>
-      <c r="J180" s="2">
+      <c r="J180" s="1">
         <v>46430</v>
       </c>
       <c r="K180" t="b">
@@ -7384,7 +7358,7 @@
       <c r="H181">
         <v>290</v>
       </c>
-      <c r="J181" s="2">
+      <c r="J181" s="1">
         <v>46467</v>
       </c>
       <c r="K181" t="b">
@@ -7416,7 +7390,7 @@
       <c r="H182">
         <v>317</v>
       </c>
-      <c r="J182" s="2">
+      <c r="J182" s="1">
         <v>46529</v>
       </c>
       <c r="K182" t="b">
@@ -7448,7 +7422,7 @@
       <c r="H183">
         <v>420</v>
       </c>
-      <c r="J183" s="2">
+      <c r="J183" s="1">
         <v>46566</v>
       </c>
       <c r="K183" t="b">
@@ -7480,7 +7454,7 @@
       <c r="H184">
         <v>426</v>
       </c>
-      <c r="J184" s="2">
+      <c r="J184" s="1">
         <v>46571</v>
       </c>
       <c r="K184" t="b">
@@ -7512,7 +7486,7 @@
       <c r="H185">
         <v>721</v>
       </c>
-      <c r="J185" s="2">
+      <c r="J185" s="1">
         <v>46325</v>
       </c>
       <c r="K185" t="b">
@@ -7544,7 +7518,7 @@
       <c r="H186">
         <v>721</v>
       </c>
-      <c r="J186" s="2">
+      <c r="J186" s="1">
         <v>46325</v>
       </c>
       <c r="K186" t="b">
@@ -7576,7 +7550,7 @@
       <c r="H187">
         <v>850</v>
       </c>
-      <c r="J187" s="2">
+      <c r="J187" s="1">
         <v>46345</v>
       </c>
       <c r="K187" t="b">
@@ -7608,7 +7582,7 @@
       <c r="H188">
         <v>850</v>
       </c>
-      <c r="J188" s="2">
+      <c r="J188" s="1">
         <v>46345</v>
       </c>
       <c r="K188" t="b">
@@ -7640,7 +7614,7 @@
       <c r="H189">
         <v>1661</v>
       </c>
-      <c r="J189" s="2">
+      <c r="J189" s="1">
         <v>46498</v>
       </c>
       <c r="K189" t="b">
@@ -7672,7 +7646,7 @@
       <c r="H190">
         <v>1661</v>
       </c>
-      <c r="J190" s="2">
+      <c r="J190" s="1">
         <v>46498</v>
       </c>
       <c r="K190" t="b">
@@ -7704,7 +7678,7 @@
       <c r="H191">
         <v>488</v>
       </c>
-      <c r="J191" s="2">
+      <c r="J191" s="1">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -7736,7 +7710,7 @@
       <c r="H192">
         <v>25565</v>
       </c>
-      <c r="J192" s="2">
+      <c r="J192" s="1">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -7768,7 +7742,7 @@
       <c r="H193">
         <v>25567</v>
       </c>
-      <c r="J193" s="2">
+      <c r="J193" s="1">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -7800,7 +7774,7 @@
       <c r="H194">
         <v>31293</v>
       </c>
-      <c r="J194" s="2">
+      <c r="J194" s="1">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="332">
   <si>
     <t>matricula</t>
   </si>
@@ -49,9 +49,6 @@
     <t>vencido</t>
   </si>
   <si>
-    <t>PCE-PC2047</t>
-  </si>
-  <si>
     <t>A000AH4R</t>
   </si>
   <si>
@@ -67,405 +64,405 @@
     <t>PCE-PC2360</t>
   </si>
   <si>
+    <t>18B464</t>
+  </si>
+  <si>
     <t>PZL/12/085</t>
   </si>
   <si>
-    <t>18B464</t>
-  </si>
-  <si>
     <t>A00260B2</t>
   </si>
   <si>
     <t>RWA11F115</t>
   </si>
   <si>
+    <t>CRAZAEYU119</t>
+  </si>
+  <si>
+    <t>A0040MHL</t>
+  </si>
+  <si>
     <t>A004166F</t>
   </si>
   <si>
-    <t>A0040MHL</t>
-  </si>
-  <si>
-    <t>CRAZAEYU119</t>
+    <t>YUAB001H725</t>
   </si>
   <si>
     <t>PCE-PC2232</t>
   </si>
   <si>
-    <t>YUAB001H725</t>
-  </si>
-  <si>
     <t>PCE-PC2055</t>
   </si>
   <si>
+    <t>PC-EPC0431</t>
+  </si>
+  <si>
     <t>PCE-PC0797</t>
   </si>
   <si>
+    <t>5X424</t>
+  </si>
+  <si>
     <t>5H725</t>
   </si>
   <si>
     <t>A000CT12</t>
   </si>
   <si>
+    <t>6X312</t>
+  </si>
+  <si>
     <t>5X499</t>
   </si>
   <si>
-    <t>5X424</t>
-  </si>
-  <si>
-    <t>6X312</t>
-  </si>
-  <si>
-    <t>S00562</t>
-  </si>
-  <si>
-    <t>PCE-PC2290</t>
+    <t>PCE-PC2050</t>
+  </si>
+  <si>
+    <t>090520002930A9</t>
+  </si>
+  <si>
+    <t>98053601.0</t>
+  </si>
+  <si>
+    <t>PCE-PC2358</t>
+  </si>
+  <si>
+    <t>PCE-PC2223</t>
+  </si>
+  <si>
+    <t>CRAZAFLZ243</t>
+  </si>
+  <si>
+    <t>PCE-PC2257</t>
+  </si>
+  <si>
+    <t>PCE-PC1211</t>
+  </si>
+  <si>
+    <t>PCE-PC1002</t>
+  </si>
+  <si>
+    <t>PZL/10/027</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>PCE-PC0776</t>
+  </si>
+  <si>
+    <t>905200298400.0</t>
+  </si>
+  <si>
+    <t>2223.0</t>
+  </si>
+  <si>
+    <t>PCE-PC2261</t>
+  </si>
+  <si>
+    <t>090520028327B</t>
+  </si>
+  <si>
+    <t>16829339.0</t>
+  </si>
+  <si>
+    <t>9T787</t>
+  </si>
+  <si>
+    <t>PZL/07/088</t>
+  </si>
+  <si>
+    <t>PCE-PC1570</t>
+  </si>
+  <si>
+    <t>17176905.0</t>
+  </si>
+  <si>
+    <t>PZL/09/072</t>
+  </si>
+  <si>
+    <t>JHZ-17-026</t>
+  </si>
+  <si>
+    <t>PCE-PC0743</t>
+  </si>
+  <si>
+    <t>5784241.0</t>
+  </si>
+  <si>
+    <t>090520028EC43</t>
+  </si>
+  <si>
+    <t>4572.0</t>
   </si>
   <si>
     <t>PCE-PC2115</t>
   </si>
   <si>
-    <t>PCE-PC2358</t>
-  </si>
-  <si>
-    <t>9804953.0</t>
-  </si>
-  <si>
-    <t>090520002930A9</t>
-  </si>
-  <si>
-    <t>PCE-PC2223</t>
-  </si>
-  <si>
-    <t>PCE-PC1570</t>
-  </si>
-  <si>
-    <t>090520028EC43</t>
-  </si>
-  <si>
-    <t>PCE-PC0743</t>
-  </si>
-  <si>
-    <t>PCE-PC1666</t>
-  </si>
-  <si>
-    <t>905200298400.0</t>
-  </si>
-  <si>
-    <t>9704228.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2257</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>PCE-PC1860</t>
-  </si>
-  <si>
-    <t>2223.0</t>
-  </si>
-  <si>
-    <t>PCE-PC2261</t>
-  </si>
-  <si>
-    <t>090520028327B</t>
-  </si>
-  <si>
-    <t>17176905.0</t>
-  </si>
-  <si>
-    <t>9T787</t>
-  </si>
-  <si>
-    <t>PCE-PC0776</t>
-  </si>
-  <si>
-    <t>PZL/09/072</t>
-  </si>
-  <si>
-    <t>JHZ-17-026</t>
-  </si>
-  <si>
-    <t>PCE-PC1211</t>
-  </si>
-  <si>
-    <t>PZL/10/027</t>
-  </si>
-  <si>
-    <t>16829339.0</t>
-  </si>
-  <si>
-    <t>CRAZAFLZ243</t>
+    <t>338.0</t>
+  </si>
+  <si>
+    <t>9802842.0</t>
+  </si>
+  <si>
+    <t>SM2702</t>
+  </si>
+  <si>
+    <t>A0039K1D</t>
+  </si>
+  <si>
+    <t>A003H05Y</t>
+  </si>
+  <si>
+    <t>RWA29E680</t>
+  </si>
+  <si>
+    <t>A003FFF9</t>
+  </si>
+  <si>
+    <t>CRAZAEOM091</t>
+  </si>
+  <si>
+    <t>1905XL</t>
+  </si>
+  <si>
+    <t>9757.0</t>
+  </si>
+  <si>
+    <t>11200478.0</t>
+  </si>
+  <si>
+    <t>9038.0</t>
+  </si>
+  <si>
+    <t>PZLL010SB</t>
   </si>
   <si>
     <t>11100371.0</t>
   </si>
   <si>
+    <t>862.0</t>
+  </si>
+  <si>
+    <t>11402681.0</t>
+  </si>
+  <si>
+    <t>7475.0</t>
+  </si>
+  <si>
+    <t>16A856</t>
+  </si>
+  <si>
+    <t>A0037CAC</t>
+  </si>
+  <si>
+    <t>8890.0</t>
+  </si>
+  <si>
+    <t>1705.0</t>
+  </si>
+  <si>
+    <t>2K221</t>
+  </si>
+  <si>
+    <t>D-0397408</t>
+  </si>
+  <si>
+    <t>391730-020</t>
+  </si>
+  <si>
+    <t>110076.0</t>
+  </si>
+  <si>
+    <t>170-07437</t>
+  </si>
+  <si>
+    <t>B10811395</t>
+  </si>
+  <si>
+    <t>10603746.0</t>
+  </si>
+  <si>
+    <t>10BC80</t>
+  </si>
+  <si>
+    <t>392140-009</t>
+  </si>
+  <si>
+    <t>9803650.0</t>
+  </si>
+  <si>
     <t>5784237.0</t>
   </si>
   <si>
-    <t>A003FFF9</t>
-  </si>
-  <si>
-    <t>CRAZAEOM091</t>
-  </si>
-  <si>
-    <t>A0039K1D</t>
-  </si>
-  <si>
-    <t>A003H05Y</t>
-  </si>
-  <si>
-    <t>RWA29E680</t>
-  </si>
-  <si>
-    <t>5784241.0</t>
-  </si>
-  <si>
-    <t>PZL/07/088</t>
-  </si>
-  <si>
-    <t>9038.0</t>
-  </si>
-  <si>
-    <t>9757.0</t>
-  </si>
-  <si>
-    <t>862.0</t>
-  </si>
-  <si>
-    <t>11200478.0</t>
-  </si>
-  <si>
-    <t>9802842.0</t>
-  </si>
-  <si>
-    <t>11402681.0</t>
-  </si>
-  <si>
-    <t>10000618.0</t>
-  </si>
-  <si>
-    <t>1905XL</t>
-  </si>
-  <si>
-    <t>PZLL010SB</t>
-  </si>
-  <si>
-    <t>7475.0</t>
-  </si>
-  <si>
-    <t>8890.0</t>
-  </si>
-  <si>
-    <t>6454.0</t>
-  </si>
-  <si>
-    <t>A0037CAC</t>
-  </si>
-  <si>
-    <t>2K221</t>
-  </si>
-  <si>
-    <t>D-0397408</t>
-  </si>
-  <si>
-    <t>391730-020</t>
-  </si>
-  <si>
-    <t>110076.0</t>
-  </si>
-  <si>
-    <t>170-07437</t>
-  </si>
-  <si>
-    <t>B10811395</t>
-  </si>
-  <si>
-    <t>10603746.0</t>
-  </si>
-  <si>
-    <t>10BC80</t>
-  </si>
-  <si>
-    <t>846.0</t>
+    <t>A87528</t>
+  </si>
+  <si>
+    <t>B10811727</t>
+  </si>
+  <si>
+    <t>7572.0</t>
+  </si>
+  <si>
+    <t>8737.0</t>
+  </si>
+  <si>
+    <t>1012821-019</t>
+  </si>
+  <si>
+    <t>929.0</t>
+  </si>
+  <si>
+    <t>D58293653</t>
+  </si>
+  <si>
+    <t>A-24022580</t>
+  </si>
+  <si>
+    <t>A-24022576</t>
+  </si>
+  <si>
+    <t>70.0</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>44.0</t>
+  </si>
+  <si>
+    <t>61.0</t>
+  </si>
+  <si>
+    <t>71.0</t>
+  </si>
+  <si>
+    <t>393069-038</t>
+  </si>
+  <si>
+    <t>G-45677217</t>
+  </si>
+  <si>
+    <t>7869.0</t>
+  </si>
+  <si>
+    <t>D-00397388</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>240.0</t>
+  </si>
+  <si>
+    <t>D00398015</t>
+  </si>
+  <si>
+    <t>E09393184</t>
   </si>
   <si>
     <t>210-10043</t>
   </si>
   <si>
-    <t>248.0</t>
-  </si>
-  <si>
-    <t>D58293589</t>
-  </si>
-  <si>
-    <t>392140-009</t>
-  </si>
-  <si>
-    <t>A87528</t>
-  </si>
-  <si>
-    <t>B10811727</t>
-  </si>
-  <si>
-    <t>7572.0</t>
-  </si>
-  <si>
-    <t>1012821-019</t>
-  </si>
-  <si>
-    <t>8737.0</t>
-  </si>
-  <si>
-    <t>929.0</t>
-  </si>
-  <si>
-    <t>D58293653</t>
-  </si>
-  <si>
-    <t>98053601.0</t>
-  </si>
-  <si>
-    <t>A-24022580</t>
-  </si>
-  <si>
-    <t>A-24022576</t>
+    <t>D00398016</t>
+  </si>
+  <si>
+    <t>D00397796</t>
+  </si>
+  <si>
+    <t>9600123.0</t>
+  </si>
+  <si>
+    <t>B10811720</t>
+  </si>
+  <si>
+    <t>D-00397408</t>
+  </si>
+  <si>
+    <t>7044.0</t>
+  </si>
+  <si>
+    <t>210-10039</t>
+  </si>
+  <si>
+    <t>2986900100469.0</t>
+  </si>
+  <si>
+    <t>3726.0</t>
+  </si>
+  <si>
+    <t>C66369</t>
+  </si>
+  <si>
+    <t>I-01810674</t>
+  </si>
+  <si>
+    <t>210-13181</t>
+  </si>
+  <si>
+    <t>11100370.0</t>
+  </si>
+  <si>
+    <t>912962.0</t>
+  </si>
+  <si>
+    <t>7911.0</t>
+  </si>
+  <si>
+    <t>10000617.0</t>
+  </si>
+  <si>
+    <t>D00398018</t>
+  </si>
+  <si>
+    <t>2986900100392.0</t>
+  </si>
+  <si>
+    <t>2986900100467.0</t>
+  </si>
+  <si>
+    <t>2986900100513.0</t>
+  </si>
+  <si>
+    <t>11A</t>
+  </si>
+  <si>
+    <t>960707.0</t>
+  </si>
+  <si>
+    <t>210-10042</t>
+  </si>
+  <si>
+    <t>399407-032</t>
+  </si>
+  <si>
+    <t>5784239.0</t>
+  </si>
+  <si>
+    <t>T-24634412</t>
+  </si>
+  <si>
+    <t>396315-038</t>
+  </si>
+  <si>
+    <t>D00397793</t>
   </si>
   <si>
     <t>399910-010</t>
   </si>
   <si>
-    <t>157.0</t>
-  </si>
-  <si>
-    <t>393069-038</t>
-  </si>
-  <si>
-    <t>G-45677217</t>
-  </si>
-  <si>
-    <t>7869.0</t>
-  </si>
-  <si>
-    <t>D-00397388</t>
-  </si>
-  <si>
-    <t>960005.0</t>
-  </si>
-  <si>
-    <t>D00398015</t>
-  </si>
-  <si>
-    <t>396315-038</t>
-  </si>
-  <si>
-    <t>E09393184</t>
-  </si>
-  <si>
-    <t>D00398016</t>
-  </si>
-  <si>
-    <t>D00397796</t>
-  </si>
-  <si>
-    <t>B10811720</t>
-  </si>
-  <si>
-    <t>9804951.0</t>
-  </si>
-  <si>
-    <t>D-00397408</t>
-  </si>
-  <si>
-    <t>7044.0</t>
-  </si>
-  <si>
-    <t>210-10039</t>
-  </si>
-  <si>
-    <t>2986900100469.0</t>
-  </si>
-  <si>
-    <t>3726.0</t>
-  </si>
-  <si>
-    <t>C66369</t>
-  </si>
-  <si>
-    <t>I-01810674</t>
-  </si>
-  <si>
-    <t>210-13181</t>
-  </si>
-  <si>
-    <t>11100370.0</t>
-  </si>
-  <si>
-    <t>912962.0</t>
-  </si>
-  <si>
-    <t>7911.0</t>
-  </si>
-  <si>
-    <t>10000617.0</t>
-  </si>
-  <si>
-    <t>D00398018</t>
-  </si>
-  <si>
-    <t>2986900100392.0</t>
-  </si>
-  <si>
-    <t>2986900100467.0</t>
-  </si>
-  <si>
-    <t>2986900100513.0</t>
-  </si>
-  <si>
-    <t>11A</t>
-  </si>
-  <si>
-    <t>960707.0</t>
-  </si>
-  <si>
-    <t>210-10042</t>
-  </si>
-  <si>
-    <t>399407-032</t>
-  </si>
-  <si>
-    <t>5784239.0</t>
-  </si>
-  <si>
-    <t>T-24634412</t>
-  </si>
-  <si>
-    <t>D00398014</t>
-  </si>
-  <si>
-    <t>100A</t>
-  </si>
-  <si>
     <t>1779.0</t>
   </si>
   <si>
     <t>D00397933</t>
   </si>
   <si>
-    <t>PCE-PC1002</t>
-  </si>
-  <si>
-    <t>102.0</t>
-  </si>
-  <si>
     <t>9601404.0</t>
   </si>
   <si>
-    <t>D00397793</t>
-  </si>
-  <si>
     <t>2395-05-01 00:00:00</t>
   </si>
   <si>
@@ -487,34 +484,22 @@
     <t>7.0</t>
   </si>
   <si>
-    <t>792.0</t>
-  </si>
-  <si>
-    <t>46.0</t>
-  </si>
-  <si>
-    <t>487.0</t>
-  </si>
-  <si>
-    <t>1187-5</t>
-  </si>
-  <si>
-    <t>2006.0</t>
-  </si>
-  <si>
-    <t>AB44</t>
-  </si>
-  <si>
-    <t>31.0</t>
+    <t>797.0</t>
+  </si>
+  <si>
+    <t>775.0</t>
   </si>
   <si>
     <t>38.0</t>
   </si>
   <si>
-    <t>775.0</t>
-  </si>
-  <si>
-    <t>797.0</t>
+    <t>2545-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>2514-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>246.0</t>
   </si>
   <si>
     <t>1435-5</t>
@@ -523,7 +508,7 @@
     <t>2913.0</t>
   </si>
   <si>
-    <t>246.0</t>
+    <t>4041-05-01 00:00:00</t>
   </si>
   <si>
     <t>970.0</t>
@@ -532,18 +517,18 @@
     <t>08G</t>
   </si>
   <si>
-    <t>2545-05-01 00:00:00</t>
-  </si>
-  <si>
-    <t>2514-05-01 00:00:00</t>
-  </si>
-  <si>
-    <t>4041-05-01 00:00:00</t>
+    <t>B4H-011</t>
   </si>
   <si>
     <t>2004.0</t>
   </si>
   <si>
+    <t>5351.0</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
     <t>B4H-038</t>
   </si>
   <si>
@@ -553,51 +538,63 @@
     <t>47.0</t>
   </si>
   <si>
-    <t>B4H-011</t>
-  </si>
-  <si>
-    <t>32.0</t>
+    <t>480.0</t>
+  </si>
+  <si>
+    <t>B4H-051</t>
+  </si>
+  <si>
+    <t>25.0</t>
   </si>
   <si>
     <t>82.0</t>
   </si>
   <si>
-    <t>480.0</t>
-  </si>
-  <si>
-    <t>B4H-051</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
     <t>2890.0</t>
   </si>
   <si>
+    <t>278.0</t>
+  </si>
+  <si>
     <t>2305-05-01 00:00:00</t>
   </si>
   <si>
+    <t>B4H-040</t>
+  </si>
+  <si>
+    <t>272.0</t>
+  </si>
+  <si>
     <t>822-5</t>
   </si>
   <si>
+    <t>3481-05-01 00:00:00</t>
+  </si>
+  <si>
+    <t>687.0</t>
+  </si>
+  <si>
+    <t>AS41538</t>
+  </si>
+  <si>
     <t>4609-05-01 00:00:00</t>
   </si>
   <si>
     <t>3124-05-01 00:00:00</t>
   </si>
   <si>
+    <t>Z28L22A</t>
+  </si>
+  <si>
     <t>39.0</t>
   </si>
   <si>
-    <t>Z28L22A</t>
+    <t>92E</t>
   </si>
   <si>
     <t>29.0</t>
   </si>
   <si>
-    <t>92E</t>
-  </si>
-  <si>
     <t>UNK-01</t>
   </si>
   <si>
@@ -610,42 +607,39 @@
     <t>208-2724-2</t>
   </si>
   <si>
+    <t>3011713.0</t>
+  </si>
+  <si>
+    <t>2651023-23</t>
+  </si>
+  <si>
     <t>3044000.0</t>
   </si>
   <si>
-    <t>3011713.0</t>
-  </si>
-  <si>
-    <t>2651023-23</t>
-  </si>
-  <si>
     <t>3026812.0</t>
   </si>
   <si>
     <t>3013411.0</t>
   </si>
   <si>
-    <t>HSIPT6A-114A</t>
+    <t>HSI PT6A-114A</t>
   </si>
   <si>
     <t>3013111.0</t>
   </si>
   <si>
+    <t>3027798.0</t>
+  </si>
+  <si>
     <t>3013712.0</t>
   </si>
   <si>
-    <t>3027798.0</t>
-  </si>
-  <si>
-    <t>200SGL153Q</t>
+    <t>023694-000</t>
   </si>
   <si>
     <t>30994-001</t>
   </si>
   <si>
-    <t>023694-000</t>
-  </si>
-  <si>
     <t>2651023-19</t>
   </si>
   <si>
@@ -658,16 +652,19 @@
     <t>2651022-20-1</t>
   </si>
   <si>
+    <t>3049038-03</t>
+  </si>
+  <si>
+    <t>2651022-15</t>
+  </si>
+  <si>
+    <t>200SGL119Q</t>
+  </si>
+  <si>
     <t>540-1407-4</t>
   </si>
   <si>
-    <t>2651022-15</t>
-  </si>
-  <si>
-    <t>200SGL119Q</t>
-  </si>
-  <si>
-    <t>3049038-03</t>
+    <t>3121248-03</t>
   </si>
   <si>
     <t>5934PAM-3</t>
@@ -688,18 +685,18 @@
     <t>C482001-0402</t>
   </si>
   <si>
+    <t>3244809-4</t>
+  </si>
+  <si>
     <t>P7036368-01</t>
   </si>
   <si>
+    <t>RT-A1200</t>
+  </si>
+  <si>
     <t>DCN3-4120</t>
   </si>
   <si>
-    <t>RT-A1200</t>
-  </si>
-  <si>
-    <t>3244809-4</t>
-  </si>
-  <si>
     <t>LRU-1/P</t>
   </si>
   <si>
@@ -733,6 +730,12 @@
     <t>2622311-16</t>
   </si>
   <si>
+    <t>2641011-1</t>
+  </si>
+  <si>
+    <t>2613440-1</t>
+  </si>
+  <si>
     <t>2643062-1</t>
   </si>
   <si>
@@ -748,21 +751,21 @@
     <t>7EK50</t>
   </si>
   <si>
+    <t>F6177</t>
+  </si>
+  <si>
+    <t>74025.0</t>
+  </si>
+  <si>
+    <t>59875.0</t>
+  </si>
+  <si>
+    <t>66503.0</t>
+  </si>
+  <si>
     <t>95270.0</t>
   </si>
   <si>
-    <t>74025.0</t>
-  </si>
-  <si>
-    <t>F6177</t>
-  </si>
-  <si>
-    <t>59875.0</t>
-  </si>
-  <si>
-    <t>66503.0</t>
-  </si>
-  <si>
     <t>077L2</t>
   </si>
   <si>
@@ -781,15 +784,15 @@
     <t>18560.0</t>
   </si>
   <si>
+    <t>7213.0</t>
+  </si>
+  <si>
+    <t>1LGE7</t>
+  </si>
+  <si>
     <t>002FK</t>
   </si>
   <si>
-    <t>1LGE7</t>
-  </si>
-  <si>
-    <t>7213.0</t>
-  </si>
-  <si>
     <t>80049.0</t>
   </si>
   <si>
@@ -808,49 +811,49 @@
     <t>71513.0</t>
   </si>
   <si>
-    <t>1ETA</t>
-  </si>
-  <si>
-    <t>7ETA</t>
+    <t>7 ETA</t>
   </si>
   <si>
     <t>PAMALS</t>
   </si>
   <si>
-    <t>1/5GAV</t>
-  </si>
-  <si>
-    <t>2ETA</t>
-  </si>
-  <si>
-    <t>5ETA</t>
+    <t>1/5 GAV</t>
+  </si>
+  <si>
+    <t>2 ETA</t>
+  </si>
+  <si>
+    <t>5 ETA</t>
+  </si>
+  <si>
+    <t>1 ETA</t>
   </si>
   <si>
     <t>CLA</t>
   </si>
   <si>
-    <t>DACTAII</t>
-  </si>
-  <si>
-    <t>6ETA</t>
-  </si>
-  <si>
-    <t>1/15GAV</t>
+    <t>6 ETA</t>
+  </si>
+  <si>
+    <t>1/15 GAV</t>
+  </si>
+  <si>
+    <t>DACTA II</t>
+  </si>
+  <si>
+    <t>TBO</t>
+  </si>
+  <si>
+    <t>IC</t>
+  </si>
+  <si>
+    <t>100H</t>
   </si>
   <si>
     <t>MOT18A6</t>
   </si>
   <si>
-    <t>TBO</t>
-  </si>
-  <si>
-    <t>IC</t>
-  </si>
-  <si>
-    <t>100H</t>
-  </si>
-  <si>
-    <t>REV.GERAL</t>
+    <t>REV. GERAL</t>
   </si>
   <si>
     <t>REVG</t>
@@ -862,58 +865,49 @@
     <t>MOT1M12</t>
   </si>
   <si>
+    <t>200H</t>
+  </si>
+  <si>
+    <t>3000H</t>
+  </si>
+  <si>
+    <t>2800H</t>
+  </si>
+  <si>
+    <t>3400H</t>
+  </si>
+  <si>
+    <t>3300H</t>
+  </si>
+  <si>
+    <t>HSI</t>
+  </si>
+  <si>
+    <t>400H</t>
+  </si>
+  <si>
+    <t>MOT2M6</t>
+  </si>
+  <si>
+    <t>INSPC</t>
+  </si>
+  <si>
+    <t>CRI.</t>
+  </si>
+  <si>
+    <t>REV 5000</t>
+  </si>
+  <si>
+    <t>CRI</t>
+  </si>
+  <si>
     <t>TEC</t>
   </si>
   <si>
-    <t>3900H</t>
-  </si>
-  <si>
-    <t>MOT2M6</t>
-  </si>
-  <si>
-    <t>200H</t>
-  </si>
-  <si>
-    <t>3000H</t>
-  </si>
-  <si>
-    <t>300H</t>
-  </si>
-  <si>
-    <t>700H</t>
-  </si>
-  <si>
-    <t>400H</t>
-  </si>
-  <si>
-    <t>2800H</t>
-  </si>
-  <si>
-    <t>3300H</t>
-  </si>
-  <si>
-    <t>HSI</t>
-  </si>
-  <si>
-    <t>3400H</t>
-  </si>
-  <si>
-    <t>CRI.</t>
-  </si>
-  <si>
-    <t>REV5000</t>
-  </si>
-  <si>
-    <t>INSPC</t>
-  </si>
-  <si>
-    <t>CRI</t>
-  </si>
-  <si>
     <t>TLV</t>
   </si>
   <si>
-    <t>CRI12M</t>
+    <t>CRI 12M</t>
   </si>
   <si>
     <t>1.0</t>
@@ -922,16 +916,16 @@
     <t>12M</t>
   </si>
   <si>
-    <t>TROCAFILT</t>
+    <t>TROCA FILT</t>
+  </si>
+  <si>
+    <t>CRI (12M)</t>
   </si>
   <si>
     <t>MONT</t>
   </si>
   <si>
-    <t>CRI(12M)</t>
-  </si>
-  <si>
-    <t>INSPCRIT</t>
+    <t>INSP CRIT</t>
   </si>
   <si>
     <t>PESAGEM</t>
@@ -955,82 +949,67 @@
     <t>Pouso</t>
   </si>
   <si>
-    <t>-317m</t>
-  </si>
-  <si>
-    <t>-164m</t>
-  </si>
-  <si>
-    <t>-27m</t>
-  </si>
-  <si>
-    <t>-25m</t>
-  </si>
-  <si>
-    <t>-23m</t>
-  </si>
-  <si>
-    <t>-21m</t>
-  </si>
-  <si>
-    <t>-7m</t>
-  </si>
-  <si>
-    <t>-3m</t>
-  </si>
-  <si>
-    <t>-2m</t>
-  </si>
-  <si>
-    <t>2m</t>
-  </si>
-  <si>
-    <t>3m</t>
-  </si>
-  <si>
-    <t>4m</t>
-  </si>
-  <si>
-    <t>5m</t>
-  </si>
-  <si>
-    <t>6m</t>
-  </si>
-  <si>
-    <t>7m</t>
-  </si>
-  <si>
-    <t>8m</t>
-  </si>
-  <si>
-    <t>9m</t>
-  </si>
-  <si>
-    <t>10m</t>
-  </si>
-  <si>
-    <t>11m</t>
-  </si>
-  <si>
-    <t>-14d</t>
-  </si>
-  <si>
-    <t>1d</t>
-  </si>
-  <si>
-    <t>14d</t>
-  </si>
-  <si>
-    <t>23d</t>
-  </si>
-  <si>
-    <t>24d</t>
-  </si>
-  <si>
-    <t>1me23d</t>
-  </si>
-  <si>
-    <t>1me25d</t>
+    <t>-318 m</t>
+  </si>
+  <si>
+    <t>-165 m</t>
+  </si>
+  <si>
+    <t>-28 m</t>
+  </si>
+  <si>
+    <t>-26 m</t>
+  </si>
+  <si>
+    <t>-24 m</t>
+  </si>
+  <si>
+    <t>-22 m</t>
+  </si>
+  <si>
+    <t>-8 m</t>
+  </si>
+  <si>
+    <t>1 m</t>
+  </si>
+  <si>
+    <t>2 m</t>
+  </si>
+  <si>
+    <t>3 m</t>
+  </si>
+  <si>
+    <t>4 m</t>
+  </si>
+  <si>
+    <t>5 m</t>
+  </si>
+  <si>
+    <t>6 m</t>
+  </si>
+  <si>
+    <t>7 m</t>
+  </si>
+  <si>
+    <t>8 m</t>
+  </si>
+  <si>
+    <t>9 m</t>
+  </si>
+  <si>
+    <t>10 m</t>
+  </si>
+  <si>
+    <t>11 m</t>
+  </si>
+  <si>
+    <t>-27 d</t>
+  </si>
+  <si>
+    <t>-14 d</t>
+  </si>
+  <si>
+    <t>24 d</t>
   </si>
 </sst>
 </file>
@@ -1409,28 +1388,28 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H2">
-        <v>-4402.8</v>
+        <v>-4300.3</v>
       </c>
       <c r="J2" s="1">
-        <v>41388</v>
+        <v>39285</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
@@ -1441,28 +1420,28 @@
         <v>12</v>
       </c>
       <c r="B3">
-        <v>2740</v>
+        <v>2730</v>
       </c>
       <c r="C3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H3">
-        <v>-4254.8</v>
+        <v>-2354.2</v>
       </c>
       <c r="J3" s="1">
-        <v>39285</v>
+        <v>40669</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
@@ -1473,10 +1452,10 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>2730</v>
+        <v>2704</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D4" t="s">
         <v>243</v>
@@ -1485,13 +1464,13 @@
         <v>266</v>
       </c>
       <c r="F4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H4">
-        <v>-2354.2</v>
+        <v>-910.7</v>
       </c>
       <c r="J4" s="1">
         <v>40669</v>
@@ -1508,25 +1487,25 @@
         <v>2704</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E5" t="s">
         <v>266</v>
       </c>
       <c r="F5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H5">
-        <v>-896.8</v>
+        <v>-868</v>
       </c>
       <c r="J5" s="1">
-        <v>40669</v>
+        <v>44884</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1537,28 +1516,28 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>2704</v>
+        <v>2708</v>
       </c>
       <c r="C6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H6">
-        <v>-854.1</v>
+        <v>-483.8</v>
       </c>
       <c r="J6" s="1">
-        <v>44884</v>
+        <v>43855</v>
       </c>
       <c r="K6" t="b">
         <v>1</v>
@@ -1569,28 +1548,28 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>2708</v>
+        <v>2740</v>
       </c>
       <c r="C7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F7" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H7">
-        <v>-413.2</v>
+        <v>-417</v>
       </c>
       <c r="J7" s="1">
-        <v>43855</v>
+        <v>46014</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
@@ -1598,31 +1577,31 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>2732</v>
+        <v>2740</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
         <v>243</v>
       </c>
       <c r="E8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H8">
-        <v>-391.8</v>
+        <v>-414.2</v>
       </c>
       <c r="J8" s="1">
-        <v>42769</v>
+        <v>46014</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1630,31 +1609,31 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>2740</v>
+        <v>2732</v>
       </c>
       <c r="C9" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F9" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H9">
-        <v>-371.5</v>
+        <v>-391.8</v>
       </c>
       <c r="J9" s="1">
-        <v>46014</v>
+        <v>42769</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1665,28 +1644,28 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>2740</v>
+        <v>2719</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H10">
-        <v>-368.8</v>
+        <v>-391.6</v>
       </c>
       <c r="J10" s="1">
-        <v>46014</v>
+        <v>45804</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1694,7 +1673,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>2719</v>
@@ -1703,19 +1682,19 @@
         <v>202</v>
       </c>
       <c r="D11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
         <v>268</v>
       </c>
       <c r="F11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G11" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H11">
-        <v>-359</v>
+        <v>-391.6</v>
       </c>
       <c r="J11" s="1">
         <v>45804</v>
@@ -1729,28 +1708,28 @@
         <v>19</v>
       </c>
       <c r="B12">
-        <v>2719</v>
+        <v>2743</v>
       </c>
       <c r="C12" t="s">
         <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H12">
-        <v>-359</v>
+        <v>-372.9</v>
       </c>
       <c r="J12" s="1">
-        <v>45804</v>
+        <v>42821</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1767,22 +1746,22 @@
         <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E13" t="s">
         <v>269</v>
       </c>
       <c r="F13" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G13" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H13">
-        <v>-351</v>
+        <v>-372.9</v>
       </c>
       <c r="J13" s="1">
-        <v>42821</v>
+        <v>46014</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -1796,10 +1775,10 @@
         <v>2743</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E14" t="s">
         <v>269</v>
@@ -1808,10 +1787,10 @@
         <v>275</v>
       </c>
       <c r="G14" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H14">
-        <v>-351</v>
+        <v>-372.9</v>
       </c>
       <c r="J14" s="1">
         <v>46014</v>
@@ -1828,10 +1807,10 @@
         <v>2743</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E15" t="s">
         <v>269</v>
@@ -1840,10 +1819,10 @@
         <v>275</v>
       </c>
       <c r="G15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H15">
-        <v>-351</v>
+        <v>-372.9</v>
       </c>
       <c r="J15" s="1">
         <v>46014</v>
@@ -1860,10 +1839,10 @@
         <v>2743</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E16" t="s">
         <v>269</v>
@@ -1872,13 +1851,13 @@
         <v>275</v>
       </c>
       <c r="G16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H16">
-        <v>-351</v>
+        <v>-367.8</v>
       </c>
       <c r="J16" s="1">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -1892,22 +1871,22 @@
         <v>2743</v>
       </c>
       <c r="C17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D17" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
         <v>269</v>
       </c>
       <c r="F17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G17" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H17">
-        <v>-345.8</v>
+        <v>-367.8</v>
       </c>
       <c r="J17" s="1">
         <v>46017</v>
@@ -1921,28 +1900,28 @@
         <v>25</v>
       </c>
       <c r="B18">
-        <v>2743</v>
+        <v>2722</v>
       </c>
       <c r="C18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D18" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E18" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F18" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="G18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H18">
-        <v>-345.8</v>
+        <v>-347.2</v>
       </c>
       <c r="J18" s="1">
-        <v>46017</v>
+        <v>40979</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -1953,13 +1932,13 @@
         <v>26</v>
       </c>
       <c r="B19">
-        <v>2722</v>
+        <v>2719</v>
       </c>
       <c r="C19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E19" t="s">
         <v>268</v>
@@ -1968,13 +1947,13 @@
         <v>281</v>
       </c>
       <c r="G19" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H19">
-        <v>-264.2</v>
+        <v>-293.8</v>
       </c>
       <c r="J19" s="1">
-        <v>40979</v>
+        <v>45846</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -1988,19 +1967,19 @@
         <v>2733</v>
       </c>
       <c r="C20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F20" t="s">
         <v>277</v>
       </c>
       <c r="G20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H20">
         <v>-206.4</v>
@@ -2020,19 +1999,19 @@
         <v>2733</v>
       </c>
       <c r="C21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E21" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F21" t="s">
         <v>275</v>
       </c>
       <c r="G21" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H21">
         <v>-131.6</v>
@@ -2052,19 +2031,19 @@
         <v>2733</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E22" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F22" t="s">
         <v>275</v>
       </c>
       <c r="G22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H22">
         <v>-131.6</v>
@@ -2084,19 +2063,19 @@
         <v>2733</v>
       </c>
       <c r="C23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F23" t="s">
         <v>275</v>
       </c>
       <c r="G23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H23">
         <v>-131.6</v>
@@ -2116,19 +2095,19 @@
         <v>2733</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D24" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E24" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F24" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H24">
         <v>-131.6</v>
@@ -2148,19 +2127,19 @@
         <v>2733</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D25" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E25" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F25" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G25" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H25">
         <v>-131.6</v>
@@ -2177,28 +2156,28 @@
         <v>33</v>
       </c>
       <c r="B26">
-        <v>2743</v>
+        <v>2702</v>
       </c>
       <c r="C26" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F26" t="s">
         <v>282</v>
       </c>
       <c r="G26" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H26">
-        <v>-105</v>
+        <v>-98.3</v>
       </c>
       <c r="J26" s="1">
-        <v>46161</v>
+        <v>41204</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -2209,28 +2188,28 @@
         <v>34</v>
       </c>
       <c r="B27">
-        <v>2729</v>
+        <v>2739</v>
       </c>
       <c r="C27" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F27" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G27" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H27">
-        <v>-79.8</v>
+        <v>-47.2</v>
       </c>
       <c r="J27" s="1">
-        <v>43340</v>
+        <v>44011</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -2241,28 +2220,28 @@
         <v>35</v>
       </c>
       <c r="B28">
-        <v>2732</v>
+        <v>2702</v>
       </c>
       <c r="C28" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D28" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F28" t="s">
         <v>283</v>
       </c>
       <c r="G28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H28">
-        <v>-12.3</v>
+        <v>-22.3</v>
       </c>
       <c r="J28" s="1">
-        <v>46048</v>
+        <v>46226</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -2276,25 +2255,25 @@
         <v>2736</v>
       </c>
       <c r="C29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D29" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
         <v>265</v>
       </c>
       <c r="F29" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="G29" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J29" s="1">
-        <v>46211</v>
+        <v>46265</v>
       </c>
       <c r="K29" t="b">
         <v>0</v>
@@ -2305,28 +2284,28 @@
         <v>37</v>
       </c>
       <c r="B30">
-        <v>2733</v>
+        <v>2723</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D30" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G30" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H30">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J30" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
@@ -2337,28 +2316,28 @@
         <v>38</v>
       </c>
       <c r="B31">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="C31" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G31" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H31">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="J31" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
@@ -2369,28 +2348,28 @@
         <v>39</v>
       </c>
       <c r="B32">
-        <v>2723</v>
+        <v>2709</v>
       </c>
       <c r="C32" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E32" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G32" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H32">
-        <v>7.5</v>
+        <v>12.8</v>
       </c>
       <c r="J32" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
@@ -2401,28 +2380,28 @@
         <v>40</v>
       </c>
       <c r="B33">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E33" t="s">
         <v>265</v>
       </c>
       <c r="F33" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G33" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H33">
-        <v>10.7</v>
+        <v>14</v>
       </c>
       <c r="J33" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
@@ -2430,31 +2409,31 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34">
-        <v>2743</v>
+        <v>2736</v>
       </c>
       <c r="C34" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D34" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E34" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F34" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G34" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H34">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="J34" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
@@ -2462,31 +2441,31 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35">
-        <v>2742</v>
+        <v>2727</v>
       </c>
       <c r="C35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E35" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F35" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="G35" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H35">
-        <v>30.8</v>
+        <v>20.4</v>
       </c>
       <c r="J35" s="1">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
@@ -2494,31 +2473,31 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36">
-        <v>2731</v>
+        <v>2738</v>
       </c>
       <c r="C36" t="s">
         <v>198</v>
       </c>
       <c r="D36" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E36" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F36" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="G36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H36">
-        <v>37.1</v>
+        <v>21.2</v>
       </c>
       <c r="J36" s="1">
-        <v>46256</v>
+        <v>46265</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
@@ -2526,31 +2505,31 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>2721</v>
+        <v>2736</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D37" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E37" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F37" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G37" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H37">
-        <v>42.8</v>
+        <v>26.2</v>
       </c>
       <c r="J37" s="1">
-        <v>46276</v>
+        <v>46265</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
@@ -2558,31 +2537,31 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38">
-        <v>2722</v>
+        <v>2704</v>
       </c>
       <c r="C38" t="s">
         <v>208</v>
       </c>
       <c r="D38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E38" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F38" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G38" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H38">
-        <v>45.2</v>
+        <v>33.6</v>
       </c>
       <c r="J38" s="1">
-        <v>46234</v>
+        <v>46364</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -2590,31 +2569,31 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39">
-        <v>2709</v>
+        <v>2740</v>
       </c>
       <c r="C39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D39" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E39" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F39" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G39" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H39">
-        <v>46</v>
+        <v>42.2</v>
       </c>
       <c r="J39" s="1">
-        <v>46251</v>
+        <v>46269</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
@@ -2622,31 +2601,31 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40">
-        <v>2704</v>
+        <v>2721</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D40" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E40" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G40" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H40">
-        <v>47.5</v>
+        <v>42.8</v>
       </c>
       <c r="J40" s="1">
-        <v>46456</v>
+        <v>46291</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
@@ -2654,31 +2633,31 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41">
-        <v>2741</v>
+        <v>2704</v>
       </c>
       <c r="C41" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F41" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="G41" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H41">
-        <v>57.2</v>
+        <v>45.7</v>
       </c>
       <c r="J41" s="1">
-        <v>46246</v>
+        <v>46395</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
@@ -2686,31 +2665,31 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42">
-        <v>2704</v>
+        <v>2720</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D42" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="F42" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G42" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H42">
-        <v>59.6</v>
+        <v>47.2</v>
       </c>
       <c r="J42" s="1">
-        <v>46487</v>
+        <v>46280</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
@@ -2718,31 +2697,31 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43">
         <v>2720</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E43" t="s">
         <v>272</v>
       </c>
       <c r="F43" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="G43" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H43">
-        <v>75.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="J43" s="1">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
@@ -2750,31 +2729,31 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44">
-        <v>2720</v>
+        <v>2740</v>
       </c>
       <c r="C44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E44" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F44" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G44" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H44">
-        <v>76.8</v>
+        <v>60</v>
       </c>
       <c r="J44" s="1">
-        <v>46285</v>
+        <v>46281</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
@@ -2782,31 +2761,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B45">
-        <v>2704</v>
+        <v>2743</v>
       </c>
       <c r="C45" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F45" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="G45" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H45">
-        <v>83.2</v>
+        <v>62.6</v>
       </c>
       <c r="J45" s="1">
-        <v>46547</v>
+        <v>46265</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
@@ -2814,7 +2793,7 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>2743</v>
@@ -2823,22 +2802,22 @@
         <v>202</v>
       </c>
       <c r="D46" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E46" t="s">
         <v>269</v>
       </c>
       <c r="F46" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G46" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H46">
-        <v>84.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J46" s="1">
-        <v>46240</v>
+        <v>46265</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
@@ -2846,31 +2825,31 @@
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B47">
-        <v>2740</v>
+        <v>2722</v>
       </c>
       <c r="C47" t="s">
         <v>198</v>
       </c>
       <c r="D47" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E47" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F47" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H47">
-        <v>85.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="J47" s="1">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="K47" t="b">
         <v>0</v>
@@ -2878,31 +2857,31 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48">
-        <v>2743</v>
+        <v>2737</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F48" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H48">
-        <v>86.5</v>
+        <v>68.3</v>
       </c>
       <c r="J48" s="1">
-        <v>46241</v>
+        <v>46278</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
@@ -2910,31 +2889,31 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B49">
-        <v>2743</v>
+        <v>2704</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D49" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E49" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F49" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G49" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H49">
-        <v>91.7</v>
+        <v>69.2</v>
       </c>
       <c r="J49" s="1">
-        <v>46243</v>
+        <v>46453</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
@@ -2942,16 +2921,16 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>2743</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D50" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E50" t="s">
         <v>269</v>
@@ -2960,13 +2939,13 @@
         <v>276</v>
       </c>
       <c r="G50" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H50">
-        <v>91.7</v>
+        <v>69.8</v>
       </c>
       <c r="J50" s="1">
-        <v>46243</v>
+        <v>46265</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
@@ -2974,31 +2953,31 @@
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B51">
-        <v>2738</v>
+        <v>2743</v>
       </c>
       <c r="C51" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E51" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H51">
-        <v>91.7</v>
+        <v>69.8</v>
       </c>
       <c r="J51" s="1">
-        <v>46250</v>
+        <v>46265</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
@@ -3006,31 +2985,31 @@
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B52">
-        <v>2738</v>
+        <v>2742</v>
       </c>
       <c r="C52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D52" t="s">
         <v>243</v>
       </c>
       <c r="E52" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F52" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="G52" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H52">
-        <v>98.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="J52" s="1">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
@@ -3038,31 +3017,31 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B53">
-        <v>2740</v>
+        <v>2742</v>
       </c>
       <c r="C53" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D53" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E53" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F53" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G53" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H53">
-        <v>105.5</v>
+        <v>72.2</v>
       </c>
       <c r="J53" s="1">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
@@ -3070,31 +3049,31 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B54">
-        <v>2736</v>
+        <v>2743</v>
       </c>
       <c r="C54" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D54" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E54" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G54" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H54">
-        <v>105.6</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J54" s="1">
-        <v>46361</v>
+        <v>46265</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
@@ -3102,31 +3081,31 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B55">
-        <v>2736</v>
+        <v>2704</v>
       </c>
       <c r="C55" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D55" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E55" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F55" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="G55" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H55">
-        <v>105.7</v>
+        <v>82.8</v>
       </c>
       <c r="J55" s="1">
-        <v>46362</v>
+        <v>46487</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
@@ -3134,31 +3113,31 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B56">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D56" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E56" t="s">
         <v>265</v>
       </c>
       <c r="F56" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="G56" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H56">
-        <v>110.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="J56" s="1">
-        <v>46275</v>
+        <v>46285</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
@@ -3166,31 +3145,31 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B57">
-        <v>2736</v>
+        <v>2704</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D57" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G57" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H57">
-        <v>113.2</v>
+        <v>84.8</v>
       </c>
       <c r="J57" s="1">
-        <v>46377</v>
+        <v>46492</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
@@ -3198,31 +3177,31 @@
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B58">
-        <v>2732</v>
+        <v>2741</v>
       </c>
       <c r="C58" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D58" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E58" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F58" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G58" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H58">
-        <v>128.8</v>
+        <v>104.9</v>
       </c>
       <c r="J58" s="1">
-        <v>46434</v>
+        <v>46297</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
@@ -3230,31 +3209,31 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59">
-        <v>2732</v>
+        <v>2719</v>
       </c>
       <c r="C59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D59" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E59" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F59" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G59" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H59">
-        <v>128.8</v>
+        <v>107.6</v>
       </c>
       <c r="J59" s="1">
-        <v>46434</v>
+        <v>46283</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
@@ -3262,31 +3241,31 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60">
-        <v>2732</v>
+        <v>2741</v>
       </c>
       <c r="C60" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D60" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E60" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F60" t="s">
         <v>275</v>
       </c>
       <c r="G60" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H60">
-        <v>128.8</v>
+        <v>111.9</v>
       </c>
       <c r="J60" s="1">
-        <v>46434</v>
+        <v>46300</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
@@ -3294,31 +3273,31 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61">
-        <v>2732</v>
+        <v>2741</v>
       </c>
       <c r="C61" t="s">
         <v>205</v>
       </c>
       <c r="D61" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F61" t="s">
         <v>275</v>
       </c>
       <c r="G61" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H61">
-        <v>128.8</v>
+        <v>111.9</v>
       </c>
       <c r="J61" s="1">
-        <v>46434</v>
+        <v>46300</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
@@ -3326,31 +3305,31 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B62">
-        <v>2732</v>
+        <v>2741</v>
       </c>
       <c r="C62" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D62" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E62" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G62" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H62">
-        <v>128.8</v>
+        <v>111.9</v>
       </c>
       <c r="J62" s="1">
-        <v>46434</v>
+        <v>46300</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
@@ -3358,31 +3337,31 @@
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="C63" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D63" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E63" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F63" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G63" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H63">
-        <v>135</v>
+        <v>111.9</v>
       </c>
       <c r="J63" s="1">
-        <v>46280</v>
+        <v>46300</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
@@ -3390,31 +3369,31 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64">
-        <v>2722</v>
+        <v>2741</v>
       </c>
       <c r="C64" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D64" t="s">
         <v>243</v>
       </c>
       <c r="E64" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G64" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H64">
-        <v>150.6</v>
+        <v>111.9</v>
       </c>
       <c r="J64" s="1">
-        <v>46271</v>
+        <v>46300</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
@@ -3422,10 +3401,10 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B65">
-        <v>2709</v>
+        <v>2738</v>
       </c>
       <c r="C65" t="s">
         <v>214</v>
@@ -3434,19 +3413,19 @@
         <v>249</v>
       </c>
       <c r="E65" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F65" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="G65" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H65">
-        <v>174.2</v>
+        <v>128.8</v>
       </c>
       <c r="J65" s="1">
-        <v>46363</v>
+        <v>46308</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
@@ -3454,31 +3433,31 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66">
         <v>2740</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E66" t="s">
         <v>265</v>
       </c>
       <c r="F66" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G66" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H66">
-        <v>176.6</v>
+        <v>131.1</v>
       </c>
       <c r="J66" s="1">
-        <v>46334</v>
+        <v>46336</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
@@ -3486,31 +3465,31 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B67">
-        <v>2721</v>
+        <v>2740</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D67" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E67" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F67" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="G67" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H67">
-        <v>177.4</v>
+        <v>138.4</v>
       </c>
       <c r="J67" s="1">
-        <v>46407</v>
+        <v>46343</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
@@ -3518,31 +3497,31 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68">
-        <v>2740</v>
+        <v>2709</v>
       </c>
       <c r="C68" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D68" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E68" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F68" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="G68" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H68">
-        <v>183.9</v>
+        <v>141</v>
       </c>
       <c r="J68" s="1">
-        <v>46341</v>
+        <v>46350</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
@@ -3550,31 +3529,31 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B69">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="C69" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D69" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E69" t="s">
         <v>265</v>
       </c>
       <c r="F69" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="G69" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H69">
-        <v>191.7</v>
+        <v>162</v>
       </c>
       <c r="J69" s="1">
-        <v>46300</v>
+        <v>46391</v>
       </c>
       <c r="K69" t="b">
         <v>0</v>
@@ -3582,31 +3561,31 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B70">
-        <v>2723</v>
+        <v>2737</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E70" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F70" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G70" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H70">
-        <v>200</v>
+        <v>167.2</v>
       </c>
       <c r="J70" s="1">
-        <v>46336</v>
+        <v>46330</v>
       </c>
       <c r="K70" t="b">
         <v>0</v>
@@ -3614,31 +3593,31 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71">
-        <v>2741</v>
+        <v>2721</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E71" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F71" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G71" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H71">
-        <v>201.1</v>
+        <v>177.4</v>
       </c>
       <c r="J71" s="1">
-        <v>46319</v>
+        <v>46418</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
@@ -3646,31 +3625,31 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B72">
-        <v>2738</v>
+        <v>2723</v>
       </c>
       <c r="C72" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D72" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E72" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F72" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G72" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H72">
-        <v>206.5</v>
+        <v>200</v>
       </c>
       <c r="J72" s="1">
-        <v>46308</v>
+        <v>46356</v>
       </c>
       <c r="K72" t="b">
         <v>0</v>
@@ -3678,31 +3657,31 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B73">
-        <v>2740</v>
+        <v>2731</v>
       </c>
       <c r="C73" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D73" t="s">
         <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F73" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="G73" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H73">
-        <v>207.5</v>
+        <v>203.6</v>
       </c>
       <c r="J73" s="1">
-        <v>46390</v>
+        <v>46436</v>
       </c>
       <c r="K73" t="b">
         <v>0</v>
@@ -3710,31 +3689,31 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B74">
-        <v>2731</v>
+        <v>2736</v>
       </c>
       <c r="C74" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E74" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F74" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="G74" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H74">
-        <v>247</v>
+        <v>221.2</v>
       </c>
       <c r="J74" s="1">
-        <v>46443</v>
+        <v>46426</v>
       </c>
       <c r="K74" t="b">
         <v>0</v>
@@ -3742,31 +3721,31 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B75">
-        <v>2743</v>
+        <v>2739</v>
       </c>
       <c r="C75" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="D75" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E75" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F75" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G75" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H75">
-        <v>285.3</v>
+        <v>240.8</v>
       </c>
       <c r="J75" s="1">
-        <v>46304</v>
+        <v>46450</v>
       </c>
       <c r="K75" t="b">
         <v>0</v>
@@ -3774,31 +3753,31 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B76">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C76" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D76" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E76" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F76" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G76" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H76">
-        <v>290.8</v>
+        <v>245.8</v>
       </c>
       <c r="J76" s="1">
-        <v>46362</v>
+        <v>46452</v>
       </c>
       <c r="K76" t="b">
         <v>0</v>
@@ -3806,31 +3785,31 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B77">
-        <v>2739</v>
+        <v>2743</v>
       </c>
       <c r="C77" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D77" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="E77" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F77" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G77" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H77">
-        <v>295.2</v>
+        <v>263.4</v>
       </c>
       <c r="J77" s="1">
-        <v>46463</v>
+        <v>46322</v>
       </c>
       <c r="K77" t="b">
         <v>0</v>
@@ -3838,31 +3817,31 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B78">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="C78" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D78" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E78" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F78" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="G78" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H78">
-        <v>300.2</v>
+        <v>275.2</v>
       </c>
       <c r="J78" s="1">
-        <v>46466</v>
+        <v>46433</v>
       </c>
       <c r="K78" t="b">
         <v>0</v>
@@ -3870,31 +3849,31 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B79">
         <v>2706</v>
       </c>
       <c r="C79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E79" t="s">
         <v>266</v>
       </c>
       <c r="F79" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="G79" t="s">
+        <v>309</v>
+      </c>
+      <c r="H79">
+        <v>-9540</v>
+      </c>
+      <c r="I79" t="s">
         <v>311</v>
-      </c>
-      <c r="H79">
-        <v>-9510</v>
-      </c>
-      <c r="I79" t="s">
-        <v>313</v>
       </c>
       <c r="J79" s="1">
         <v>36557</v>
@@ -3905,31 +3884,31 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B80">
         <v>2740</v>
       </c>
       <c r="C80" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D80" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E80" t="s">
         <v>265</v>
       </c>
       <c r="F80" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G80" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H80">
-        <v>-4920</v>
+        <v>-4950</v>
       </c>
       <c r="I80" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J80" s="1">
         <v>41275</v>
@@ -3940,31 +3919,31 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B81">
         <v>2724</v>
       </c>
       <c r="C81" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D81" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E81" t="s">
         <v>266</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G81" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H81">
-        <v>-810</v>
+        <v>-840</v>
       </c>
       <c r="I81" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J81" s="1">
         <v>45380</v>
@@ -3975,16 +3954,16 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B82">
         <v>2724</v>
       </c>
       <c r="C82" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D82" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E82" t="s">
         <v>266</v>
@@ -3993,13 +3972,13 @@
         <v>275</v>
       </c>
       <c r="G82" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H82">
-        <v>-750</v>
+        <v>-780</v>
       </c>
       <c r="I82" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J82" s="1">
         <v>45421</v>
@@ -4010,31 +3989,31 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B83">
         <v>2724</v>
       </c>
       <c r="C83" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D83" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E83" t="s">
         <v>266</v>
       </c>
       <c r="F83" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G83" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H83">
-        <v>-750</v>
+        <v>-780</v>
       </c>
       <c r="I83" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J83" s="1">
         <v>45428</v>
@@ -4045,31 +4024,31 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84">
         <v>2724</v>
       </c>
       <c r="C84" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D84" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E84" t="s">
         <v>266</v>
       </c>
       <c r="F84" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G84" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H84">
-        <v>-690</v>
+        <v>-720</v>
       </c>
       <c r="I84" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="J84" s="1">
         <v>45490</v>
@@ -4080,31 +4059,31 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B85">
         <v>2724</v>
       </c>
       <c r="C85" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E85" t="s">
         <v>266</v>
       </c>
       <c r="F85" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G85" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H85">
-        <v>-630</v>
+        <v>-660</v>
       </c>
       <c r="I85" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J85" s="1">
         <v>45566</v>
@@ -4115,31 +4094,31 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B86">
         <v>2730</v>
       </c>
       <c r="C86" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D86" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E86" t="s">
         <v>266</v>
       </c>
       <c r="F86" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G86" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H86">
-        <v>-210</v>
+        <v>-240</v>
       </c>
       <c r="I86" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="J86" s="1">
         <v>45986</v>
@@ -4150,104 +4129,104 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B87">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="C87" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D87" t="s">
         <v>253</v>
       </c>
       <c r="E87" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F87" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="G87" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H87">
-        <v>-90</v>
+        <v>30</v>
       </c>
       <c r="I87" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J87" s="1">
-        <v>46106</v>
+        <v>46284</v>
       </c>
       <c r="K87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B88">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C88" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D88" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E88" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F88" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G88" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H88">
-        <v>-60</v>
+        <v>60</v>
       </c>
       <c r="I88" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J88" s="1">
-        <v>46142</v>
+        <v>46305</v>
       </c>
       <c r="K88" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="C89" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="D89" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E89" t="s">
         <v>265</v>
       </c>
       <c r="F89" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G89" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H89">
         <v>60</v>
       </c>
       <c r="I89" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J89" s="1">
-        <v>46274</v>
+        <v>46310</v>
       </c>
       <c r="K89" t="b">
         <v>0</v>
@@ -4255,34 +4234,34 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90">
-        <v>2727</v>
+        <v>2739</v>
       </c>
       <c r="C90" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
         <v>256</v>
       </c>
       <c r="E90" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F90" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="G90" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H90">
         <v>60</v>
       </c>
       <c r="I90" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J90" s="1">
-        <v>46276</v>
+        <v>46317</v>
       </c>
       <c r="K90" t="b">
         <v>0</v>
@@ -4290,34 +4269,34 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B91">
-        <v>2740</v>
+        <v>2731</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D91" t="s">
         <v>252</v>
       </c>
       <c r="E91" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F91" t="s">
         <v>298</v>
       </c>
       <c r="G91" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H91">
         <v>60</v>
       </c>
       <c r="I91" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J91" s="1">
-        <v>46284</v>
+        <v>46319</v>
       </c>
       <c r="K91" t="b">
         <v>0</v>
@@ -4325,34 +4304,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B92">
-        <v>2739</v>
+        <v>2727</v>
       </c>
       <c r="C92" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E92" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F92" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="G92" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H92">
         <v>90</v>
       </c>
       <c r="I92" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J92" s="1">
-        <v>46317</v>
+        <v>46333</v>
       </c>
       <c r="K92" t="b">
         <v>0</v>
@@ -4360,34 +4339,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B93">
-        <v>2731</v>
+        <v>2721</v>
       </c>
       <c r="C93" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D93" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E93" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F93" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G93" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H93">
         <v>90</v>
       </c>
       <c r="I93" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J93" s="1">
-        <v>46319</v>
+        <v>46338</v>
       </c>
       <c r="K93" t="b">
         <v>0</v>
@@ -4395,34 +4374,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B94">
-        <v>2727</v>
+        <v>2721</v>
       </c>
       <c r="C94" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E94" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F94" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G94" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H94">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I94" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J94" s="1">
-        <v>46333</v>
+        <v>46338</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
@@ -4430,34 +4409,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B95">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="C95" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D95" t="s">
         <v>254</v>
       </c>
       <c r="E95" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F95" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="G95" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H95">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I95" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J95" s="1">
-        <v>46338</v>
+        <v>46341</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
@@ -4465,34 +4444,34 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96">
-        <v>2721</v>
+        <v>2703</v>
       </c>
       <c r="C96" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D96" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E96" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="F96" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G96" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H96">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I96" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J96" s="1">
-        <v>46338</v>
+        <v>46344</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
@@ -4500,34 +4479,34 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B97">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="C97" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="D97" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E97" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F97" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="G97" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H97">
         <v>120</v>
       </c>
       <c r="I97" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J97" s="1">
-        <v>46341</v>
+        <v>46360</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
@@ -4535,34 +4514,34 @@
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B98">
-        <v>2703</v>
+        <v>2728</v>
       </c>
       <c r="C98" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D98" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E98" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F98" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G98" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H98">
         <v>120</v>
       </c>
       <c r="I98" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J98" s="1">
-        <v>46344</v>
+        <v>46360</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
@@ -4570,34 +4549,34 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B99">
-        <v>2702</v>
+        <v>2734</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="D99" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="E99" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F99" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G99" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H99">
         <v>120</v>
       </c>
       <c r="I99" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J99" s="1">
-        <v>46354</v>
+        <v>46367</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
@@ -4605,34 +4584,34 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B100">
-        <v>2721</v>
+        <v>2732</v>
       </c>
       <c r="C100" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D100" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="E100" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F100" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="G100" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H100">
         <v>120</v>
       </c>
       <c r="I100" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J100" s="1">
-        <v>46360</v>
+        <v>46375</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
@@ -4640,34 +4619,34 @@
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B101">
-        <v>2728</v>
+        <v>2730</v>
       </c>
       <c r="C101" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D101" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E101" t="s">
         <v>266</v>
       </c>
       <c r="F101" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G101" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H101">
         <v>120</v>
       </c>
       <c r="I101" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J101" s="1">
-        <v>46360</v>
+        <v>46387</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
@@ -4675,34 +4654,34 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B102">
-        <v>2737</v>
+        <v>2732</v>
       </c>
       <c r="C102" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D102" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E102" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F102" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G102" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H102">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I102" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J102" s="1">
-        <v>46366</v>
+        <v>46387</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
@@ -4710,34 +4689,34 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B103">
-        <v>2732</v>
+        <v>2736</v>
       </c>
       <c r="C103" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D103" t="s">
         <v>258</v>
       </c>
       <c r="E103" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F103" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="G103" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H103">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I103" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J103" s="1">
-        <v>46375</v>
+        <v>46387</v>
       </c>
       <c r="K103" t="b">
         <v>0</v>
@@ -4745,31 +4724,31 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B104">
         <v>2728</v>
       </c>
       <c r="C104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D104" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E104" t="s">
         <v>266</v>
       </c>
       <c r="F104" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G104" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H104">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I104" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J104" s="1">
         <v>46388</v>
@@ -4780,31 +4759,31 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105">
         <v>2704</v>
       </c>
       <c r="C105" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D105" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E105" t="s">
         <v>266</v>
       </c>
       <c r="F105" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G105" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H105">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I105" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J105" s="1">
         <v>46401</v>
@@ -4815,31 +4794,31 @@
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B106">
         <v>2704</v>
       </c>
       <c r="C106" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D106" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E106" t="s">
         <v>266</v>
       </c>
       <c r="F106" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G106" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H106">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I106" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J106" s="1">
         <v>46401</v>
@@ -4850,31 +4829,31 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B107">
         <v>2709</v>
       </c>
       <c r="C107" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E107" t="s">
         <v>272</v>
       </c>
       <c r="F107" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G107" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H107">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I107" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J107" s="1">
         <v>46401</v>
@@ -4885,34 +4864,34 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B108">
-        <v>2704</v>
+        <v>2741</v>
       </c>
       <c r="C108" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D108" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E108" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F108" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="G108" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H108">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I108" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="J108" s="1">
-        <v>46413</v>
+        <v>46412</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
@@ -4920,34 +4899,34 @@
     </row>
     <row r="109" spans="1:11">
       <c r="A109" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B109">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C109" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D109" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E109" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F109" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G109" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H109">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I109" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J109" s="1">
-        <v>46424</v>
+        <v>46412</v>
       </c>
       <c r="K109" t="b">
         <v>0</v>
@@ -4955,34 +4934,34 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B110">
-        <v>2736</v>
+        <v>2740</v>
       </c>
       <c r="C110" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D110" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E110" t="s">
         <v>265</v>
       </c>
       <c r="F110" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G110" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H110">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="I110" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="J110" s="1">
-        <v>46427</v>
+        <v>46412</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
@@ -4990,34 +4969,34 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B111">
-        <v>2739</v>
+        <v>2733</v>
       </c>
       <c r="C111" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D111" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E111" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F111" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G111" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H111">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I111" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J111" s="1">
-        <v>46437</v>
+        <v>46424</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
@@ -5025,34 +5004,34 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B112">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="C112" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D112" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E112" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F112" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G112" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H112">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="I112" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J112" s="1">
-        <v>46451</v>
+        <v>46437</v>
       </c>
       <c r="K112" t="b">
         <v>0</v>
@@ -5060,34 +5039,34 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B113">
-        <v>2738</v>
+        <v>2719</v>
       </c>
       <c r="C113" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D113" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E113" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F113" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G113" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H113">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I113" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="J113" s="1">
-        <v>46455</v>
+        <v>46451</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
@@ -5095,34 +5074,34 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B114">
-        <v>2720</v>
+        <v>2741</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E114" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F114" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G114" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H114">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I114" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="J114" s="1">
-        <v>46457</v>
+        <v>46451</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
@@ -5130,34 +5109,34 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B115">
-        <v>2708</v>
+        <v>2738</v>
       </c>
       <c r="C115" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D115" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E115" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F115" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G115" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H115">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I115" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J115" s="1">
-        <v>46462</v>
+        <v>46455</v>
       </c>
       <c r="K115" t="b">
         <v>0</v>
@@ -5165,34 +5144,34 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B116">
-        <v>2734</v>
+        <v>2708</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D116" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E116" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F116" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G116" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H116">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I116" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J116" s="1">
-        <v>46464</v>
+        <v>46456</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
@@ -5200,34 +5179,34 @@
     </row>
     <row r="117" spans="1:11">
       <c r="A117" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B117">
-        <v>2723</v>
+        <v>2720</v>
       </c>
       <c r="C117" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D117" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E117" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F117" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="G117" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H117">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="I117" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J117" s="1">
-        <v>46470</v>
+        <v>46457</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
@@ -5235,34 +5214,34 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B118">
-        <v>2728</v>
+        <v>2734</v>
       </c>
       <c r="C118" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D118" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E118" t="s">
         <v>266</v>
       </c>
       <c r="F118" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G118" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H118">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="I118" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="J118" s="1">
-        <v>46485</v>
+        <v>46464</v>
       </c>
       <c r="K118" t="b">
         <v>0</v>
@@ -5270,34 +5249,34 @@
     </row>
     <row r="119" spans="1:11">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119">
-        <v>2741</v>
+        <v>2723</v>
       </c>
       <c r="C119" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D119" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E119" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="F119" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="G119" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H119">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="I119" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="J119" s="1">
-        <v>46499</v>
+        <v>46470</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
@@ -5305,34 +5284,34 @@
     </row>
     <row r="120" spans="1:11">
       <c r="A120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B120">
-        <v>2722</v>
+        <v>2728</v>
       </c>
       <c r="C120" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D120" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E120" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F120" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G120" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H120">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I120" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J120" s="1">
-        <v>46504</v>
+        <v>46485</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
@@ -5340,34 +5319,34 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B121">
-        <v>2737</v>
+        <v>2741</v>
       </c>
       <c r="C121" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D121" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E121" t="s">
         <v>265</v>
       </c>
       <c r="F121" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="G121" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H121">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I121" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J121" s="1">
-        <v>46504</v>
+        <v>46499</v>
       </c>
       <c r="K121" t="b">
         <v>0</v>
@@ -5375,34 +5354,34 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B122">
-        <v>2743</v>
+        <v>2722</v>
       </c>
       <c r="C122" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D122" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E122" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F122" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="G122" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H122">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I122" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J122" s="1">
-        <v>46507</v>
+        <v>46504</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
@@ -5410,34 +5389,34 @@
     </row>
     <row r="123" spans="1:11">
       <c r="A123" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B123">
-        <v>2702</v>
+        <v>2737</v>
       </c>
       <c r="C123" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D123" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E123" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F123" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G123" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H123">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I123" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J123" s="1">
-        <v>46508</v>
+        <v>46504</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
@@ -5445,34 +5424,34 @@
     </row>
     <row r="124" spans="1:11">
       <c r="A124" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B124">
-        <v>2728</v>
+        <v>2743</v>
       </c>
       <c r="C124" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D124" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E124" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F124" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G124" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H124">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I124" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J124" s="1">
-        <v>46512</v>
+        <v>46507</v>
       </c>
       <c r="K124" t="b">
         <v>0</v>
@@ -5480,34 +5459,34 @@
     </row>
     <row r="125" spans="1:11">
       <c r="A125" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B125">
-        <v>2731</v>
+        <v>2702</v>
       </c>
       <c r="C125" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D125" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E125" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F125" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="G125" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H125">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="I125" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J125" s="1">
-        <v>46512</v>
+        <v>46508</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
@@ -5515,34 +5494,34 @@
     </row>
     <row r="126" spans="1:11">
       <c r="A126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B126">
-        <v>2703</v>
+        <v>2728</v>
       </c>
       <c r="C126" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="D126" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E126" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F126" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G126" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H126">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="I126" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="J126" s="1">
-        <v>46528</v>
+        <v>46512</v>
       </c>
       <c r="K126" t="b">
         <v>0</v>
@@ -5550,34 +5529,34 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B127">
-        <v>2704</v>
+        <v>2731</v>
       </c>
       <c r="C127" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="D127" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="E127" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F127" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="G127" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H127">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I127" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J127" s="1">
-        <v>46529</v>
+        <v>46512</v>
       </c>
       <c r="K127" t="b">
         <v>0</v>
@@ -5585,34 +5564,34 @@
     </row>
     <row r="128" spans="1:11">
       <c r="A128" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B128">
-        <v>2736</v>
+        <v>2703</v>
       </c>
       <c r="C128" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D128" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E128" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F128" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="G128" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H128">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="I128" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J128" s="1">
-        <v>46537</v>
+        <v>46528</v>
       </c>
       <c r="K128" t="b">
         <v>0</v>
@@ -5620,34 +5599,34 @@
     </row>
     <row r="129" spans="1:11">
       <c r="A129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B129">
-        <v>2737</v>
+        <v>2704</v>
       </c>
       <c r="C129" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="D129" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E129" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F129" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="G129" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H129">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="I129" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="J129" s="1">
-        <v>46546</v>
+        <v>46529</v>
       </c>
       <c r="K129" t="b">
         <v>0</v>
@@ -5655,34 +5634,34 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B130">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="C130" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D130" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E130" t="s">
         <v>265</v>
       </c>
       <c r="F130" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="G130" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H130">
-        <v>330</v>
+        <v>270</v>
       </c>
       <c r="I130" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="J130" s="1">
-        <v>46547</v>
+        <v>46537</v>
       </c>
       <c r="K130" t="b">
         <v>0</v>
@@ -5690,34 +5669,34 @@
     </row>
     <row r="131" spans="1:11">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B131">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="C131" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D131" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E131" t="s">
         <v>265</v>
       </c>
       <c r="F131" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H131">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I131" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J131" s="1">
-        <v>46547</v>
+        <v>46546</v>
       </c>
       <c r="K131" t="b">
         <v>0</v>
@@ -5725,31 +5704,31 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B132">
-        <v>2738</v>
+        <v>2740</v>
       </c>
       <c r="C132" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D132" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E132" t="s">
         <v>265</v>
       </c>
       <c r="F132" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="G132" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H132">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I132" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J132" s="1">
         <v>46547</v>
@@ -5760,34 +5739,34 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B133">
-        <v>2708</v>
+        <v>2736</v>
       </c>
       <c r="C133" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D133" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E133" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F133" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G133" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H133">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I133" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J133" s="1">
-        <v>46551</v>
+        <v>46547</v>
       </c>
       <c r="K133" t="b">
         <v>0</v>
@@ -5795,34 +5774,34 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B134">
-        <v>2708</v>
+        <v>2738</v>
       </c>
       <c r="C134" t="s">
         <v>222</v>
       </c>
       <c r="D134" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="E134" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F134" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G134" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H134">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I134" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J134" s="1">
-        <v>46560</v>
+        <v>46547</v>
       </c>
       <c r="K134" t="b">
         <v>0</v>
@@ -5830,34 +5809,34 @@
     </row>
     <row r="135" spans="1:11">
       <c r="A135" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B135">
-        <v>2738</v>
+        <v>2708</v>
       </c>
       <c r="C135" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D135" t="s">
         <v>254</v>
       </c>
       <c r="E135" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F135" t="s">
-        <v>304</v>
+        <v>279</v>
       </c>
       <c r="G135" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H135">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I135" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J135" s="1">
-        <v>46564</v>
+        <v>46551</v>
       </c>
       <c r="K135" t="b">
         <v>0</v>
@@ -5865,34 +5844,34 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B136">
-        <v>2703</v>
+        <v>2708</v>
       </c>
       <c r="C136" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D136" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E136" t="s">
         <v>267</v>
       </c>
       <c r="F136" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G136" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H136">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="I136" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J136" s="1">
-        <v>46567</v>
+        <v>46560</v>
       </c>
       <c r="K136" t="b">
         <v>0</v>
@@ -5900,34 +5879,34 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B137">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="C137" t="s">
         <v>219</v>
       </c>
       <c r="D137" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E137" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F137" t="s">
+        <v>301</v>
+      </c>
+      <c r="G137" t="s">
+        <v>309</v>
+      </c>
+      <c r="H137">
         <v>300</v>
       </c>
-      <c r="G137" t="s">
-        <v>311</v>
-      </c>
-      <c r="H137">
-        <v>330</v>
-      </c>
       <c r="I137" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J137" s="1">
-        <v>46568</v>
+        <v>46564</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
@@ -5935,34 +5914,34 @@
     </row>
     <row r="138" spans="1:11">
       <c r="A138" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B138">
-        <v>2723</v>
+        <v>2703</v>
       </c>
       <c r="C138" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D138" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E138" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F138" t="s">
+        <v>299</v>
+      </c>
+      <c r="G138" t="s">
+        <v>309</v>
+      </c>
+      <c r="H138">
         <v>300</v>
       </c>
-      <c r="G138" t="s">
-        <v>311</v>
-      </c>
-      <c r="H138">
-        <v>330</v>
-      </c>
       <c r="I138" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J138" s="1">
-        <v>46571</v>
+        <v>46567</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
@@ -5970,69 +5949,69 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B139">
-        <v>2733</v>
+        <v>2742</v>
       </c>
       <c r="C139" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D139" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E139" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G139" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H139">
-        <v>-14</v>
+        <v>300</v>
       </c>
       <c r="I139" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J139" s="1">
-        <v>46197</v>
+        <v>46568</v>
       </c>
       <c r="K139" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11">
       <c r="A140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B140">
-        <v>2729</v>
+        <v>2736</v>
       </c>
       <c r="C140" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D140" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E140" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F140" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G140" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>330</v>
       </c>
       <c r="I140" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="J140" s="1">
-        <v>46212</v>
+        <v>46578</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
@@ -6040,34 +6019,34 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B141">
-        <v>2730</v>
+        <v>2737</v>
       </c>
       <c r="C141" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D141" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E141" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F141" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G141" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H141">
-        <v>14</v>
+        <v>330</v>
       </c>
       <c r="I141" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J141" s="1">
-        <v>46225</v>
+        <v>46592</v>
       </c>
       <c r="K141" t="b">
         <v>0</v>
@@ -6075,34 +6054,34 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B142">
-        <v>2727</v>
+        <v>2737</v>
       </c>
       <c r="C142" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="D142" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="E142" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="F142" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="G142" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H142">
-        <v>23</v>
+        <v>330</v>
       </c>
       <c r="I142" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="J142" s="1">
-        <v>46234</v>
+        <v>46592</v>
       </c>
       <c r="K142" t="b">
         <v>0</v>
@@ -6110,104 +6089,104 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B143">
-        <v>2741</v>
+        <v>2729</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D143" t="s">
         <v>255</v>
       </c>
       <c r="E143" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F143" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="G143" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H143">
-        <v>24</v>
+        <v>-27</v>
       </c>
       <c r="I143" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="J143" s="1">
-        <v>46234</v>
+        <v>46212</v>
       </c>
       <c r="K143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:11">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B144">
-        <v>2727</v>
+        <v>2730</v>
       </c>
       <c r="C144" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="D144" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E144" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="F144" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G144" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H144">
-        <v>53</v>
+        <v>-14</v>
       </c>
       <c r="I144" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="J144" s="1">
-        <v>46263</v>
+        <v>46225</v>
       </c>
       <c r="K144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B145">
-        <v>2737</v>
+        <v>2727</v>
       </c>
       <c r="C145" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D145" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E145" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F145" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G145" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H145">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I145" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="J145" s="1">
-        <v>46266</v>
+        <v>46263</v>
       </c>
       <c r="K145" t="b">
         <v>0</v>
@@ -6215,25 +6194,25 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B146">
         <v>2724</v>
       </c>
       <c r="C146" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D146" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E146" t="s">
         <v>266</v>
       </c>
       <c r="F146" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G146" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H146">
         <v>-1476</v>
@@ -6247,25 +6226,25 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B147">
         <v>2724</v>
       </c>
       <c r="C147" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D147" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E147" t="s">
         <v>266</v>
       </c>
       <c r="F147" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G147" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H147">
         <v>-1469</v>
@@ -6279,28 +6258,28 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B148">
         <v>2736</v>
       </c>
       <c r="C148" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D148" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E148" t="s">
         <v>265</v>
       </c>
       <c r="F148" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G148" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H148">
-        <v>-1121</v>
+        <v>-1186</v>
       </c>
       <c r="J148" s="1">
         <v>45295</v>
@@ -6311,28 +6290,28 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B149">
         <v>2740</v>
       </c>
       <c r="C149" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D149" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E149" t="s">
         <v>265</v>
       </c>
       <c r="F149" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G149" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H149">
-        <v>-1018</v>
+        <v>-1048</v>
       </c>
       <c r="J149" s="1">
         <v>45617</v>
@@ -6343,28 +6322,28 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B150">
         <v>2740</v>
       </c>
       <c r="C150" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D150" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E150" t="s">
         <v>265</v>
       </c>
       <c r="F150" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G150" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H150">
-        <v>-950</v>
+        <v>-980</v>
       </c>
       <c r="J150" s="1">
         <v>45677</v>
@@ -6375,28 +6354,28 @@
     </row>
     <row r="151" spans="1:11">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B151">
         <v>2720</v>
       </c>
       <c r="C151" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D151" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E151" t="s">
         <v>272</v>
       </c>
       <c r="F151" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G151" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H151">
-        <v>-943</v>
+        <v>-961</v>
       </c>
       <c r="J151" s="1">
         <v>44944</v>
@@ -6407,25 +6386,25 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B152">
         <v>2703</v>
       </c>
       <c r="C152" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D152" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E152" t="s">
         <v>267</v>
       </c>
       <c r="F152" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G152" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H152">
         <v>-252</v>
@@ -6439,255 +6418,255 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B153">
-        <v>2742</v>
+        <v>2719</v>
       </c>
       <c r="C153" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D153" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E153" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F153" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G153" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H153">
-        <v>-196</v>
+        <v>3</v>
       </c>
       <c r="J153" s="1">
-        <v>45988</v>
+        <v>46265</v>
       </c>
       <c r="K153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B154">
-        <v>2742</v>
+        <v>2719</v>
       </c>
       <c r="C154" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D154" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E154" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F154" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G154" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H154">
-        <v>-196</v>
+        <v>3</v>
       </c>
       <c r="J154" s="1">
-        <v>45988</v>
+        <v>46265</v>
       </c>
       <c r="K154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B155">
-        <v>2743</v>
+        <v>2728</v>
       </c>
       <c r="C155" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D155" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E155" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F155" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="G155" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H155">
-        <v>-47</v>
+        <v>43</v>
       </c>
       <c r="J155" s="1">
-        <v>46176</v>
+        <v>46440</v>
       </c>
       <c r="K155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B156">
-        <v>2743</v>
+        <v>2728</v>
       </c>
       <c r="C156" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D156" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E156" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F156" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="G156" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H156">
-        <v>-47</v>
+        <v>43</v>
       </c>
       <c r="J156" s="1">
-        <v>46176</v>
+        <v>46440</v>
       </c>
       <c r="K156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B157">
-        <v>2733</v>
+        <v>2722</v>
       </c>
       <c r="C157" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D157" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E157" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F157" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="G157" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H157">
-        <v>-33</v>
+        <v>72</v>
       </c>
       <c r="J157" s="1">
-        <v>46199</v>
+        <v>46289</v>
       </c>
       <c r="K157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:11">
       <c r="A158" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B158">
-        <v>2733</v>
+        <v>2722</v>
       </c>
       <c r="C158" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D158" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E158" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F158" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="G158" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H158">
-        <v>-33</v>
+        <v>72</v>
       </c>
       <c r="J158" s="1">
-        <v>46199</v>
+        <v>46289</v>
       </c>
       <c r="K158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B159">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="C159" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E159" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F159" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G159" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H159">
-        <v>-6</v>
+        <v>81</v>
       </c>
       <c r="J159" s="1">
-        <v>45967</v>
+        <v>46405</v>
       </c>
       <c r="K159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B160">
-        <v>2728</v>
+        <v>2732</v>
       </c>
       <c r="C160" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D160" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E160" t="s">
         <v>266</v>
       </c>
       <c r="F160" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="G160" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H160">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="J160" s="1">
-        <v>46440</v>
+        <v>46463</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
@@ -6695,31 +6674,31 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B161">
-        <v>2728</v>
+        <v>2741</v>
       </c>
       <c r="C161" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D161" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E161" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F161" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="G161" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H161">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="J161" s="1">
-        <v>46440</v>
+        <v>46353</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
@@ -6727,31 +6706,31 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B162">
-        <v>2719</v>
+        <v>2739</v>
       </c>
       <c r="C162" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D162" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E162" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F162" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="G162" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H162">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="J162" s="1">
-        <v>46264</v>
+        <v>46417</v>
       </c>
       <c r="K162" t="b">
         <v>0</v>
@@ -6759,31 +6738,31 @@
     </row>
     <row r="163" spans="1:11">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B163">
-        <v>2719</v>
+        <v>2723</v>
       </c>
       <c r="C163" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D163" t="s">
         <v>263</v>
       </c>
       <c r="E163" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G163" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H163">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="J163" s="1">
-        <v>46264</v>
+        <v>46271</v>
       </c>
       <c r="K163" t="b">
         <v>0</v>
@@ -6791,31 +6770,31 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B164">
-        <v>2732</v>
+        <v>2723</v>
       </c>
       <c r="C164" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E164" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F164" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="G164" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H164">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="J164" s="1">
-        <v>46463</v>
+        <v>46271</v>
       </c>
       <c r="K164" t="b">
         <v>0</v>
@@ -6823,31 +6802,31 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B165">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="C165" t="s">
         <v>233</v>
       </c>
       <c r="D165" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="E165" t="s">
         <v>265</v>
       </c>
       <c r="F165" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="G165" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H165">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="J165" s="1">
-        <v>46337</v>
+        <v>46458</v>
       </c>
       <c r="K165" t="b">
         <v>0</v>
@@ -6855,31 +6834,31 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B166">
-        <v>2736</v>
+        <v>2720</v>
       </c>
       <c r="C166" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D166" t="s">
         <v>263</v>
       </c>
       <c r="E166" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F166" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G166" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H166">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="J166" s="1">
-        <v>46451</v>
+        <v>46381</v>
       </c>
       <c r="K166" t="b">
         <v>0</v>
@@ -6887,31 +6866,31 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B167">
-        <v>2723</v>
+        <v>2728</v>
       </c>
       <c r="C167" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D167" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E167" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F167" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="G167" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H167">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="J167" s="1">
-        <v>46245</v>
+        <v>46592</v>
       </c>
       <c r="K167" t="b">
         <v>0</v>
@@ -6919,31 +6898,31 @@
     </row>
     <row r="168" spans="1:11">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B168">
-        <v>2723</v>
+        <v>2731</v>
       </c>
       <c r="C168" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E168" t="s">
         <v>270</v>
       </c>
       <c r="F168" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G168" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H168">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="J168" s="1">
-        <v>46245</v>
+        <v>46441</v>
       </c>
       <c r="K168" t="b">
         <v>0</v>
@@ -6951,31 +6930,31 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B169">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="C169" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E169" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F169" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="G169" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H169">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="J169" s="1">
-        <v>46324</v>
+        <v>46391</v>
       </c>
       <c r="K169" t="b">
         <v>0</v>
@@ -6983,31 +6962,31 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B170">
-        <v>2722</v>
+        <v>2709</v>
       </c>
       <c r="C170" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D170" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E170" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F170" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="G170" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H170">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="J170" s="1">
-        <v>46324</v>
+        <v>46385</v>
       </c>
       <c r="K170" t="b">
         <v>0</v>
@@ -7015,31 +6994,31 @@
     </row>
     <row r="171" spans="1:11">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B171">
-        <v>2739</v>
+        <v>2709</v>
       </c>
       <c r="C171" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D171" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="E171" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F171" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="G171" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H171">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="J171" s="1">
-        <v>46426</v>
+        <v>46387</v>
       </c>
       <c r="K171" t="b">
         <v>0</v>
@@ -7047,31 +7026,31 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B172">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="C172" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E172" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F172" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G172" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H172">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="J172" s="1">
-        <v>46383</v>
+        <v>46399</v>
       </c>
       <c r="K172" t="b">
         <v>0</v>
@@ -7079,31 +7058,31 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B173">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="C173" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D173" t="s">
         <v>263</v>
       </c>
       <c r="E173" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F173" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G173" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H173">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="J173" s="1">
-        <v>46392</v>
+        <v>46399</v>
       </c>
       <c r="K173" t="b">
         <v>0</v>
@@ -7111,31 +7090,31 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B174">
-        <v>2709</v>
+        <v>2738</v>
       </c>
       <c r="C174" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D174" t="s">
         <v>263</v>
       </c>
       <c r="E174" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="F174" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G174" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H174">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="J174" s="1">
-        <v>46390</v>
+        <v>46458</v>
       </c>
       <c r="K174" t="b">
         <v>0</v>
@@ -7143,31 +7122,31 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B175">
-        <v>2709</v>
+        <v>2706</v>
       </c>
       <c r="C175" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D175" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="E175" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F175" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G175" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H175">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="J175" s="1">
-        <v>46392</v>
+        <v>46528</v>
       </c>
       <c r="K175" t="b">
         <v>0</v>
@@ -7175,31 +7154,31 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B176">
-        <v>2736</v>
+        <v>2733</v>
       </c>
       <c r="C176" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D176" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E176" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F176" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="G176" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H176">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="J176" s="1">
-        <v>46506</v>
+        <v>46540</v>
       </c>
       <c r="K176" t="b">
         <v>0</v>
@@ -7207,31 +7186,31 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B177">
         <v>2731</v>
       </c>
       <c r="C177" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D177" t="s">
         <v>263</v>
       </c>
       <c r="E177" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F177" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G177" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H177">
-        <v>246</v>
+        <v>340</v>
       </c>
       <c r="J177" s="1">
-        <v>46478</v>
+        <v>46547</v>
       </c>
       <c r="K177" t="b">
         <v>0</v>
@@ -7239,31 +7218,31 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B178">
-        <v>2706</v>
+        <v>2738</v>
       </c>
       <c r="C178" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="D178" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E178" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F178" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="G178" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H178">
-        <v>248</v>
+        <v>364</v>
       </c>
       <c r="J178" s="1">
-        <v>46500</v>
+        <v>46557</v>
       </c>
       <c r="K178" t="b">
         <v>0</v>
@@ -7271,31 +7250,31 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B179">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C179" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E179" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F179" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G179" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H179">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="J179" s="1">
-        <v>46430</v>
+        <v>46571</v>
       </c>
       <c r="K179" t="b">
         <v>0</v>
@@ -7303,31 +7282,31 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B180">
-        <v>2719</v>
+        <v>2733</v>
       </c>
       <c r="C180" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D180" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E180" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F180" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G180" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H180">
-        <v>276</v>
+        <v>368</v>
       </c>
       <c r="J180" s="1">
-        <v>46430</v>
+        <v>46571</v>
       </c>
       <c r="K180" t="b">
         <v>0</v>
@@ -7335,31 +7314,31 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B181">
         <v>2738</v>
       </c>
       <c r="C181" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D181" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="E181" t="s">
         <v>265</v>
       </c>
       <c r="F181" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="G181" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H181">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="J181" s="1">
-        <v>46467</v>
+        <v>46562</v>
       </c>
       <c r="K181" t="b">
         <v>0</v>
@@ -7367,31 +7346,31 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B182">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="C182" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D182" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E182" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="F182" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G182" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H182">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="J182" s="1">
-        <v>46529</v>
+        <v>46574</v>
       </c>
       <c r="K182" t="b">
         <v>0</v>
@@ -7399,31 +7378,31 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B183">
-        <v>2738</v>
+        <v>2731</v>
       </c>
       <c r="C183" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D183" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E183" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F183" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="G183" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H183">
-        <v>420</v>
+        <v>385</v>
       </c>
       <c r="J183" s="1">
-        <v>46566</v>
+        <v>46574</v>
       </c>
       <c r="K183" t="b">
         <v>0</v>
@@ -7431,31 +7410,31 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B184">
-        <v>2738</v>
+        <v>2720</v>
       </c>
       <c r="C184" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D184" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E184" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F184" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="G184" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H184">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="J184" s="1">
-        <v>46571</v>
+        <v>46578</v>
       </c>
       <c r="K184" t="b">
         <v>0</v>
@@ -7463,31 +7442,31 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B185">
         <v>2723</v>
       </c>
       <c r="C185" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D185" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E185" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F185" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G185" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H185">
         <v>721</v>
       </c>
       <c r="J185" s="1">
-        <v>46325</v>
+        <v>46345</v>
       </c>
       <c r="K185" t="b">
         <v>0</v>
@@ -7495,31 +7474,31 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B186">
         <v>2723</v>
       </c>
       <c r="C186" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D186" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E186" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F186" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G186" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H186">
         <v>721</v>
       </c>
       <c r="J186" s="1">
-        <v>46325</v>
+        <v>46345</v>
       </c>
       <c r="K186" t="b">
         <v>0</v>
@@ -7527,7 +7506,7 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B187">
         <v>2723</v>
@@ -7536,22 +7515,22 @@
         <v>235</v>
       </c>
       <c r="D187" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E187" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F187" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G187" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H187">
         <v>850</v>
       </c>
       <c r="J187" s="1">
-        <v>46345</v>
+        <v>46366</v>
       </c>
       <c r="K187" t="b">
         <v>0</v>
@@ -7559,31 +7538,31 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B188">
         <v>2723</v>
       </c>
       <c r="C188" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D188" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F188" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G188" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H188">
         <v>850</v>
       </c>
       <c r="J188" s="1">
-        <v>46345</v>
+        <v>46366</v>
       </c>
       <c r="K188" t="b">
         <v>0</v>
@@ -7591,31 +7570,31 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B189">
         <v>2723</v>
       </c>
       <c r="C189" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D189" t="s">
         <v>263</v>
       </c>
       <c r="E189" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F189" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G189" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H189">
         <v>1661</v>
       </c>
       <c r="J189" s="1">
-        <v>46498</v>
+        <v>46524</v>
       </c>
       <c r="K189" t="b">
         <v>0</v>
@@ -7623,31 +7602,31 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B190">
         <v>2723</v>
       </c>
       <c r="C190" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D190" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E190" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F190" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G190" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H190">
         <v>1661</v>
       </c>
       <c r="J190" s="1">
-        <v>46498</v>
+        <v>46524</v>
       </c>
       <c r="K190" t="b">
         <v>0</v>
@@ -7655,25 +7634,25 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B191">
         <v>2724</v>
       </c>
       <c r="C191" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D191" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E191" t="s">
         <v>266</v>
       </c>
       <c r="F191" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G191" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H191">
         <v>488</v>
@@ -7687,25 +7666,25 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B192">
         <v>2724</v>
       </c>
       <c r="C192" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D192" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E192" t="s">
         <v>266</v>
       </c>
       <c r="F192" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G192" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H192">
         <v>25565</v>
@@ -7719,25 +7698,25 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B193">
         <v>2724</v>
       </c>
       <c r="C193" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D193" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E193" t="s">
         <v>266</v>
       </c>
       <c r="F193" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G193" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H193">
         <v>25567</v>
@@ -7751,25 +7730,25 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B194">
         <v>2724</v>
       </c>
       <c r="C194" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D194" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E194" t="s">
         <v>266</v>
       </c>
       <c r="F194" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G194" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H194">
         <v>31293</v>

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1019,8 +1019,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1036,7 +1044,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1044,12 +1052,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1349,37 +1375,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1408,7 +1434,7 @@
       <c r="H2">
         <v>-4300.3</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="2">
         <v>39285</v>
       </c>
       <c r="K2" t="b">
@@ -1440,7 +1466,7 @@
       <c r="H3">
         <v>-2354.2</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="2">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1472,7 +1498,7 @@
       <c r="H4">
         <v>-910.7</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="2">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1504,7 +1530,7 @@
       <c r="H5">
         <v>-868</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="2">
         <v>44884</v>
       </c>
       <c r="K5" t="b">
@@ -1536,7 +1562,7 @@
       <c r="H6">
         <v>-483.8</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="2">
         <v>43855</v>
       </c>
       <c r="K6" t="b">
@@ -1568,7 +1594,7 @@
       <c r="H7">
         <v>-417</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="2">
         <v>46014</v>
       </c>
       <c r="K7" t="b">
@@ -1600,7 +1626,7 @@
       <c r="H8">
         <v>-414.2</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="2">
         <v>46014</v>
       </c>
       <c r="K8" t="b">
@@ -1632,7 +1658,7 @@
       <c r="H9">
         <v>-391.8</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="2">
         <v>42769</v>
       </c>
       <c r="K9" t="b">
@@ -1664,7 +1690,7 @@
       <c r="H10">
         <v>-391.6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="2">
         <v>45804</v>
       </c>
       <c r="K10" t="b">
@@ -1696,7 +1722,7 @@
       <c r="H11">
         <v>-391.6</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="2">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -1728,7 +1754,7 @@
       <c r="H12">
         <v>-372.9</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="2">
         <v>42821</v>
       </c>
       <c r="K12" t="b">
@@ -1760,7 +1786,7 @@
       <c r="H13">
         <v>-372.9</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="2">
         <v>46014</v>
       </c>
       <c r="K13" t="b">
@@ -1792,7 +1818,7 @@
       <c r="H14">
         <v>-372.9</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="2">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1824,7 +1850,7 @@
       <c r="H15">
         <v>-372.9</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="2">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1856,7 +1882,7 @@
       <c r="H16">
         <v>-367.8</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="2">
         <v>46017</v>
       </c>
       <c r="K16" t="b">
@@ -1888,7 +1914,7 @@
       <c r="H17">
         <v>-367.8</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="2">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1920,7 +1946,7 @@
       <c r="H18">
         <v>-347.2</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="2">
         <v>40979</v>
       </c>
       <c r="K18" t="b">
@@ -1952,7 +1978,7 @@
       <c r="H19">
         <v>-293.8</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="2">
         <v>45846</v>
       </c>
       <c r="K19" t="b">
@@ -1984,7 +2010,7 @@
       <c r="H20">
         <v>-206.4</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="2">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -2016,7 +2042,7 @@
       <c r="H21">
         <v>-131.6</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="2">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -2048,7 +2074,7 @@
       <c r="H22">
         <v>-131.6</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="2">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -2080,7 +2106,7 @@
       <c r="H23">
         <v>-131.6</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="2">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -2112,7 +2138,7 @@
       <c r="H24">
         <v>-131.6</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="2">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -2144,7 +2170,7 @@
       <c r="H25">
         <v>-131.6</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="2">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -2176,7 +2202,7 @@
       <c r="H26">
         <v>-98.3</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="2">
         <v>41204</v>
       </c>
       <c r="K26" t="b">
@@ -2208,7 +2234,7 @@
       <c r="H27">
         <v>-47.2</v>
       </c>
-      <c r="J27" s="1">
+      <c r="J27" s="2">
         <v>44011</v>
       </c>
       <c r="K27" t="b">
@@ -2240,7 +2266,7 @@
       <c r="H28">
         <v>-22.3</v>
       </c>
-      <c r="J28" s="1">
+      <c r="J28" s="2">
         <v>46226</v>
       </c>
       <c r="K28" t="b">
@@ -2272,7 +2298,7 @@
       <c r="H29">
         <v>4.7</v>
       </c>
-      <c r="J29" s="1">
+      <c r="J29" s="2">
         <v>46265</v>
       </c>
       <c r="K29" t="b">
@@ -2304,7 +2330,7 @@
       <c r="H30">
         <v>7.5</v>
       </c>
-      <c r="J30" s="1">
+      <c r="J30" s="2">
         <v>46265</v>
       </c>
       <c r="K30" t="b">
@@ -2336,7 +2362,7 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="2">
         <v>46265</v>
       </c>
       <c r="K31" t="b">
@@ -2368,7 +2394,7 @@
       <c r="H32">
         <v>12.8</v>
       </c>
-      <c r="J32" s="1">
+      <c r="J32" s="2">
         <v>46265</v>
       </c>
       <c r="K32" t="b">
@@ -2400,7 +2426,7 @@
       <c r="H33">
         <v>14</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="2">
         <v>46265</v>
       </c>
       <c r="K33" t="b">
@@ -2432,7 +2458,7 @@
       <c r="H34">
         <v>17.8</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="2">
         <v>46265</v>
       </c>
       <c r="K34" t="b">
@@ -2464,7 +2490,7 @@
       <c r="H35">
         <v>20.4</v>
       </c>
-      <c r="J35" s="1">
+      <c r="J35" s="2">
         <v>46265</v>
       </c>
       <c r="K35" t="b">
@@ -2496,7 +2522,7 @@
       <c r="H36">
         <v>21.2</v>
       </c>
-      <c r="J36" s="1">
+      <c r="J36" s="2">
         <v>46265</v>
       </c>
       <c r="K36" t="b">
@@ -2528,7 +2554,7 @@
       <c r="H37">
         <v>26.2</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37" s="2">
         <v>46265</v>
       </c>
       <c r="K37" t="b">
@@ -2560,7 +2586,7 @@
       <c r="H38">
         <v>33.6</v>
       </c>
-      <c r="J38" s="1">
+      <c r="J38" s="2">
         <v>46364</v>
       </c>
       <c r="K38" t="b">
@@ -2592,7 +2618,7 @@
       <c r="H39">
         <v>42.2</v>
       </c>
-      <c r="J39" s="1">
+      <c r="J39" s="2">
         <v>46269</v>
       </c>
       <c r="K39" t="b">
@@ -2624,7 +2650,7 @@
       <c r="H40">
         <v>42.8</v>
       </c>
-      <c r="J40" s="1">
+      <c r="J40" s="2">
         <v>46291</v>
       </c>
       <c r="K40" t="b">
@@ -2656,7 +2682,7 @@
       <c r="H41">
         <v>45.7</v>
       </c>
-      <c r="J41" s="1">
+      <c r="J41" s="2">
         <v>46395</v>
       </c>
       <c r="K41" t="b">
@@ -2688,7 +2714,7 @@
       <c r="H42">
         <v>47.2</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42" s="2">
         <v>46280</v>
       </c>
       <c r="K42" t="b">
@@ -2720,7 +2746,7 @@
       <c r="H43">
         <v>48.7</v>
       </c>
-      <c r="J43" s="1">
+      <c r="J43" s="2">
         <v>46281</v>
       </c>
       <c r="K43" t="b">
@@ -2752,7 +2778,7 @@
       <c r="H44">
         <v>60</v>
       </c>
-      <c r="J44" s="1">
+      <c r="J44" s="2">
         <v>46281</v>
       </c>
       <c r="K44" t="b">
@@ -2784,7 +2810,7 @@
       <c r="H45">
         <v>62.6</v>
       </c>
-      <c r="J45" s="1">
+      <c r="J45" s="2">
         <v>46265</v>
       </c>
       <c r="K45" t="b">
@@ -2816,7 +2842,7 @@
       <c r="H46">
         <v>64.59999999999999</v>
       </c>
-      <c r="J46" s="1">
+      <c r="J46" s="2">
         <v>46265</v>
       </c>
       <c r="K46" t="b">
@@ -2848,7 +2874,7 @@
       <c r="H47">
         <v>67.59999999999999</v>
       </c>
-      <c r="J47" s="1">
+      <c r="J47" s="2">
         <v>46267</v>
       </c>
       <c r="K47" t="b">
@@ -2880,7 +2906,7 @@
       <c r="H48">
         <v>68.3</v>
       </c>
-      <c r="J48" s="1">
+      <c r="J48" s="2">
         <v>46278</v>
       </c>
       <c r="K48" t="b">
@@ -2912,7 +2938,7 @@
       <c r="H49">
         <v>69.2</v>
       </c>
-      <c r="J49" s="1">
+      <c r="J49" s="2">
         <v>46453</v>
       </c>
       <c r="K49" t="b">
@@ -2944,7 +2970,7 @@
       <c r="H50">
         <v>69.8</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50" s="2">
         <v>46265</v>
       </c>
       <c r="K50" t="b">
@@ -2976,7 +3002,7 @@
       <c r="H51">
         <v>69.8</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51" s="2">
         <v>46265</v>
       </c>
       <c r="K51" t="b">
@@ -3008,7 +3034,7 @@
       <c r="H52">
         <v>72.2</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52" s="2">
         <v>46275</v>
       </c>
       <c r="K52" t="b">
@@ -3040,7 +3066,7 @@
       <c r="H53">
         <v>72.2</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53" s="2">
         <v>46275</v>
       </c>
       <c r="K53" t="b">
@@ -3072,7 +3098,7 @@
       <c r="H54">
         <v>78.09999999999999</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54" s="2">
         <v>46265</v>
       </c>
       <c r="K54" t="b">
@@ -3104,7 +3130,7 @@
       <c r="H55">
         <v>82.8</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55" s="2">
         <v>46487</v>
       </c>
       <c r="K55" t="b">
@@ -3136,7 +3162,7 @@
       <c r="H56">
         <v>83.09999999999999</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56" s="2">
         <v>46285</v>
       </c>
       <c r="K56" t="b">
@@ -3168,7 +3194,7 @@
       <c r="H57">
         <v>84.8</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57" s="2">
         <v>46492</v>
       </c>
       <c r="K57" t="b">
@@ -3200,7 +3226,7 @@
       <c r="H58">
         <v>104.9</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58" s="2">
         <v>46297</v>
       </c>
       <c r="K58" t="b">
@@ -3232,7 +3258,7 @@
       <c r="H59">
         <v>107.6</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59" s="2">
         <v>46283</v>
       </c>
       <c r="K59" t="b">
@@ -3264,7 +3290,7 @@
       <c r="H60">
         <v>111.9</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60" s="2">
         <v>46300</v>
       </c>
       <c r="K60" t="b">
@@ -3296,7 +3322,7 @@
       <c r="H61">
         <v>111.9</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61" s="2">
         <v>46300</v>
       </c>
       <c r="K61" t="b">
@@ -3328,7 +3354,7 @@
       <c r="H62">
         <v>111.9</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62" s="2">
         <v>46300</v>
       </c>
       <c r="K62" t="b">
@@ -3360,7 +3386,7 @@
       <c r="H63">
         <v>111.9</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63" s="2">
         <v>46300</v>
       </c>
       <c r="K63" t="b">
@@ -3392,7 +3418,7 @@
       <c r="H64">
         <v>111.9</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64" s="2">
         <v>46300</v>
       </c>
       <c r="K64" t="b">
@@ -3424,7 +3450,7 @@
       <c r="H65">
         <v>128.8</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65" s="2">
         <v>46308</v>
       </c>
       <c r="K65" t="b">
@@ -3456,7 +3482,7 @@
       <c r="H66">
         <v>131.1</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66" s="2">
         <v>46336</v>
       </c>
       <c r="K66" t="b">
@@ -3488,7 +3514,7 @@
       <c r="H67">
         <v>138.4</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67" s="2">
         <v>46343</v>
       </c>
       <c r="K67" t="b">
@@ -3520,7 +3546,7 @@
       <c r="H68">
         <v>141</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68" s="2">
         <v>46350</v>
       </c>
       <c r="K68" t="b">
@@ -3552,7 +3578,7 @@
       <c r="H69">
         <v>162</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69" s="2">
         <v>46391</v>
       </c>
       <c r="K69" t="b">
@@ -3584,7 +3610,7 @@
       <c r="H70">
         <v>167.2</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70" s="2">
         <v>46330</v>
       </c>
       <c r="K70" t="b">
@@ -3616,7 +3642,7 @@
       <c r="H71">
         <v>177.4</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71" s="2">
         <v>46418</v>
       </c>
       <c r="K71" t="b">
@@ -3648,7 +3674,7 @@
       <c r="H72">
         <v>200</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72" s="2">
         <v>46356</v>
       </c>
       <c r="K72" t="b">
@@ -3680,7 +3706,7 @@
       <c r="H73">
         <v>203.6</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73" s="2">
         <v>46436</v>
       </c>
       <c r="K73" t="b">
@@ -3712,7 +3738,7 @@
       <c r="H74">
         <v>221.2</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74" s="2">
         <v>46426</v>
       </c>
       <c r="K74" t="b">
@@ -3744,7 +3770,7 @@
       <c r="H75">
         <v>240.8</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75" s="2">
         <v>46450</v>
       </c>
       <c r="K75" t="b">
@@ -3776,7 +3802,7 @@
       <c r="H76">
         <v>245.8</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76" s="2">
         <v>46452</v>
       </c>
       <c r="K76" t="b">
@@ -3808,7 +3834,7 @@
       <c r="H77">
         <v>263.4</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77" s="2">
         <v>46322</v>
       </c>
       <c r="K77" t="b">
@@ -3840,7 +3866,7 @@
       <c r="H78">
         <v>275.2</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78" s="2">
         <v>46433</v>
       </c>
       <c r="K78" t="b">
@@ -3875,7 +3901,7 @@
       <c r="I79" t="s">
         <v>311</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79" s="2">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -3910,7 +3936,7 @@
       <c r="I80" t="s">
         <v>312</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80" s="2">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -3945,7 +3971,7 @@
       <c r="I81" t="s">
         <v>313</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81" s="2">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -3980,7 +4006,7 @@
       <c r="I82" t="s">
         <v>314</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82" s="2">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4015,7 +4041,7 @@
       <c r="I83" t="s">
         <v>314</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83" s="2">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4050,7 +4076,7 @@
       <c r="I84" t="s">
         <v>315</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84" s="2">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4085,7 +4111,7 @@
       <c r="I85" t="s">
         <v>316</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85" s="2">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4120,7 +4146,7 @@
       <c r="I86" t="s">
         <v>317</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86" s="2">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4155,7 +4181,7 @@
       <c r="I87" t="s">
         <v>318</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87" s="2">
         <v>46284</v>
       </c>
       <c r="K87" t="b">
@@ -4190,7 +4216,7 @@
       <c r="I88" t="s">
         <v>319</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88" s="2">
         <v>46305</v>
       </c>
       <c r="K88" t="b">
@@ -4225,7 +4251,7 @@
       <c r="I89" t="s">
         <v>319</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89" s="2">
         <v>46310</v>
       </c>
       <c r="K89" t="b">
@@ -4260,7 +4286,7 @@
       <c r="I90" t="s">
         <v>319</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90" s="2">
         <v>46317</v>
       </c>
       <c r="K90" t="b">
@@ -4295,7 +4321,7 @@
       <c r="I91" t="s">
         <v>319</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91" s="2">
         <v>46319</v>
       </c>
       <c r="K91" t="b">
@@ -4330,7 +4356,7 @@
       <c r="I92" t="s">
         <v>320</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92" s="2">
         <v>46333</v>
       </c>
       <c r="K92" t="b">
@@ -4365,7 +4391,7 @@
       <c r="I93" t="s">
         <v>320</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93" s="2">
         <v>46338</v>
       </c>
       <c r="K93" t="b">
@@ -4400,7 +4426,7 @@
       <c r="I94" t="s">
         <v>320</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94" s="2">
         <v>46338</v>
       </c>
       <c r="K94" t="b">
@@ -4435,7 +4461,7 @@
       <c r="I95" t="s">
         <v>320</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95" s="2">
         <v>46341</v>
       </c>
       <c r="K95" t="b">
@@ -4470,7 +4496,7 @@
       <c r="I96" t="s">
         <v>320</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96" s="2">
         <v>46344</v>
       </c>
       <c r="K96" t="b">
@@ -4505,7 +4531,7 @@
       <c r="I97" t="s">
         <v>321</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97" s="2">
         <v>46360</v>
       </c>
       <c r="K97" t="b">
@@ -4540,7 +4566,7 @@
       <c r="I98" t="s">
         <v>321</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98" s="2">
         <v>46360</v>
       </c>
       <c r="K98" t="b">
@@ -4575,7 +4601,7 @@
       <c r="I99" t="s">
         <v>321</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99" s="2">
         <v>46367</v>
       </c>
       <c r="K99" t="b">
@@ -4610,7 +4636,7 @@
       <c r="I100" t="s">
         <v>321</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J100" s="2">
         <v>46375</v>
       </c>
       <c r="K100" t="b">
@@ -4645,7 +4671,7 @@
       <c r="I101" t="s">
         <v>321</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J101" s="2">
         <v>46387</v>
       </c>
       <c r="K101" t="b">
@@ -4680,7 +4706,7 @@
       <c r="I102" t="s">
         <v>321</v>
       </c>
-      <c r="J102" s="1">
+      <c r="J102" s="2">
         <v>46387</v>
       </c>
       <c r="K102" t="b">
@@ -4715,7 +4741,7 @@
       <c r="I103" t="s">
         <v>321</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J103" s="2">
         <v>46387</v>
       </c>
       <c r="K103" t="b">
@@ -4750,7 +4776,7 @@
       <c r="I104" t="s">
         <v>321</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J104" s="2">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -4785,7 +4811,7 @@
       <c r="I105" t="s">
         <v>322</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J105" s="2">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -4820,7 +4846,7 @@
       <c r="I106" t="s">
         <v>322</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J106" s="2">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -4855,7 +4881,7 @@
       <c r="I107" t="s">
         <v>322</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J107" s="2">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -4890,7 +4916,7 @@
       <c r="I108" t="s">
         <v>322</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J108" s="2">
         <v>46412</v>
       </c>
       <c r="K108" t="b">
@@ -4925,7 +4951,7 @@
       <c r="I109" t="s">
         <v>322</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J109" s="2">
         <v>46412</v>
       </c>
       <c r="K109" t="b">
@@ -4960,7 +4986,7 @@
       <c r="I110" t="s">
         <v>322</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J110" s="2">
         <v>46412</v>
       </c>
       <c r="K110" t="b">
@@ -4995,7 +5021,7 @@
       <c r="I111" t="s">
         <v>323</v>
       </c>
-      <c r="J111" s="1">
+      <c r="J111" s="2">
         <v>46424</v>
       </c>
       <c r="K111" t="b">
@@ -5030,7 +5056,7 @@
       <c r="I112" t="s">
         <v>323</v>
       </c>
-      <c r="J112" s="1">
+      <c r="J112" s="2">
         <v>46437</v>
       </c>
       <c r="K112" t="b">
@@ -5065,7 +5091,7 @@
       <c r="I113" t="s">
         <v>323</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J113" s="2">
         <v>46451</v>
       </c>
       <c r="K113" t="b">
@@ -5100,7 +5126,7 @@
       <c r="I114" t="s">
         <v>323</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J114" s="2">
         <v>46451</v>
       </c>
       <c r="K114" t="b">
@@ -5135,7 +5161,7 @@
       <c r="I115" t="s">
         <v>324</v>
       </c>
-      <c r="J115" s="1">
+      <c r="J115" s="2">
         <v>46455</v>
       </c>
       <c r="K115" t="b">
@@ -5170,7 +5196,7 @@
       <c r="I116" t="s">
         <v>324</v>
       </c>
-      <c r="J116" s="1">
+      <c r="J116" s="2">
         <v>46456</v>
       </c>
       <c r="K116" t="b">
@@ -5205,7 +5231,7 @@
       <c r="I117" t="s">
         <v>324</v>
       </c>
-      <c r="J117" s="1">
+      <c r="J117" s="2">
         <v>46457</v>
       </c>
       <c r="K117" t="b">
@@ -5240,7 +5266,7 @@
       <c r="I118" t="s">
         <v>324</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J118" s="2">
         <v>46464</v>
       </c>
       <c r="K118" t="b">
@@ -5275,7 +5301,7 @@
       <c r="I119" t="s">
         <v>324</v>
       </c>
-      <c r="J119" s="1">
+      <c r="J119" s="2">
         <v>46470</v>
       </c>
       <c r="K119" t="b">
@@ -5310,7 +5336,7 @@
       <c r="I120" t="s">
         <v>325</v>
       </c>
-      <c r="J120" s="1">
+      <c r="J120" s="2">
         <v>46485</v>
       </c>
       <c r="K120" t="b">
@@ -5345,7 +5371,7 @@
       <c r="I121" t="s">
         <v>325</v>
       </c>
-      <c r="J121" s="1">
+      <c r="J121" s="2">
         <v>46499</v>
       </c>
       <c r="K121" t="b">
@@ -5380,7 +5406,7 @@
       <c r="I122" t="s">
         <v>325</v>
       </c>
-      <c r="J122" s="1">
+      <c r="J122" s="2">
         <v>46504</v>
       </c>
       <c r="K122" t="b">
@@ -5415,7 +5441,7 @@
       <c r="I123" t="s">
         <v>325</v>
       </c>
-      <c r="J123" s="1">
+      <c r="J123" s="2">
         <v>46504</v>
       </c>
       <c r="K123" t="b">
@@ -5450,7 +5476,7 @@
       <c r="I124" t="s">
         <v>325</v>
       </c>
-      <c r="J124" s="1">
+      <c r="J124" s="2">
         <v>46507</v>
       </c>
       <c r="K124" t="b">
@@ -5485,7 +5511,7 @@
       <c r="I125" t="s">
         <v>325</v>
       </c>
-      <c r="J125" s="1">
+      <c r="J125" s="2">
         <v>46508</v>
       </c>
       <c r="K125" t="b">
@@ -5520,7 +5546,7 @@
       <c r="I126" t="s">
         <v>325</v>
       </c>
-      <c r="J126" s="1">
+      <c r="J126" s="2">
         <v>46512</v>
       </c>
       <c r="K126" t="b">
@@ -5555,7 +5581,7 @@
       <c r="I127" t="s">
         <v>326</v>
       </c>
-      <c r="J127" s="1">
+      <c r="J127" s="2">
         <v>46512</v>
       </c>
       <c r="K127" t="b">
@@ -5590,7 +5616,7 @@
       <c r="I128" t="s">
         <v>326</v>
       </c>
-      <c r="J128" s="1">
+      <c r="J128" s="2">
         <v>46528</v>
       </c>
       <c r="K128" t="b">
@@ -5625,7 +5651,7 @@
       <c r="I129" t="s">
         <v>326</v>
       </c>
-      <c r="J129" s="1">
+      <c r="J129" s="2">
         <v>46529</v>
       </c>
       <c r="K129" t="b">
@@ -5660,7 +5686,7 @@
       <c r="I130" t="s">
         <v>326</v>
       </c>
-      <c r="J130" s="1">
+      <c r="J130" s="2">
         <v>46537</v>
       </c>
       <c r="K130" t="b">
@@ -5695,7 +5721,7 @@
       <c r="I131" t="s">
         <v>327</v>
       </c>
-      <c r="J131" s="1">
+      <c r="J131" s="2">
         <v>46546</v>
       </c>
       <c r="K131" t="b">
@@ -5730,7 +5756,7 @@
       <c r="I132" t="s">
         <v>327</v>
       </c>
-      <c r="J132" s="1">
+      <c r="J132" s="2">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -5765,7 +5791,7 @@
       <c r="I133" t="s">
         <v>327</v>
       </c>
-      <c r="J133" s="1">
+      <c r="J133" s="2">
         <v>46547</v>
       </c>
       <c r="K133" t="b">
@@ -5800,7 +5826,7 @@
       <c r="I134" t="s">
         <v>327</v>
       </c>
-      <c r="J134" s="1">
+      <c r="J134" s="2">
         <v>46547</v>
       </c>
       <c r="K134" t="b">
@@ -5835,7 +5861,7 @@
       <c r="I135" t="s">
         <v>327</v>
       </c>
-      <c r="J135" s="1">
+      <c r="J135" s="2">
         <v>46551</v>
       </c>
       <c r="K135" t="b">
@@ -5870,7 +5896,7 @@
       <c r="I136" t="s">
         <v>327</v>
       </c>
-      <c r="J136" s="1">
+      <c r="J136" s="2">
         <v>46560</v>
       </c>
       <c r="K136" t="b">
@@ -5905,7 +5931,7 @@
       <c r="I137" t="s">
         <v>327</v>
       </c>
-      <c r="J137" s="1">
+      <c r="J137" s="2">
         <v>46564</v>
       </c>
       <c r="K137" t="b">
@@ -5940,7 +5966,7 @@
       <c r="I138" t="s">
         <v>327</v>
       </c>
-      <c r="J138" s="1">
+      <c r="J138" s="2">
         <v>46567</v>
       </c>
       <c r="K138" t="b">
@@ -5975,7 +6001,7 @@
       <c r="I139" t="s">
         <v>327</v>
       </c>
-      <c r="J139" s="1">
+      <c r="J139" s="2">
         <v>46568</v>
       </c>
       <c r="K139" t="b">
@@ -6010,7 +6036,7 @@
       <c r="I140" t="s">
         <v>328</v>
       </c>
-      <c r="J140" s="1">
+      <c r="J140" s="2">
         <v>46578</v>
       </c>
       <c r="K140" t="b">
@@ -6045,7 +6071,7 @@
       <c r="I141" t="s">
         <v>328</v>
       </c>
-      <c r="J141" s="1">
+      <c r="J141" s="2">
         <v>46592</v>
       </c>
       <c r="K141" t="b">
@@ -6080,7 +6106,7 @@
       <c r="I142" t="s">
         <v>328</v>
       </c>
-      <c r="J142" s="1">
+      <c r="J142" s="2">
         <v>46592</v>
       </c>
       <c r="K142" t="b">
@@ -6115,7 +6141,7 @@
       <c r="I143" t="s">
         <v>329</v>
       </c>
-      <c r="J143" s="1">
+      <c r="J143" s="2">
         <v>46212</v>
       </c>
       <c r="K143" t="b">
@@ -6150,7 +6176,7 @@
       <c r="I144" t="s">
         <v>330</v>
       </c>
-      <c r="J144" s="1">
+      <c r="J144" s="2">
         <v>46225</v>
       </c>
       <c r="K144" t="b">
@@ -6185,7 +6211,7 @@
       <c r="I145" t="s">
         <v>331</v>
       </c>
-      <c r="J145" s="1">
+      <c r="J145" s="2">
         <v>46263</v>
       </c>
       <c r="K145" t="b">
@@ -6217,7 +6243,7 @@
       <c r="H146">
         <v>-1476</v>
       </c>
-      <c r="J146" s="1">
+      <c r="J146" s="2">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -6249,7 +6275,7 @@
       <c r="H147">
         <v>-1469</v>
       </c>
-      <c r="J147" s="1">
+      <c r="J147" s="2">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -6281,7 +6307,7 @@
       <c r="H148">
         <v>-1186</v>
       </c>
-      <c r="J148" s="1">
+      <c r="J148" s="2">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -6313,7 +6339,7 @@
       <c r="H149">
         <v>-1048</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="2">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -6345,7 +6371,7 @@
       <c r="H150">
         <v>-980</v>
       </c>
-      <c r="J150" s="1">
+      <c r="J150" s="2">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -6377,7 +6403,7 @@
       <c r="H151">
         <v>-961</v>
       </c>
-      <c r="J151" s="1">
+      <c r="J151" s="2">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -6409,7 +6435,7 @@
       <c r="H152">
         <v>-252</v>
       </c>
-      <c r="J152" s="1">
+      <c r="J152" s="2">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -6441,7 +6467,7 @@
       <c r="H153">
         <v>3</v>
       </c>
-      <c r="J153" s="1">
+      <c r="J153" s="2">
         <v>46265</v>
       </c>
       <c r="K153" t="b">
@@ -6473,7 +6499,7 @@
       <c r="H154">
         <v>3</v>
       </c>
-      <c r="J154" s="1">
+      <c r="J154" s="2">
         <v>46265</v>
       </c>
       <c r="K154" t="b">
@@ -6505,7 +6531,7 @@
       <c r="H155">
         <v>43</v>
       </c>
-      <c r="J155" s="1">
+      <c r="J155" s="2">
         <v>46440</v>
       </c>
       <c r="K155" t="b">
@@ -6537,7 +6563,7 @@
       <c r="H156">
         <v>43</v>
       </c>
-      <c r="J156" s="1">
+      <c r="J156" s="2">
         <v>46440</v>
       </c>
       <c r="K156" t="b">
@@ -6569,7 +6595,7 @@
       <c r="H157">
         <v>72</v>
       </c>
-      <c r="J157" s="1">
+      <c r="J157" s="2">
         <v>46289</v>
       </c>
       <c r="K157" t="b">
@@ -6601,7 +6627,7 @@
       <c r="H158">
         <v>72</v>
       </c>
-      <c r="J158" s="1">
+      <c r="J158" s="2">
         <v>46289</v>
       </c>
       <c r="K158" t="b">
@@ -6633,7 +6659,7 @@
       <c r="H159">
         <v>81</v>
       </c>
-      <c r="J159" s="1">
+      <c r="J159" s="2">
         <v>46405</v>
       </c>
       <c r="K159" t="b">
@@ -6665,7 +6691,7 @@
       <c r="H160">
         <v>102</v>
       </c>
-      <c r="J160" s="1">
+      <c r="J160" s="2">
         <v>46463</v>
       </c>
       <c r="K160" t="b">
@@ -6697,7 +6723,7 @@
       <c r="H161">
         <v>109</v>
       </c>
-      <c r="J161" s="1">
+      <c r="J161" s="2">
         <v>46353</v>
       </c>
       <c r="K161" t="b">
@@ -6729,7 +6755,7 @@
       <c r="H162">
         <v>127</v>
       </c>
-      <c r="J162" s="1">
+      <c r="J162" s="2">
         <v>46417</v>
       </c>
       <c r="K162" t="b">
@@ -6761,7 +6787,7 @@
       <c r="H163">
         <v>152</v>
       </c>
-      <c r="J163" s="1">
+      <c r="J163" s="2">
         <v>46271</v>
       </c>
       <c r="K163" t="b">
@@ -6793,7 +6819,7 @@
       <c r="H164">
         <v>152</v>
       </c>
-      <c r="J164" s="1">
+      <c r="J164" s="2">
         <v>46271</v>
       </c>
       <c r="K164" t="b">
@@ -6825,7 +6851,7 @@
       <c r="H165">
         <v>153</v>
       </c>
-      <c r="J165" s="1">
+      <c r="J165" s="2">
         <v>46458</v>
       </c>
       <c r="K165" t="b">
@@ -6857,7 +6883,7 @@
       <c r="H166">
         <v>158</v>
       </c>
-      <c r="J166" s="1">
+      <c r="J166" s="2">
         <v>46381</v>
       </c>
       <c r="K166" t="b">
@@ -6889,7 +6915,7 @@
       <c r="H167">
         <v>163</v>
       </c>
-      <c r="J167" s="1">
+      <c r="J167" s="2">
         <v>46592</v>
       </c>
       <c r="K167" t="b">
@@ -6921,7 +6947,7 @@
       <c r="H168">
         <v>167</v>
       </c>
-      <c r="J168" s="1">
+      <c r="J168" s="2">
         <v>46441</v>
       </c>
       <c r="K168" t="b">
@@ -6953,7 +6979,7 @@
       <c r="H169">
         <v>169</v>
       </c>
-      <c r="J169" s="1">
+      <c r="J169" s="2">
         <v>46391</v>
       </c>
       <c r="K169" t="b">
@@ -6985,7 +7011,7 @@
       <c r="H170">
         <v>184</v>
       </c>
-      <c r="J170" s="1">
+      <c r="J170" s="2">
         <v>46385</v>
       </c>
       <c r="K170" t="b">
@@ -7017,7 +7043,7 @@
       <c r="H171">
         <v>186</v>
       </c>
-      <c r="J171" s="1">
+      <c r="J171" s="2">
         <v>46387</v>
       </c>
       <c r="K171" t="b">
@@ -7049,7 +7075,7 @@
       <c r="H172">
         <v>206</v>
       </c>
-      <c r="J172" s="1">
+      <c r="J172" s="2">
         <v>46399</v>
       </c>
       <c r="K172" t="b">
@@ -7081,7 +7107,7 @@
       <c r="H173">
         <v>206</v>
       </c>
-      <c r="J173" s="1">
+      <c r="J173" s="2">
         <v>46399</v>
       </c>
       <c r="K173" t="b">
@@ -7113,7 +7139,7 @@
       <c r="H174">
         <v>234</v>
       </c>
-      <c r="J174" s="1">
+      <c r="J174" s="2">
         <v>46458</v>
       </c>
       <c r="K174" t="b">
@@ -7145,7 +7171,7 @@
       <c r="H175">
         <v>248</v>
       </c>
-      <c r="J175" s="1">
+      <c r="J175" s="2">
         <v>46528</v>
       </c>
       <c r="K175" t="b">
@@ -7177,7 +7203,7 @@
       <c r="H176">
         <v>317</v>
       </c>
-      <c r="J176" s="1">
+      <c r="J176" s="2">
         <v>46540</v>
       </c>
       <c r="K176" t="b">
@@ -7209,7 +7235,7 @@
       <c r="H177">
         <v>340</v>
       </c>
-      <c r="J177" s="1">
+      <c r="J177" s="2">
         <v>46547</v>
       </c>
       <c r="K177" t="b">
@@ -7241,7 +7267,7 @@
       <c r="H178">
         <v>364</v>
       </c>
-      <c r="J178" s="1">
+      <c r="J178" s="2">
         <v>46557</v>
       </c>
       <c r="K178" t="b">
@@ -7273,7 +7299,7 @@
       <c r="H179">
         <v>368</v>
       </c>
-      <c r="J179" s="1">
+      <c r="J179" s="2">
         <v>46571</v>
       </c>
       <c r="K179" t="b">
@@ -7305,7 +7331,7 @@
       <c r="H180">
         <v>368</v>
       </c>
-      <c r="J180" s="1">
+      <c r="J180" s="2">
         <v>46571</v>
       </c>
       <c r="K180" t="b">
@@ -7337,7 +7363,7 @@
       <c r="H181">
         <v>370</v>
       </c>
-      <c r="J181" s="1">
+      <c r="J181" s="2">
         <v>46562</v>
       </c>
       <c r="K181" t="b">
@@ -7369,7 +7395,7 @@
       <c r="H182">
         <v>385</v>
       </c>
-      <c r="J182" s="1">
+      <c r="J182" s="2">
         <v>46574</v>
       </c>
       <c r="K182" t="b">
@@ -7401,7 +7427,7 @@
       <c r="H183">
         <v>385</v>
       </c>
-      <c r="J183" s="1">
+      <c r="J183" s="2">
         <v>46574</v>
       </c>
       <c r="K183" t="b">
@@ -7433,7 +7459,7 @@
       <c r="H184">
         <v>417</v>
       </c>
-      <c r="J184" s="1">
+      <c r="J184" s="2">
         <v>46578</v>
       </c>
       <c r="K184" t="b">
@@ -7465,7 +7491,7 @@
       <c r="H185">
         <v>721</v>
       </c>
-      <c r="J185" s="1">
+      <c r="J185" s="2">
         <v>46345</v>
       </c>
       <c r="K185" t="b">
@@ -7497,7 +7523,7 @@
       <c r="H186">
         <v>721</v>
       </c>
-      <c r="J186" s="1">
+      <c r="J186" s="2">
         <v>46345</v>
       </c>
       <c r="K186" t="b">
@@ -7529,7 +7555,7 @@
       <c r="H187">
         <v>850</v>
       </c>
-      <c r="J187" s="1">
+      <c r="J187" s="2">
         <v>46366</v>
       </c>
       <c r="K187" t="b">
@@ -7561,7 +7587,7 @@
       <c r="H188">
         <v>850</v>
       </c>
-      <c r="J188" s="1">
+      <c r="J188" s="2">
         <v>46366</v>
       </c>
       <c r="K188" t="b">
@@ -7593,7 +7619,7 @@
       <c r="H189">
         <v>1661</v>
       </c>
-      <c r="J189" s="1">
+      <c r="J189" s="2">
         <v>46524</v>
       </c>
       <c r="K189" t="b">
@@ -7625,7 +7651,7 @@
       <c r="H190">
         <v>1661</v>
       </c>
-      <c r="J190" s="1">
+      <c r="J190" s="2">
         <v>46524</v>
       </c>
       <c r="K190" t="b">
@@ -7657,7 +7683,7 @@
       <c r="H191">
         <v>488</v>
       </c>
-      <c r="J191" s="1">
+      <c r="J191" s="2">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -7689,7 +7715,7 @@
       <c r="H192">
         <v>25565</v>
       </c>
-      <c r="J192" s="1">
+      <c r="J192" s="2">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -7721,7 +7747,7 @@
       <c r="H193">
         <v>25567</v>
       </c>
-      <c r="J193" s="1">
+      <c r="J193" s="2">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -7753,7 +7779,7 @@
       <c r="H194">
         <v>31293</v>
       </c>
-      <c r="J194" s="1">
+      <c r="J194" s="2">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -1019,16 +1019,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1044,7 +1036,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1052,30 +1044,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1375,37 +1349,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1434,7 +1408,7 @@
       <c r="H2">
         <v>-4300.3</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>39285</v>
       </c>
       <c r="K2" t="b">
@@ -1466,7 +1440,7 @@
       <c r="H3">
         <v>-2354.2</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="1">
         <v>40669</v>
       </c>
       <c r="K3" t="b">
@@ -1498,7 +1472,7 @@
       <c r="H4">
         <v>-910.7</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="1">
         <v>40669</v>
       </c>
       <c r="K4" t="b">
@@ -1530,7 +1504,7 @@
       <c r="H5">
         <v>-868</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="1">
         <v>44884</v>
       </c>
       <c r="K5" t="b">
@@ -1562,7 +1536,7 @@
       <c r="H6">
         <v>-483.8</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="1">
         <v>43855</v>
       </c>
       <c r="K6" t="b">
@@ -1594,7 +1568,7 @@
       <c r="H7">
         <v>-417</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="1">
         <v>46014</v>
       </c>
       <c r="K7" t="b">
@@ -1626,7 +1600,7 @@
       <c r="H8">
         <v>-414.2</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="1">
         <v>46014</v>
       </c>
       <c r="K8" t="b">
@@ -1658,7 +1632,7 @@
       <c r="H9">
         <v>-391.8</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="1">
         <v>42769</v>
       </c>
       <c r="K9" t="b">
@@ -1690,7 +1664,7 @@
       <c r="H10">
         <v>-391.6</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="1">
         <v>45804</v>
       </c>
       <c r="K10" t="b">
@@ -1722,7 +1696,7 @@
       <c r="H11">
         <v>-391.6</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="1">
         <v>45804</v>
       </c>
       <c r="K11" t="b">
@@ -1754,7 +1728,7 @@
       <c r="H12">
         <v>-372.9</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="1">
         <v>42821</v>
       </c>
       <c r="K12" t="b">
@@ -1786,7 +1760,7 @@
       <c r="H13">
         <v>-372.9</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="1">
         <v>46014</v>
       </c>
       <c r="K13" t="b">
@@ -1818,7 +1792,7 @@
       <c r="H14">
         <v>-372.9</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="1">
         <v>46014</v>
       </c>
       <c r="K14" t="b">
@@ -1850,7 +1824,7 @@
       <c r="H15">
         <v>-372.9</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="1">
         <v>46014</v>
       </c>
       <c r="K15" t="b">
@@ -1882,7 +1856,7 @@
       <c r="H16">
         <v>-367.8</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="1">
         <v>46017</v>
       </c>
       <c r="K16" t="b">
@@ -1914,7 +1888,7 @@
       <c r="H17">
         <v>-367.8</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="1">
         <v>46017</v>
       </c>
       <c r="K17" t="b">
@@ -1946,7 +1920,7 @@
       <c r="H18">
         <v>-347.2</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="1">
         <v>40979</v>
       </c>
       <c r="K18" t="b">
@@ -1978,7 +1952,7 @@
       <c r="H19">
         <v>-293.8</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="1">
         <v>45846</v>
       </c>
       <c r="K19" t="b">
@@ -2010,7 +1984,7 @@
       <c r="H20">
         <v>-206.4</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="1">
         <v>36669</v>
       </c>
       <c r="K20" t="b">
@@ -2042,7 +2016,7 @@
       <c r="H21">
         <v>-131.6</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="1">
         <v>46111</v>
       </c>
       <c r="K21" t="b">
@@ -2074,7 +2048,7 @@
       <c r="H22">
         <v>-131.6</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="1">
         <v>46111</v>
       </c>
       <c r="K22" t="b">
@@ -2106,7 +2080,7 @@
       <c r="H23">
         <v>-131.6</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="1">
         <v>46111</v>
       </c>
       <c r="K23" t="b">
@@ -2138,7 +2112,7 @@
       <c r="H24">
         <v>-131.6</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="1">
         <v>46111</v>
       </c>
       <c r="K24" t="b">
@@ -2170,7 +2144,7 @@
       <c r="H25">
         <v>-131.6</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>46111</v>
       </c>
       <c r="K25" t="b">
@@ -2202,7 +2176,7 @@
       <c r="H26">
         <v>-98.3</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="1">
         <v>41204</v>
       </c>
       <c r="K26" t="b">
@@ -2234,7 +2208,7 @@
       <c r="H27">
         <v>-47.2</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="1">
         <v>44011</v>
       </c>
       <c r="K27" t="b">
@@ -2266,7 +2240,7 @@
       <c r="H28">
         <v>-22.3</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="1">
         <v>46226</v>
       </c>
       <c r="K28" t="b">
@@ -2298,7 +2272,7 @@
       <c r="H29">
         <v>4.7</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="1">
         <v>46265</v>
       </c>
       <c r="K29" t="b">
@@ -2330,7 +2304,7 @@
       <c r="H30">
         <v>7.5</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="1">
         <v>46265</v>
       </c>
       <c r="K30" t="b">
@@ -2362,7 +2336,7 @@
       <c r="H31">
         <v>10</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="1">
         <v>46265</v>
       </c>
       <c r="K31" t="b">
@@ -2394,7 +2368,7 @@
       <c r="H32">
         <v>12.8</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="1">
         <v>46265</v>
       </c>
       <c r="K32" t="b">
@@ -2426,7 +2400,7 @@
       <c r="H33">
         <v>14</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="1">
         <v>46265</v>
       </c>
       <c r="K33" t="b">
@@ -2458,7 +2432,7 @@
       <c r="H34">
         <v>17.8</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="1">
         <v>46265</v>
       </c>
       <c r="K34" t="b">
@@ -2490,7 +2464,7 @@
       <c r="H35">
         <v>20.4</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="1">
         <v>46265</v>
       </c>
       <c r="K35" t="b">
@@ -2522,7 +2496,7 @@
       <c r="H36">
         <v>21.2</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="1">
         <v>46265</v>
       </c>
       <c r="K36" t="b">
@@ -2554,7 +2528,7 @@
       <c r="H37">
         <v>26.2</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>46265</v>
       </c>
       <c r="K37" t="b">
@@ -2586,7 +2560,7 @@
       <c r="H38">
         <v>33.6</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="1">
         <v>46364</v>
       </c>
       <c r="K38" t="b">
@@ -2618,7 +2592,7 @@
       <c r="H39">
         <v>42.2</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="1">
         <v>46269</v>
       </c>
       <c r="K39" t="b">
@@ -2650,7 +2624,7 @@
       <c r="H40">
         <v>42.8</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="1">
         <v>46291</v>
       </c>
       <c r="K40" t="b">
@@ -2682,7 +2656,7 @@
       <c r="H41">
         <v>45.7</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="1">
         <v>46395</v>
       </c>
       <c r="K41" t="b">
@@ -2714,7 +2688,7 @@
       <c r="H42">
         <v>47.2</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="1">
         <v>46280</v>
       </c>
       <c r="K42" t="b">
@@ -2746,7 +2720,7 @@
       <c r="H43">
         <v>48.7</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>46281</v>
       </c>
       <c r="K43" t="b">
@@ -2778,7 +2752,7 @@
       <c r="H44">
         <v>60</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="1">
         <v>46281</v>
       </c>
       <c r="K44" t="b">
@@ -2810,7 +2784,7 @@
       <c r="H45">
         <v>62.6</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="1">
         <v>46265</v>
       </c>
       <c r="K45" t="b">
@@ -2842,7 +2816,7 @@
       <c r="H46">
         <v>64.59999999999999</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="1">
         <v>46265</v>
       </c>
       <c r="K46" t="b">
@@ -2874,7 +2848,7 @@
       <c r="H47">
         <v>67.59999999999999</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="1">
         <v>46267</v>
       </c>
       <c r="K47" t="b">
@@ -2906,7 +2880,7 @@
       <c r="H48">
         <v>68.3</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="1">
         <v>46278</v>
       </c>
       <c r="K48" t="b">
@@ -2938,7 +2912,7 @@
       <c r="H49">
         <v>69.2</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>46453</v>
       </c>
       <c r="K49" t="b">
@@ -2970,7 +2944,7 @@
       <c r="H50">
         <v>69.8</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="1">
         <v>46265</v>
       </c>
       <c r="K50" t="b">
@@ -3002,7 +2976,7 @@
       <c r="H51">
         <v>69.8</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="1">
         <v>46265</v>
       </c>
       <c r="K51" t="b">
@@ -3034,7 +3008,7 @@
       <c r="H52">
         <v>72.2</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="1">
         <v>46275</v>
       </c>
       <c r="K52" t="b">
@@ -3066,7 +3040,7 @@
       <c r="H53">
         <v>72.2</v>
       </c>
-      <c r="J53" s="2">
+      <c r="J53" s="1">
         <v>46275</v>
       </c>
       <c r="K53" t="b">
@@ -3098,7 +3072,7 @@
       <c r="H54">
         <v>78.09999999999999</v>
       </c>
-      <c r="J54" s="2">
+      <c r="J54" s="1">
         <v>46265</v>
       </c>
       <c r="K54" t="b">
@@ -3130,7 +3104,7 @@
       <c r="H55">
         <v>82.8</v>
       </c>
-      <c r="J55" s="2">
+      <c r="J55" s="1">
         <v>46487</v>
       </c>
       <c r="K55" t="b">
@@ -3162,7 +3136,7 @@
       <c r="H56">
         <v>83.09999999999999</v>
       </c>
-      <c r="J56" s="2">
+      <c r="J56" s="1">
         <v>46285</v>
       </c>
       <c r="K56" t="b">
@@ -3194,7 +3168,7 @@
       <c r="H57">
         <v>84.8</v>
       </c>
-      <c r="J57" s="2">
+      <c r="J57" s="1">
         <v>46492</v>
       </c>
       <c r="K57" t="b">
@@ -3226,7 +3200,7 @@
       <c r="H58">
         <v>104.9</v>
       </c>
-      <c r="J58" s="2">
+      <c r="J58" s="1">
         <v>46297</v>
       </c>
       <c r="K58" t="b">
@@ -3258,7 +3232,7 @@
       <c r="H59">
         <v>107.6</v>
       </c>
-      <c r="J59" s="2">
+      <c r="J59" s="1">
         <v>46283</v>
       </c>
       <c r="K59" t="b">
@@ -3290,7 +3264,7 @@
       <c r="H60">
         <v>111.9</v>
       </c>
-      <c r="J60" s="2">
+      <c r="J60" s="1">
         <v>46300</v>
       </c>
       <c r="K60" t="b">
@@ -3322,7 +3296,7 @@
       <c r="H61">
         <v>111.9</v>
       </c>
-      <c r="J61" s="2">
+      <c r="J61" s="1">
         <v>46300</v>
       </c>
       <c r="K61" t="b">
@@ -3354,7 +3328,7 @@
       <c r="H62">
         <v>111.9</v>
       </c>
-      <c r="J62" s="2">
+      <c r="J62" s="1">
         <v>46300</v>
       </c>
       <c r="K62" t="b">
@@ -3386,7 +3360,7 @@
       <c r="H63">
         <v>111.9</v>
       </c>
-      <c r="J63" s="2">
+      <c r="J63" s="1">
         <v>46300</v>
       </c>
       <c r="K63" t="b">
@@ -3418,7 +3392,7 @@
       <c r="H64">
         <v>111.9</v>
       </c>
-      <c r="J64" s="2">
+      <c r="J64" s="1">
         <v>46300</v>
       </c>
       <c r="K64" t="b">
@@ -3450,7 +3424,7 @@
       <c r="H65">
         <v>128.8</v>
       </c>
-      <c r="J65" s="2">
+      <c r="J65" s="1">
         <v>46308</v>
       </c>
       <c r="K65" t="b">
@@ -3482,7 +3456,7 @@
       <c r="H66">
         <v>131.1</v>
       </c>
-      <c r="J66" s="2">
+      <c r="J66" s="1">
         <v>46336</v>
       </c>
       <c r="K66" t="b">
@@ -3514,7 +3488,7 @@
       <c r="H67">
         <v>138.4</v>
       </c>
-      <c r="J67" s="2">
+      <c r="J67" s="1">
         <v>46343</v>
       </c>
       <c r="K67" t="b">
@@ -3546,7 +3520,7 @@
       <c r="H68">
         <v>141</v>
       </c>
-      <c r="J68" s="2">
+      <c r="J68" s="1">
         <v>46350</v>
       </c>
       <c r="K68" t="b">
@@ -3578,7 +3552,7 @@
       <c r="H69">
         <v>162</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="1">
         <v>46391</v>
       </c>
       <c r="K69" t="b">
@@ -3610,7 +3584,7 @@
       <c r="H70">
         <v>167.2</v>
       </c>
-      <c r="J70" s="2">
+      <c r="J70" s="1">
         <v>46330</v>
       </c>
       <c r="K70" t="b">
@@ -3642,7 +3616,7 @@
       <c r="H71">
         <v>177.4</v>
       </c>
-      <c r="J71" s="2">
+      <c r="J71" s="1">
         <v>46418</v>
       </c>
       <c r="K71" t="b">
@@ -3674,7 +3648,7 @@
       <c r="H72">
         <v>200</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J72" s="1">
         <v>46356</v>
       </c>
       <c r="K72" t="b">
@@ -3706,7 +3680,7 @@
       <c r="H73">
         <v>203.6</v>
       </c>
-      <c r="J73" s="2">
+      <c r="J73" s="1">
         <v>46436</v>
       </c>
       <c r="K73" t="b">
@@ -3738,7 +3712,7 @@
       <c r="H74">
         <v>221.2</v>
       </c>
-      <c r="J74" s="2">
+      <c r="J74" s="1">
         <v>46426</v>
       </c>
       <c r="K74" t="b">
@@ -3770,7 +3744,7 @@
       <c r="H75">
         <v>240.8</v>
       </c>
-      <c r="J75" s="2">
+      <c r="J75" s="1">
         <v>46450</v>
       </c>
       <c r="K75" t="b">
@@ -3802,7 +3776,7 @@
       <c r="H76">
         <v>245.8</v>
       </c>
-      <c r="J76" s="2">
+      <c r="J76" s="1">
         <v>46452</v>
       </c>
       <c r="K76" t="b">
@@ -3834,7 +3808,7 @@
       <c r="H77">
         <v>263.4</v>
       </c>
-      <c r="J77" s="2">
+      <c r="J77" s="1">
         <v>46322</v>
       </c>
       <c r="K77" t="b">
@@ -3866,7 +3840,7 @@
       <c r="H78">
         <v>275.2</v>
       </c>
-      <c r="J78" s="2">
+      <c r="J78" s="1">
         <v>46433</v>
       </c>
       <c r="K78" t="b">
@@ -3901,7 +3875,7 @@
       <c r="I79" t="s">
         <v>311</v>
       </c>
-      <c r="J79" s="2">
+      <c r="J79" s="1">
         <v>36557</v>
       </c>
       <c r="K79" t="b">
@@ -3936,7 +3910,7 @@
       <c r="I80" t="s">
         <v>312</v>
       </c>
-      <c r="J80" s="2">
+      <c r="J80" s="1">
         <v>41275</v>
       </c>
       <c r="K80" t="b">
@@ -3971,7 +3945,7 @@
       <c r="I81" t="s">
         <v>313</v>
       </c>
-      <c r="J81" s="2">
+      <c r="J81" s="1">
         <v>45380</v>
       </c>
       <c r="K81" t="b">
@@ -4006,7 +3980,7 @@
       <c r="I82" t="s">
         <v>314</v>
       </c>
-      <c r="J82" s="2">
+      <c r="J82" s="1">
         <v>45421</v>
       </c>
       <c r="K82" t="b">
@@ -4041,7 +4015,7 @@
       <c r="I83" t="s">
         <v>314</v>
       </c>
-      <c r="J83" s="2">
+      <c r="J83" s="1">
         <v>45428</v>
       </c>
       <c r="K83" t="b">
@@ -4076,7 +4050,7 @@
       <c r="I84" t="s">
         <v>315</v>
       </c>
-      <c r="J84" s="2">
+      <c r="J84" s="1">
         <v>45490</v>
       </c>
       <c r="K84" t="b">
@@ -4111,7 +4085,7 @@
       <c r="I85" t="s">
         <v>316</v>
       </c>
-      <c r="J85" s="2">
+      <c r="J85" s="1">
         <v>45566</v>
       </c>
       <c r="K85" t="b">
@@ -4146,7 +4120,7 @@
       <c r="I86" t="s">
         <v>317</v>
       </c>
-      <c r="J86" s="2">
+      <c r="J86" s="1">
         <v>45986</v>
       </c>
       <c r="K86" t="b">
@@ -4181,7 +4155,7 @@
       <c r="I87" t="s">
         <v>318</v>
       </c>
-      <c r="J87" s="2">
+      <c r="J87" s="1">
         <v>46284</v>
       </c>
       <c r="K87" t="b">
@@ -4216,7 +4190,7 @@
       <c r="I88" t="s">
         <v>319</v>
       </c>
-      <c r="J88" s="2">
+      <c r="J88" s="1">
         <v>46305</v>
       </c>
       <c r="K88" t="b">
@@ -4251,7 +4225,7 @@
       <c r="I89" t="s">
         <v>319</v>
       </c>
-      <c r="J89" s="2">
+      <c r="J89" s="1">
         <v>46310</v>
       </c>
       <c r="K89" t="b">
@@ -4286,7 +4260,7 @@
       <c r="I90" t="s">
         <v>319</v>
       </c>
-      <c r="J90" s="2">
+      <c r="J90" s="1">
         <v>46317</v>
       </c>
       <c r="K90" t="b">
@@ -4321,7 +4295,7 @@
       <c r="I91" t="s">
         <v>319</v>
       </c>
-      <c r="J91" s="2">
+      <c r="J91" s="1">
         <v>46319</v>
       </c>
       <c r="K91" t="b">
@@ -4356,7 +4330,7 @@
       <c r="I92" t="s">
         <v>320</v>
       </c>
-      <c r="J92" s="2">
+      <c r="J92" s="1">
         <v>46333</v>
       </c>
       <c r="K92" t="b">
@@ -4391,7 +4365,7 @@
       <c r="I93" t="s">
         <v>320</v>
       </c>
-      <c r="J93" s="2">
+      <c r="J93" s="1">
         <v>46338</v>
       </c>
       <c r="K93" t="b">
@@ -4426,7 +4400,7 @@
       <c r="I94" t="s">
         <v>320</v>
       </c>
-      <c r="J94" s="2">
+      <c r="J94" s="1">
         <v>46338</v>
       </c>
       <c r="K94" t="b">
@@ -4461,7 +4435,7 @@
       <c r="I95" t="s">
         <v>320</v>
       </c>
-      <c r="J95" s="2">
+      <c r="J95" s="1">
         <v>46341</v>
       </c>
       <c r="K95" t="b">
@@ -4496,7 +4470,7 @@
       <c r="I96" t="s">
         <v>320</v>
       </c>
-      <c r="J96" s="2">
+      <c r="J96" s="1">
         <v>46344</v>
       </c>
       <c r="K96" t="b">
@@ -4531,7 +4505,7 @@
       <c r="I97" t="s">
         <v>321</v>
       </c>
-      <c r="J97" s="2">
+      <c r="J97" s="1">
         <v>46360</v>
       </c>
       <c r="K97" t="b">
@@ -4566,7 +4540,7 @@
       <c r="I98" t="s">
         <v>321</v>
       </c>
-      <c r="J98" s="2">
+      <c r="J98" s="1">
         <v>46360</v>
       </c>
       <c r="K98" t="b">
@@ -4601,7 +4575,7 @@
       <c r="I99" t="s">
         <v>321</v>
       </c>
-      <c r="J99" s="2">
+      <c r="J99" s="1">
         <v>46367</v>
       </c>
       <c r="K99" t="b">
@@ -4636,7 +4610,7 @@
       <c r="I100" t="s">
         <v>321</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="1">
         <v>46375</v>
       </c>
       <c r="K100" t="b">
@@ -4671,7 +4645,7 @@
       <c r="I101" t="s">
         <v>321</v>
       </c>
-      <c r="J101" s="2">
+      <c r="J101" s="1">
         <v>46387</v>
       </c>
       <c r="K101" t="b">
@@ -4706,7 +4680,7 @@
       <c r="I102" t="s">
         <v>321</v>
       </c>
-      <c r="J102" s="2">
+      <c r="J102" s="1">
         <v>46387</v>
       </c>
       <c r="K102" t="b">
@@ -4741,7 +4715,7 @@
       <c r="I103" t="s">
         <v>321</v>
       </c>
-      <c r="J103" s="2">
+      <c r="J103" s="1">
         <v>46387</v>
       </c>
       <c r="K103" t="b">
@@ -4776,7 +4750,7 @@
       <c r="I104" t="s">
         <v>321</v>
       </c>
-      <c r="J104" s="2">
+      <c r="J104" s="1">
         <v>46388</v>
       </c>
       <c r="K104" t="b">
@@ -4811,7 +4785,7 @@
       <c r="I105" t="s">
         <v>322</v>
       </c>
-      <c r="J105" s="2">
+      <c r="J105" s="1">
         <v>46401</v>
       </c>
       <c r="K105" t="b">
@@ -4846,7 +4820,7 @@
       <c r="I106" t="s">
         <v>322</v>
       </c>
-      <c r="J106" s="2">
+      <c r="J106" s="1">
         <v>46401</v>
       </c>
       <c r="K106" t="b">
@@ -4881,7 +4855,7 @@
       <c r="I107" t="s">
         <v>322</v>
       </c>
-      <c r="J107" s="2">
+      <c r="J107" s="1">
         <v>46401</v>
       </c>
       <c r="K107" t="b">
@@ -4916,7 +4890,7 @@
       <c r="I108" t="s">
         <v>322</v>
       </c>
-      <c r="J108" s="2">
+      <c r="J108" s="1">
         <v>46412</v>
       </c>
       <c r="K108" t="b">
@@ -4951,7 +4925,7 @@
       <c r="I109" t="s">
         <v>322</v>
       </c>
-      <c r="J109" s="2">
+      <c r="J109" s="1">
         <v>46412</v>
       </c>
       <c r="K109" t="b">
@@ -4986,7 +4960,7 @@
       <c r="I110" t="s">
         <v>322</v>
       </c>
-      <c r="J110" s="2">
+      <c r="J110" s="1">
         <v>46412</v>
       </c>
       <c r="K110" t="b">
@@ -5021,7 +4995,7 @@
       <c r="I111" t="s">
         <v>323</v>
       </c>
-      <c r="J111" s="2">
+      <c r="J111" s="1">
         <v>46424</v>
       </c>
       <c r="K111" t="b">
@@ -5056,7 +5030,7 @@
       <c r="I112" t="s">
         <v>323</v>
       </c>
-      <c r="J112" s="2">
+      <c r="J112" s="1">
         <v>46437</v>
       </c>
       <c r="K112" t="b">
@@ -5091,7 +5065,7 @@
       <c r="I113" t="s">
         <v>323</v>
       </c>
-      <c r="J113" s="2">
+      <c r="J113" s="1">
         <v>46451</v>
       </c>
       <c r="K113" t="b">
@@ -5126,7 +5100,7 @@
       <c r="I114" t="s">
         <v>323</v>
       </c>
-      <c r="J114" s="2">
+      <c r="J114" s="1">
         <v>46451</v>
       </c>
       <c r="K114" t="b">
@@ -5161,7 +5135,7 @@
       <c r="I115" t="s">
         <v>324</v>
       </c>
-      <c r="J115" s="2">
+      <c r="J115" s="1">
         <v>46455</v>
       </c>
       <c r="K115" t="b">
@@ -5196,7 +5170,7 @@
       <c r="I116" t="s">
         <v>324</v>
       </c>
-      <c r="J116" s="2">
+      <c r="J116" s="1">
         <v>46456</v>
       </c>
       <c r="K116" t="b">
@@ -5231,7 +5205,7 @@
       <c r="I117" t="s">
         <v>324</v>
       </c>
-      <c r="J117" s="2">
+      <c r="J117" s="1">
         <v>46457</v>
       </c>
       <c r="K117" t="b">
@@ -5266,7 +5240,7 @@
       <c r="I118" t="s">
         <v>324</v>
       </c>
-      <c r="J118" s="2">
+      <c r="J118" s="1">
         <v>46464</v>
       </c>
       <c r="K118" t="b">
@@ -5301,7 +5275,7 @@
       <c r="I119" t="s">
         <v>324</v>
       </c>
-      <c r="J119" s="2">
+      <c r="J119" s="1">
         <v>46470</v>
       </c>
       <c r="K119" t="b">
@@ -5336,7 +5310,7 @@
       <c r="I120" t="s">
         <v>325</v>
       </c>
-      <c r="J120" s="2">
+      <c r="J120" s="1">
         <v>46485</v>
       </c>
       <c r="K120" t="b">
@@ -5371,7 +5345,7 @@
       <c r="I121" t="s">
         <v>325</v>
       </c>
-      <c r="J121" s="2">
+      <c r="J121" s="1">
         <v>46499</v>
       </c>
       <c r="K121" t="b">
@@ -5406,7 +5380,7 @@
       <c r="I122" t="s">
         <v>325</v>
       </c>
-      <c r="J122" s="2">
+      <c r="J122" s="1">
         <v>46504</v>
       </c>
       <c r="K122" t="b">
@@ -5441,7 +5415,7 @@
       <c r="I123" t="s">
         <v>325</v>
       </c>
-      <c r="J123" s="2">
+      <c r="J123" s="1">
         <v>46504</v>
       </c>
       <c r="K123" t="b">
@@ -5476,7 +5450,7 @@
       <c r="I124" t="s">
         <v>325</v>
       </c>
-      <c r="J124" s="2">
+      <c r="J124" s="1">
         <v>46507</v>
       </c>
       <c r="K124" t="b">
@@ -5511,7 +5485,7 @@
       <c r="I125" t="s">
         <v>325</v>
       </c>
-      <c r="J125" s="2">
+      <c r="J125" s="1">
         <v>46508</v>
       </c>
       <c r="K125" t="b">
@@ -5546,7 +5520,7 @@
       <c r="I126" t="s">
         <v>325</v>
       </c>
-      <c r="J126" s="2">
+      <c r="J126" s="1">
         <v>46512</v>
       </c>
       <c r="K126" t="b">
@@ -5581,7 +5555,7 @@
       <c r="I127" t="s">
         <v>326</v>
       </c>
-      <c r="J127" s="2">
+      <c r="J127" s="1">
         <v>46512</v>
       </c>
       <c r="K127" t="b">
@@ -5616,7 +5590,7 @@
       <c r="I128" t="s">
         <v>326</v>
       </c>
-      <c r="J128" s="2">
+      <c r="J128" s="1">
         <v>46528</v>
       </c>
       <c r="K128" t="b">
@@ -5651,7 +5625,7 @@
       <c r="I129" t="s">
         <v>326</v>
       </c>
-      <c r="J129" s="2">
+      <c r="J129" s="1">
         <v>46529</v>
       </c>
       <c r="K129" t="b">
@@ -5686,7 +5660,7 @@
       <c r="I130" t="s">
         <v>326</v>
       </c>
-      <c r="J130" s="2">
+      <c r="J130" s="1">
         <v>46537</v>
       </c>
       <c r="K130" t="b">
@@ -5721,7 +5695,7 @@
       <c r="I131" t="s">
         <v>327</v>
       </c>
-      <c r="J131" s="2">
+      <c r="J131" s="1">
         <v>46546</v>
       </c>
       <c r="K131" t="b">
@@ -5756,7 +5730,7 @@
       <c r="I132" t="s">
         <v>327</v>
       </c>
-      <c r="J132" s="2">
+      <c r="J132" s="1">
         <v>46547</v>
       </c>
       <c r="K132" t="b">
@@ -5791,7 +5765,7 @@
       <c r="I133" t="s">
         <v>327</v>
       </c>
-      <c r="J133" s="2">
+      <c r="J133" s="1">
         <v>46547</v>
       </c>
       <c r="K133" t="b">
@@ -5826,7 +5800,7 @@
       <c r="I134" t="s">
         <v>327</v>
       </c>
-      <c r="J134" s="2">
+      <c r="J134" s="1">
         <v>46547</v>
       </c>
       <c r="K134" t="b">
@@ -5861,7 +5835,7 @@
       <c r="I135" t="s">
         <v>327</v>
       </c>
-      <c r="J135" s="2">
+      <c r="J135" s="1">
         <v>46551</v>
       </c>
       <c r="K135" t="b">
@@ -5896,7 +5870,7 @@
       <c r="I136" t="s">
         <v>327</v>
       </c>
-      <c r="J136" s="2">
+      <c r="J136" s="1">
         <v>46560</v>
       </c>
       <c r="K136" t="b">
@@ -5931,7 +5905,7 @@
       <c r="I137" t="s">
         <v>327</v>
       </c>
-      <c r="J137" s="2">
+      <c r="J137" s="1">
         <v>46564</v>
       </c>
       <c r="K137" t="b">
@@ -5966,7 +5940,7 @@
       <c r="I138" t="s">
         <v>327</v>
       </c>
-      <c r="J138" s="2">
+      <c r="J138" s="1">
         <v>46567</v>
       </c>
       <c r="K138" t="b">
@@ -6001,7 +5975,7 @@
       <c r="I139" t="s">
         <v>327</v>
       </c>
-      <c r="J139" s="2">
+      <c r="J139" s="1">
         <v>46568</v>
       </c>
       <c r="K139" t="b">
@@ -6036,7 +6010,7 @@
       <c r="I140" t="s">
         <v>328</v>
       </c>
-      <c r="J140" s="2">
+      <c r="J140" s="1">
         <v>46578</v>
       </c>
       <c r="K140" t="b">
@@ -6071,7 +6045,7 @@
       <c r="I141" t="s">
         <v>328</v>
       </c>
-      <c r="J141" s="2">
+      <c r="J141" s="1">
         <v>46592</v>
       </c>
       <c r="K141" t="b">
@@ -6106,7 +6080,7 @@
       <c r="I142" t="s">
         <v>328</v>
       </c>
-      <c r="J142" s="2">
+      <c r="J142" s="1">
         <v>46592</v>
       </c>
       <c r="K142" t="b">
@@ -6141,7 +6115,7 @@
       <c r="I143" t="s">
         <v>329</v>
       </c>
-      <c r="J143" s="2">
+      <c r="J143" s="1">
         <v>46212</v>
       </c>
       <c r="K143" t="b">
@@ -6176,7 +6150,7 @@
       <c r="I144" t="s">
         <v>330</v>
       </c>
-      <c r="J144" s="2">
+      <c r="J144" s="1">
         <v>46225</v>
       </c>
       <c r="K144" t="b">
@@ -6211,7 +6185,7 @@
       <c r="I145" t="s">
         <v>331</v>
       </c>
-      <c r="J145" s="2">
+      <c r="J145" s="1">
         <v>46263</v>
       </c>
       <c r="K145" t="b">
@@ -6243,7 +6217,7 @@
       <c r="H146">
         <v>-1476</v>
       </c>
-      <c r="J146" s="2">
+      <c r="J146" s="1">
         <v>43773</v>
       </c>
       <c r="K146" t="b">
@@ -6275,7 +6249,7 @@
       <c r="H147">
         <v>-1469</v>
       </c>
-      <c r="J147" s="2">
+      <c r="J147" s="1">
         <v>43773</v>
       </c>
       <c r="K147" t="b">
@@ -6307,7 +6281,7 @@
       <c r="H148">
         <v>-1186</v>
       </c>
-      <c r="J148" s="2">
+      <c r="J148" s="1">
         <v>45295</v>
       </c>
       <c r="K148" t="b">
@@ -6339,7 +6313,7 @@
       <c r="H149">
         <v>-1048</v>
       </c>
-      <c r="J149" s="2">
+      <c r="J149" s="1">
         <v>45617</v>
       </c>
       <c r="K149" t="b">
@@ -6371,7 +6345,7 @@
       <c r="H150">
         <v>-980</v>
       </c>
-      <c r="J150" s="2">
+      <c r="J150" s="1">
         <v>45677</v>
       </c>
       <c r="K150" t="b">
@@ -6403,7 +6377,7 @@
       <c r="H151">
         <v>-961</v>
       </c>
-      <c r="J151" s="2">
+      <c r="J151" s="1">
         <v>44944</v>
       </c>
       <c r="K151" t="b">
@@ -6435,7 +6409,7 @@
       <c r="H152">
         <v>-252</v>
       </c>
-      <c r="J152" s="2">
+      <c r="J152" s="1">
         <v>46092</v>
       </c>
       <c r="K152" t="b">
@@ -6467,7 +6441,7 @@
       <c r="H153">
         <v>3</v>
       </c>
-      <c r="J153" s="2">
+      <c r="J153" s="1">
         <v>46265</v>
       </c>
       <c r="K153" t="b">
@@ -6499,7 +6473,7 @@
       <c r="H154">
         <v>3</v>
       </c>
-      <c r="J154" s="2">
+      <c r="J154" s="1">
         <v>46265</v>
       </c>
       <c r="K154" t="b">
@@ -6531,7 +6505,7 @@
       <c r="H155">
         <v>43</v>
       </c>
-      <c r="J155" s="2">
+      <c r="J155" s="1">
         <v>46440</v>
       </c>
       <c r="K155" t="b">
@@ -6563,7 +6537,7 @@
       <c r="H156">
         <v>43</v>
       </c>
-      <c r="J156" s="2">
+      <c r="J156" s="1">
         <v>46440</v>
       </c>
       <c r="K156" t="b">
@@ -6595,7 +6569,7 @@
       <c r="H157">
         <v>72</v>
       </c>
-      <c r="J157" s="2">
+      <c r="J157" s="1">
         <v>46289</v>
       </c>
       <c r="K157" t="b">
@@ -6627,7 +6601,7 @@
       <c r="H158">
         <v>72</v>
       </c>
-      <c r="J158" s="2">
+      <c r="J158" s="1">
         <v>46289</v>
       </c>
       <c r="K158" t="b">
@@ -6659,7 +6633,7 @@
       <c r="H159">
         <v>81</v>
       </c>
-      <c r="J159" s="2">
+      <c r="J159" s="1">
         <v>46405</v>
       </c>
       <c r="K159" t="b">
@@ -6691,7 +6665,7 @@
       <c r="H160">
         <v>102</v>
       </c>
-      <c r="J160" s="2">
+      <c r="J160" s="1">
         <v>46463</v>
       </c>
       <c r="K160" t="b">
@@ -6723,7 +6697,7 @@
       <c r="H161">
         <v>109</v>
       </c>
-      <c r="J161" s="2">
+      <c r="J161" s="1">
         <v>46353</v>
       </c>
       <c r="K161" t="b">
@@ -6755,7 +6729,7 @@
       <c r="H162">
         <v>127</v>
       </c>
-      <c r="J162" s="2">
+      <c r="J162" s="1">
         <v>46417</v>
       </c>
       <c r="K162" t="b">
@@ -6787,7 +6761,7 @@
       <c r="H163">
         <v>152</v>
       </c>
-      <c r="J163" s="2">
+      <c r="J163" s="1">
         <v>46271</v>
       </c>
       <c r="K163" t="b">
@@ -6819,7 +6793,7 @@
       <c r="H164">
         <v>152</v>
       </c>
-      <c r="J164" s="2">
+      <c r="J164" s="1">
         <v>46271</v>
       </c>
       <c r="K164" t="b">
@@ -6851,7 +6825,7 @@
       <c r="H165">
         <v>153</v>
       </c>
-      <c r="J165" s="2">
+      <c r="J165" s="1">
         <v>46458</v>
       </c>
       <c r="K165" t="b">
@@ -6883,7 +6857,7 @@
       <c r="H166">
         <v>158</v>
       </c>
-      <c r="J166" s="2">
+      <c r="J166" s="1">
         <v>46381</v>
       </c>
       <c r="K166" t="b">
@@ -6915,7 +6889,7 @@
       <c r="H167">
         <v>163</v>
       </c>
-      <c r="J167" s="2">
+      <c r="J167" s="1">
         <v>46592</v>
       </c>
       <c r="K167" t="b">
@@ -6947,7 +6921,7 @@
       <c r="H168">
         <v>167</v>
       </c>
-      <c r="J168" s="2">
+      <c r="J168" s="1">
         <v>46441</v>
       </c>
       <c r="K168" t="b">
@@ -6979,7 +6953,7 @@
       <c r="H169">
         <v>169</v>
       </c>
-      <c r="J169" s="2">
+      <c r="J169" s="1">
         <v>46391</v>
       </c>
       <c r="K169" t="b">
@@ -7011,7 +6985,7 @@
       <c r="H170">
         <v>184</v>
       </c>
-      <c r="J170" s="2">
+      <c r="J170" s="1">
         <v>46385</v>
       </c>
       <c r="K170" t="b">
@@ -7043,7 +7017,7 @@
       <c r="H171">
         <v>186</v>
       </c>
-      <c r="J171" s="2">
+      <c r="J171" s="1">
         <v>46387</v>
       </c>
       <c r="K171" t="b">
@@ -7075,7 +7049,7 @@
       <c r="H172">
         <v>206</v>
       </c>
-      <c r="J172" s="2">
+      <c r="J172" s="1">
         <v>46399</v>
       </c>
       <c r="K172" t="b">
@@ -7107,7 +7081,7 @@
       <c r="H173">
         <v>206</v>
       </c>
-      <c r="J173" s="2">
+      <c r="J173" s="1">
         <v>46399</v>
       </c>
       <c r="K173" t="b">
@@ -7139,7 +7113,7 @@
       <c r="H174">
         <v>234</v>
       </c>
-      <c r="J174" s="2">
+      <c r="J174" s="1">
         <v>46458</v>
       </c>
       <c r="K174" t="b">
@@ -7171,7 +7145,7 @@
       <c r="H175">
         <v>248</v>
       </c>
-      <c r="J175" s="2">
+      <c r="J175" s="1">
         <v>46528</v>
       </c>
       <c r="K175" t="b">
@@ -7203,7 +7177,7 @@
       <c r="H176">
         <v>317</v>
       </c>
-      <c r="J176" s="2">
+      <c r="J176" s="1">
         <v>46540</v>
       </c>
       <c r="K176" t="b">
@@ -7235,7 +7209,7 @@
       <c r="H177">
         <v>340</v>
       </c>
-      <c r="J177" s="2">
+      <c r="J177" s="1">
         <v>46547</v>
       </c>
       <c r="K177" t="b">
@@ -7267,7 +7241,7 @@
       <c r="H178">
         <v>364</v>
       </c>
-      <c r="J178" s="2">
+      <c r="J178" s="1">
         <v>46557</v>
       </c>
       <c r="K178" t="b">
@@ -7299,7 +7273,7 @@
       <c r="H179">
         <v>368</v>
       </c>
-      <c r="J179" s="2">
+      <c r="J179" s="1">
         <v>46571</v>
       </c>
       <c r="K179" t="b">
@@ -7331,7 +7305,7 @@
       <c r="H180">
         <v>368</v>
       </c>
-      <c r="J180" s="2">
+      <c r="J180" s="1">
         <v>46571</v>
       </c>
       <c r="K180" t="b">
@@ -7363,7 +7337,7 @@
       <c r="H181">
         <v>370</v>
       </c>
-      <c r="J181" s="2">
+      <c r="J181" s="1">
         <v>46562</v>
       </c>
       <c r="K181" t="b">
@@ -7395,7 +7369,7 @@
       <c r="H182">
         <v>385</v>
       </c>
-      <c r="J182" s="2">
+      <c r="J182" s="1">
         <v>46574</v>
       </c>
       <c r="K182" t="b">
@@ -7427,7 +7401,7 @@
       <c r="H183">
         <v>385</v>
       </c>
-      <c r="J183" s="2">
+      <c r="J183" s="1">
         <v>46574</v>
       </c>
       <c r="K183" t="b">
@@ -7459,7 +7433,7 @@
       <c r="H184">
         <v>417</v>
       </c>
-      <c r="J184" s="2">
+      <c r="J184" s="1">
         <v>46578</v>
       </c>
       <c r="K184" t="b">
@@ -7491,7 +7465,7 @@
       <c r="H185">
         <v>721</v>
       </c>
-      <c r="J185" s="2">
+      <c r="J185" s="1">
         <v>46345</v>
       </c>
       <c r="K185" t="b">
@@ -7523,7 +7497,7 @@
       <c r="H186">
         <v>721</v>
       </c>
-      <c r="J186" s="2">
+      <c r="J186" s="1">
         <v>46345</v>
       </c>
       <c r="K186" t="b">
@@ -7555,7 +7529,7 @@
       <c r="H187">
         <v>850</v>
       </c>
-      <c r="J187" s="2">
+      <c r="J187" s="1">
         <v>46366</v>
       </c>
       <c r="K187" t="b">
@@ -7587,7 +7561,7 @@
       <c r="H188">
         <v>850</v>
       </c>
-      <c r="J188" s="2">
+      <c r="J188" s="1">
         <v>46366</v>
       </c>
       <c r="K188" t="b">
@@ -7619,7 +7593,7 @@
       <c r="H189">
         <v>1661</v>
       </c>
-      <c r="J189" s="2">
+      <c r="J189" s="1">
         <v>46524</v>
       </c>
       <c r="K189" t="b">
@@ -7651,7 +7625,7 @@
       <c r="H190">
         <v>1661</v>
       </c>
-      <c r="J190" s="2">
+      <c r="J190" s="1">
         <v>46524</v>
       </c>
       <c r="K190" t="b">
@@ -7683,7 +7657,7 @@
       <c r="H191">
         <v>488</v>
       </c>
-      <c r="J191" s="2">
+      <c r="J191" s="1">
         <v>46190</v>
       </c>
       <c r="K191" t="b">
@@ -7715,7 +7689,7 @@
       <c r="H192">
         <v>25565</v>
       </c>
-      <c r="J192" s="2">
+      <c r="J192" s="1">
         <v>46190</v>
       </c>
       <c r="K192" t="b">
@@ -7747,7 +7721,7 @@
       <c r="H193">
         <v>25567</v>
       </c>
-      <c r="J193" s="2">
+      <c r="J193" s="1">
         <v>46190</v>
       </c>
       <c r="K193" t="b">
@@ -7779,7 +7753,7 @@
       <c r="H194">
         <v>31293</v>
       </c>
-      <c r="J194" s="2">
+      <c r="J194" s="1">
         <v>46190</v>
       </c>
       <c r="K194" t="b">

--- a/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
+++ b/Coordenadoria/02_Dados_Tratados/base_vencimentos_tratada.xlsx
@@ -5532,7 +5532,7 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>2731</v>
+        <v>2733</v>
       </c>
       <c r="C127" t="s">
         <v>224</v>
